--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7185E89-E2A8-481E-8174-D082ED3BF42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D37504-4442-4B67-8535-97C4CF4EEA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>ES_Prod</t>
+  </si>
+  <si>
+    <t>EE</t>
   </si>
 </sst>
 </file>
@@ -688,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -878,236 +881,241 @@
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10433,7 +10441,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -11024,10 +11032,10 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C54">
-        <v>-211.03200000000001</v>
+        <v>-6.6570737613344075</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -11035,10 +11043,10 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C55">
-        <v>-83.045000000000002</v>
+        <v>-211.03200000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -11046,10 +11054,10 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>-27.339084185091842</v>
+        <v>-83.045000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -11057,10 +11065,10 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57">
-        <v>-99.653999999999982</v>
+        <v>-27.339084185091842</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -11068,10 +11076,10 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58">
-        <v>-34.696428008002286</v>
+        <v>-99.653999999999982</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -11079,10 +11087,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C59">
-        <v>-19.54</v>
+        <v>-34.696428008002286</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -11090,10 +11098,10 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C60">
-        <v>-34.820653312201756</v>
+        <v>-19.54</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -11101,10 +11109,10 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C61">
-        <v>-55.689</v>
+        <v>-34.820653312201756</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -11112,10 +11120,10 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C62">
-        <v>-110.401</v>
+        <v>-55.689</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -11123,10 +11131,10 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C63">
-        <v>-13.995883970311864</v>
+        <v>-110.401</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -11134,10 +11142,10 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C64">
-        <v>-9.5558311621502252</v>
+        <v>-13.995883970311864</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -11145,10 +11153,10 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C65">
-        <v>-316.54799999999994</v>
+        <v>-9.5558311621502252</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -11156,10 +11164,10 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C66">
-        <v>-58.62</v>
+        <v>-316.54799999999994</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -11167,10 +11175,10 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C67">
-        <v>-286.26099999999997</v>
+        <v>-58.62</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
@@ -11178,10 +11186,10 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C68">
-        <v>-12.918429819775348</v>
+        <v>-286.26099999999997</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -11189,10 +11197,10 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-12.918429819775348</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -11200,7 +11208,7 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -11211,10 +11219,10 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C71">
-        <v>-453.32799999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -11222,10 +11230,10 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C72">
-        <v>-42.988</v>
+        <v>-453.32799999999997</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -11233,10 +11241,10 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>-42.988</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -11244,7 +11252,7 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -11255,7 +11263,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -11266,7 +11274,7 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -11277,7 +11285,7 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -11288,10 +11296,10 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C78">
-        <v>-10.747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -11299,10 +11307,10 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C79">
-        <v>-3.1361880225518983</v>
+        <v>-10.747</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
@@ -11310,10 +11318,10 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C80">
-        <v>-24.864095362311311</v>
+        <v>-3.1361880225518983</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
@@ -11321,21 +11329,21 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C81">
-        <v>-10.40036286731274</v>
+        <v>-24.864095362311311</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>-10.40036286731274</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -11343,7 +11351,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -11354,7 +11362,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -11365,7 +11373,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -11376,7 +11384,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -11387,7 +11395,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -11398,7 +11406,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -11409,7 +11417,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -11420,7 +11428,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11431,7 +11439,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11442,7 +11450,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -11453,7 +11461,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11464,7 +11472,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11475,7 +11483,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -11486,7 +11494,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -11497,7 +11505,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -11508,7 +11516,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -11519,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -11530,7 +11538,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -11541,7 +11549,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -11552,7 +11560,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -11563,7 +11571,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -11574,7 +11582,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -11585,7 +11593,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -11596,7 +11604,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -11607,7 +11615,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -11618,7 +11626,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -11629,7 +11637,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -11640,7 +11648,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -11651,7 +11659,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -11662,7 +11670,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11673,7 +11681,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11684,7 +11692,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -11695,7 +11703,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11706,7 +11714,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11717,7 +11725,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -11728,7 +11736,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11739,7 +11747,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11750,7 +11758,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11761,7 +11769,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11772,7 +11780,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11783,7 +11791,7 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11794,7 +11802,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11805,7 +11813,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -11816,7 +11824,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -11827,7 +11835,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -11838,7 +11846,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -11849,7 +11857,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -11860,7 +11868,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -11871,7 +11879,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -11882,7 +11890,7 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -11893,7 +11901,7 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -11904,7 +11912,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -11915,7 +11923,7 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -11926,7 +11934,7 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -11937,7 +11945,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -11948,7 +11956,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -11959,7 +11967,7 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -11970,7 +11978,7 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -11981,7 +11989,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -11989,13 +11997,13 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C142">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -12003,7 +12011,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12011,13 +12019,13 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -12025,7 +12033,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12036,7 +12044,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12047,7 +12055,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12058,7 +12066,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12069,7 +12077,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12080,7 +12088,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12091,7 +12099,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12102,7 +12110,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12113,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12124,7 +12132,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12135,7 +12143,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12146,7 +12154,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12157,7 +12165,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12168,7 +12176,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12179,7 +12187,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12190,7 +12198,7 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12201,7 +12209,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -12209,10 +12217,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -12223,7 +12231,7 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -12234,7 +12242,7 @@
         <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -12245,7 +12253,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -12253,10 +12261,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B166" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -12267,7 +12275,7 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -12278,9 +12286,31 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
+        <v>63</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" t="s">
+        <v>59</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B170" t="s">
         <v>70</v>
       </c>
-      <c r="C168">
+      <c r="C170">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D37504-4442-4B67-8535-97C4CF4EEA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1566B27A-FE11-4B38-9184-229B3678B3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -1151,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2148,129 +2148,145 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B126" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B127" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B129" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B130" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B131" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B133" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B134" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B135" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B136" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B137" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B138" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
+        <v>94</v>
+      </c>
+      <c r="B140" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>95</v>
+      </c>
+      <c r="B141" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>96</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B142" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2281,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I281"/>
+  <dimension ref="A1:I285"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6375,19 +6391,19 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="C142" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="D142">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="E142">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6396,7 +6412,7 @@
         <v>10000000</v>
       </c>
       <c r="H142">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -6404,19 +6420,19 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D143">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="E143">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6425,7 +6441,7 @@
         <v>10000000</v>
       </c>
       <c r="H143">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -6436,10 +6452,10 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C144" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D144">
         <v>10000</v>
@@ -6465,10 +6481,10 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D145">
         <v>10000</v>
@@ -6494,10 +6510,10 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C146" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D146">
         <v>10000</v>
@@ -6523,10 +6539,10 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C147" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D147">
         <v>10000</v>
@@ -6552,10 +6568,10 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D148">
         <v>10000</v>
@@ -6581,10 +6597,10 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D149">
         <v>10000</v>
@@ -6610,10 +6626,10 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C150" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D150">
         <v>10000</v>
@@ -6639,10 +6655,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C151" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D151">
         <v>10000</v>
@@ -6668,10 +6684,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C152" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D152">
         <v>10000</v>
@@ -6697,10 +6713,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C153" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D153">
         <v>10000</v>
@@ -6726,10 +6742,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="C154" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D154">
         <v>10000</v>
@@ -6755,10 +6771,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C155" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D155">
         <v>10000</v>
@@ -6784,10 +6800,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C156" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -6813,10 +6829,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C157" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D157">
         <v>10000</v>
@@ -6842,10 +6858,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C158" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D158">
         <v>10000</v>
@@ -6871,10 +6887,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C159" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D159">
         <v>10000</v>
@@ -6900,10 +6916,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D160">
         <v>10000</v>
@@ -6929,10 +6945,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C161" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D161">
         <v>10000</v>
@@ -6958,10 +6974,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C162" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D162">
         <v>10000</v>
@@ -6987,10 +7003,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C163" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D163">
         <v>10000</v>
@@ -7016,10 +7032,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C164" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D164">
         <v>10000</v>
@@ -7045,10 +7061,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C165" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D165">
         <v>10000</v>
@@ -7074,10 +7090,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C166" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D166">
         <v>10000</v>
@@ -7103,10 +7119,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
+        <v>56</v>
+      </c>
+      <c r="C167" t="s">
         <v>38</v>
-      </c>
-      <c r="C167" t="s">
-        <v>16</v>
       </c>
       <c r="D167">
         <v>10000</v>
@@ -7132,10 +7148,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C168" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D168">
         <v>10000</v>
@@ -7161,10 +7177,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
+        <v>38</v>
+      </c>
+      <c r="C169" t="s">
         <v>16</v>
-      </c>
-      <c r="C169" t="s">
-        <v>38</v>
       </c>
       <c r="D169">
         <v>10000</v>
@@ -7190,10 +7206,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D170">
         <v>10000</v>
@@ -7222,7 +7238,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D171">
         <v>10000</v>
@@ -7251,7 +7267,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D172">
         <v>10000</v>
@@ -7277,10 +7293,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C173" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D173">
         <v>10000</v>
@@ -7306,10 +7322,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C174" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D174">
         <v>10000</v>
@@ -7335,7 +7351,7 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C175" t="s">
         <v>16</v>
@@ -7364,10 +7380,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
+        <v>28</v>
+      </c>
+      <c r="C176" t="s">
         <v>42</v>
-      </c>
-      <c r="C176" t="s">
-        <v>28</v>
       </c>
       <c r="D176">
         <v>10000</v>
@@ -7396,7 +7412,7 @@
         <v>42</v>
       </c>
       <c r="C177" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D177">
         <v>10000</v>
@@ -7425,7 +7441,7 @@
         <v>42</v>
       </c>
       <c r="C178" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D178">
         <v>10000</v>
@@ -7454,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="C179" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D179">
         <v>10000</v>
@@ -7483,7 +7499,7 @@
         <v>42</v>
       </c>
       <c r="C180" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D180">
         <v>10000</v>
@@ -7512,7 +7528,7 @@
         <v>42</v>
       </c>
       <c r="C181" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D181">
         <v>10000</v>
@@ -7541,7 +7557,7 @@
         <v>42</v>
       </c>
       <c r="C182" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D182">
         <v>10000</v>
@@ -7570,7 +7586,7 @@
         <v>42</v>
       </c>
       <c r="C183" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D183">
         <v>10000</v>
@@ -7596,10 +7612,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C184" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D184">
         <v>10000</v>
@@ -7625,10 +7641,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C185" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D185">
         <v>10000</v>
@@ -7657,7 +7673,7 @@
         <v>60</v>
       </c>
       <c r="C186" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D186">
         <v>10000</v>
@@ -7686,7 +7702,7 @@
         <v>60</v>
       </c>
       <c r="C187" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D187">
         <v>10000</v>
@@ -7715,7 +7731,7 @@
         <v>60</v>
       </c>
       <c r="C188" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D188">
         <v>10000</v>
@@ -7741,10 +7757,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C189" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D189">
         <v>10000</v>
@@ -7770,10 +7786,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C190" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D190">
         <v>10000</v>
@@ -7802,7 +7818,7 @@
         <v>22</v>
       </c>
       <c r="C191" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D191">
         <v>10000</v>
@@ -7828,10 +7844,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
+        <v>22</v>
+      </c>
+      <c r="C192" t="s">
         <v>61</v>
-      </c>
-      <c r="C192" t="s">
-        <v>42</v>
       </c>
       <c r="D192">
         <v>10000</v>
@@ -7857,10 +7873,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C193" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D193">
         <v>10000</v>
@@ -7889,7 +7905,7 @@
         <v>61</v>
       </c>
       <c r="C194" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D194">
         <v>10000</v>
@@ -7915,7 +7931,7 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C195" t="s">
         <v>22</v>
@@ -7944,10 +7960,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C196" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D196">
         <v>10000</v>
@@ -7973,10 +7989,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C197" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D197">
         <v>10000</v>
@@ -8002,10 +8018,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
+        <v>64</v>
+      </c>
+      <c r="C198" t="s">
         <v>24</v>
-      </c>
-      <c r="C198" t="s">
-        <v>66</v>
       </c>
       <c r="D198">
         <v>10000</v>
@@ -8031,10 +8047,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C199" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D199">
         <v>10000</v>
@@ -8060,10 +8076,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C200" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D200">
         <v>10000</v>
@@ -8092,7 +8108,7 @@
         <v>18</v>
       </c>
       <c r="C201" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D201">
         <v>10000</v>
@@ -8118,10 +8134,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C202" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D202">
         <v>10000</v>
@@ -8147,10 +8163,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C203" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D203">
         <v>10000</v>
@@ -8176,7 +8192,7 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C204" t="s">
         <v>42</v>
@@ -8205,10 +8221,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C205" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D205">
         <v>10000</v>
@@ -8237,7 +8253,7 @@
         <v>62</v>
       </c>
       <c r="C206" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D206">
         <v>10000</v>
@@ -8263,10 +8279,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C207" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D207">
         <v>10000</v>
@@ -8292,10 +8308,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
+        <v>62</v>
+      </c>
+      <c r="C208" t="s">
         <v>65</v>
-      </c>
-      <c r="C208" t="s">
-        <v>62</v>
       </c>
       <c r="D208">
         <v>10000</v>
@@ -8324,7 +8340,7 @@
         <v>65</v>
       </c>
       <c r="C209" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D209">
         <v>10000</v>
@@ -8353,7 +8369,7 @@
         <v>65</v>
       </c>
       <c r="C210" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D210">
         <v>10000</v>
@@ -8379,10 +8395,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
+        <v>65</v>
+      </c>
+      <c r="C211" t="s">
         <v>66</v>
-      </c>
-      <c r="C211" t="s">
-        <v>24</v>
       </c>
       <c r="D211">
         <v>10000</v>
@@ -8408,10 +8424,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C212" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D212">
         <v>10000</v>
@@ -8440,7 +8456,7 @@
         <v>66</v>
       </c>
       <c r="C213" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D213">
         <v>10000</v>
@@ -8469,7 +8485,7 @@
         <v>66</v>
       </c>
       <c r="C214" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D214">
         <v>10000</v>
@@ -8495,10 +8511,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
+        <v>66</v>
+      </c>
+      <c r="C215" t="s">
         <v>67</v>
-      </c>
-      <c r="C215" t="s">
-        <v>68</v>
       </c>
       <c r="D215">
         <v>10000</v>
@@ -8524,10 +8540,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C216" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D216">
         <v>10000</v>
@@ -8553,10 +8569,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
+        <v>67</v>
+      </c>
+      <c r="C217" t="s">
         <v>68</v>
-      </c>
-      <c r="C217" t="s">
-        <v>67</v>
       </c>
       <c r="D217">
         <v>10000</v>
@@ -8582,10 +8598,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C218" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D218">
         <v>10000</v>
@@ -8614,7 +8630,7 @@
         <v>68</v>
       </c>
       <c r="C219" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D219">
         <v>10000</v>
@@ -8643,7 +8659,7 @@
         <v>68</v>
       </c>
       <c r="C220" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -8672,7 +8688,7 @@
         <v>68</v>
       </c>
       <c r="C221" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D221">
         <v>10000</v>
@@ -8698,10 +8714,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C222" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D222">
         <v>10000</v>
@@ -8727,10 +8743,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C223" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D223">
         <v>10000</v>
@@ -8756,7 +8772,7 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
@@ -8788,7 +8804,7 @@
         <v>51</v>
       </c>
       <c r="C225" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D225">
         <v>10000</v>
@@ -8817,7 +8833,7 @@
         <v>51</v>
       </c>
       <c r="C226" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D226">
         <v>10000</v>
@@ -8843,10 +8859,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C227" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D227">
         <v>10000</v>
@@ -8872,10 +8888,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C228" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D228">
         <v>10000</v>
@@ -8901,10 +8917,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
+        <v>26</v>
+      </c>
+      <c r="C229" t="s">
         <v>72</v>
-      </c>
-      <c r="C229" t="s">
-        <v>26</v>
       </c>
       <c r="D229">
         <v>10000</v>
@@ -8930,7 +8946,7 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C230" t="s">
         <v>53</v>
@@ -8959,10 +8975,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C231" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D231">
         <v>10000</v>
@@ -8988,10 +9004,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C232" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D232">
         <v>10000</v>
@@ -9017,10 +9033,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C233" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D233">
         <v>10000</v>
@@ -9046,10 +9062,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C234" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D234">
         <v>10000</v>
@@ -9075,10 +9091,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C235" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D235">
         <v>10000</v>
@@ -9107,7 +9123,7 @@
         <v>58</v>
       </c>
       <c r="C236" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D236">
         <v>10000</v>
@@ -9136,7 +9152,7 @@
         <v>58</v>
       </c>
       <c r="C237" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D237">
         <v>10000</v>
@@ -9162,10 +9178,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C238" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D238">
         <v>10000</v>
@@ -9191,10 +9207,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C239" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D239">
         <v>10000</v>
@@ -9220,10 +9236,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C240" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D240">
         <v>10000</v>
@@ -9252,7 +9268,7 @@
         <v>53</v>
       </c>
       <c r="C241" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D241">
         <v>10000</v>
@@ -9278,10 +9294,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C242" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D242">
         <v>10000</v>
@@ -9307,10 +9323,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C243" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D243">
         <v>10000</v>
@@ -9336,10 +9352,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C244" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D244">
         <v>10000</v>
@@ -9365,10 +9381,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C245" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D245">
         <v>10000</v>
@@ -9394,10 +9410,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C246" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9423,10 +9439,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C247" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D247">
         <v>10000</v>
@@ -9452,10 +9468,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C248" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D248">
         <v>10000</v>
@@ -9481,10 +9497,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C249" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D249">
         <v>10000</v>
@@ -9510,10 +9526,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C250" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D250">
         <v>10000</v>
@@ -9539,10 +9555,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C251" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D251">
         <v>10000</v>
@@ -9568,10 +9584,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C252" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D252">
         <v>10000</v>
@@ -9597,10 +9613,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C253" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D253">
         <v>10000</v>
@@ -9626,10 +9642,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C254" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D254">
         <v>10000</v>
@@ -9655,10 +9671,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C255" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D255">
         <v>10000</v>
@@ -9687,7 +9703,7 @@
         <v>48</v>
       </c>
       <c r="C256" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D256">
         <v>10000</v>
@@ -9716,7 +9732,7 @@
         <v>48</v>
       </c>
       <c r="C257" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D257">
         <v>10000</v>
@@ -9745,7 +9761,7 @@
         <v>48</v>
       </c>
       <c r="C258" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D258">
         <v>10000</v>
@@ -9771,10 +9787,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C259" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D259">
         <v>10000</v>
@@ -9800,10 +9816,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C260" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D260">
         <v>10000</v>
@@ -9829,10 +9845,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C261" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D261">
         <v>10000</v>
@@ -9858,10 +9874,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C262" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D262">
         <v>10000</v>
@@ -9887,10 +9903,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C263" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -9916,10 +9932,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C264" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D264">
         <v>10000</v>
@@ -9928,7 +9944,7 @@
         <v>10000</v>
       </c>
       <c r="F264">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G264">
         <v>10000000</v>
@@ -9945,10 +9961,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C265" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -9957,7 +9973,7 @@
         <v>10000</v>
       </c>
       <c r="F265">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G265">
         <v>10000000</v>
@@ -9974,10 +9990,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C266" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D266">
         <v>10000</v>
@@ -10003,10 +10019,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C267" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10032,10 +10048,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C268" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D268">
         <v>10000</v>
@@ -10061,10 +10077,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C269" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D269">
         <v>10000</v>
@@ -10090,10 +10106,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C270" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D270">
         <v>10000</v>
@@ -10119,10 +10135,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C271" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D271">
         <v>10000</v>
@@ -10148,10 +10164,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C272" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D272">
         <v>10000</v>
@@ -10177,10 +10193,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C273" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D273">
         <v>10000</v>
@@ -10206,10 +10222,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C274" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10235,10 +10251,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C275" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D275">
         <v>10000</v>
@@ -10264,10 +10280,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C276" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D276">
         <v>10000</v>
@@ -10293,10 +10309,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C277" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D277">
         <v>10000</v>
@@ -10322,10 +10338,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C278" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D278">
         <v>10000</v>
@@ -10351,10 +10367,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C279" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D279">
         <v>10000</v>
@@ -10380,10 +10396,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C280" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="D280">
         <v>10000</v>
@@ -10392,7 +10408,7 @@
         <v>10000</v>
       </c>
       <c r="F280">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G280">
         <v>10000000</v>
@@ -10409,27 +10425,143 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
+        <v>96</v>
+      </c>
+      <c r="C281" t="s">
+        <v>34</v>
+      </c>
+      <c r="D281">
+        <v>10000</v>
+      </c>
+      <c r="E281">
+        <v>10000</v>
+      </c>
+      <c r="F281">
+        <v>100</v>
+      </c>
+      <c r="G281">
+        <v>10000000</v>
+      </c>
+      <c r="H281">
+        <v>1000</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>12</v>
+      </c>
+      <c r="B282" t="s">
+        <v>53</v>
+      </c>
+      <c r="C282" t="s">
         <v>75</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D282">
+        <v>10000</v>
+      </c>
+      <c r="E282">
+        <v>10000</v>
+      </c>
+      <c r="F282">
+        <v>1</v>
+      </c>
+      <c r="G282">
+        <v>10000000</v>
+      </c>
+      <c r="H282">
+        <v>1000</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>12</v>
+      </c>
+      <c r="B283" t="s">
+        <v>75</v>
+      </c>
+      <c r="C283" t="s">
         <v>30</v>
       </c>
-      <c r="D281">
-        <v>10000</v>
-      </c>
-      <c r="E281">
-        <v>10000</v>
-      </c>
-      <c r="F281">
-        <v>1</v>
-      </c>
-      <c r="G281">
-        <v>10000000</v>
-      </c>
-      <c r="H281">
-        <v>1000</v>
-      </c>
-      <c r="I281">
+      <c r="D283">
+        <v>10000</v>
+      </c>
+      <c r="E283">
+        <v>10000</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>10000000</v>
+      </c>
+      <c r="H283">
+        <v>1000</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>12</v>
+      </c>
+      <c r="B284" t="s">
+        <v>97</v>
+      </c>
+      <c r="C284" t="s">
+        <v>72</v>
+      </c>
+      <c r="D284">
+        <v>10000</v>
+      </c>
+      <c r="E284">
+        <v>10000</v>
+      </c>
+      <c r="F284">
+        <v>100</v>
+      </c>
+      <c r="G284">
+        <v>10000000</v>
+      </c>
+      <c r="H284">
+        <v>1000</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>12</v>
+      </c>
+      <c r="B285" t="s">
+        <v>72</v>
+      </c>
+      <c r="C285" t="s">
+        <v>97</v>
+      </c>
+      <c r="D285">
+        <v>10000</v>
+      </c>
+      <c r="E285">
+        <v>10000</v>
+      </c>
+      <c r="F285">
+        <v>100</v>
+      </c>
+      <c r="G285">
+        <v>10000000</v>
+      </c>
+      <c r="H285">
+        <v>1000</v>
+      </c>
+      <c r="I285">
         <v>1</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1566B27A-FE11-4B38-9184-229B3678B3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7CE7E8-146D-4101-B7C4-1C8222EA1E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -97,12 +97,6 @@
   </si>
   <si>
     <t>FR</t>
-  </si>
-  <si>
-    <t>GR_LNG</t>
-  </si>
-  <si>
-    <t>GR</t>
   </si>
   <si>
     <t>IT_LNG</t>
@@ -309,9 +303,6 @@
     <t>FR_Prod</t>
   </si>
   <si>
-    <t>GR_Prod</t>
-  </si>
-  <si>
     <t>HU_Prod</t>
   </si>
   <si>
@@ -334,6 +325,15 @@
   </si>
   <si>
     <t>EE</t>
+  </si>
+  <si>
+    <t>EL_LNG</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>EL_Prod</t>
   </si>
 </sst>
 </file>
@@ -395,9 +395,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -435,7 +435,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -541,7 +541,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -683,7 +683,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -711,122 +711,122 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
@@ -836,37 +836,37 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
@@ -876,247 +876,247 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1180,191 +1180,191 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -1383,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -1391,7 +1391,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -1399,7 +1399,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
@@ -1412,7 +1412,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
@@ -1420,15 +1420,15 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
@@ -1436,31 +1436,31 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -1468,119 +1468,119 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
@@ -1588,34 +1588,34 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -1631,7 +1631,7 @@
         <v>18</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -1639,244 +1639,244 @@
         <v>18</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s">
         <v>40</v>
-      </c>
-      <c r="B62" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" t="s">
         <v>67</v>
-      </c>
-      <c r="B76" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" t="s">
         <v>68</v>
-      </c>
-      <c r="B80" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B88" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
         <v>18</v>
@@ -1884,199 +1884,199 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
         <v>32</v>
-      </c>
-      <c r="B93" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B96" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B106" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B111" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B112" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s">
         <v>16</v>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B117" t="s">
         <v>18</v>
@@ -2092,103 +2092,103 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B122" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B125" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B127" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B128" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B129" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
@@ -2196,31 +2196,31 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B131" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B133" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B134" t="s">
         <v>18</v>
@@ -2228,66 +2228,66 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B136" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B137" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B138" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B139" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B140" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2392,10 +2392,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D4">
         <v>73.274999999999991</v>
@@ -2421,10 +2421,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>155.83149999999998</v>
@@ -2450,10 +2450,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>25.402000000000001</v>
@@ -2479,10 +2479,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>39.08</v>
@@ -2508,10 +2508,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>122.125</v>
@@ -2537,10 +2537,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>60.573999999999998</v>
@@ -2566,10 +2566,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>74.251999999999995</v>
@@ -2595,10 +2595,10 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>655.56699999999989</v>
@@ -2624,10 +2624,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>425.97199999999998</v>
@@ -2653,10 +2653,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13">
         <v>510.97099999999995</v>
@@ -2682,10 +2682,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14">
         <v>10000</v>
@@ -2711,10 +2711,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15">
         <v>10000</v>
@@ -2740,10 +2740,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>10000</v>
@@ -2769,7 +2769,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -2798,10 +2798,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18">
         <v>10000</v>
@@ -2827,10 +2827,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D19">
         <v>10000</v>
@@ -2856,10 +2856,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20">
         <v>10000</v>
@@ -2885,7 +2885,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -2914,10 +2914,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D22">
         <v>10000</v>
@@ -2943,10 +2943,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -2972,10 +2972,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -3001,10 +3001,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D25">
         <v>10000</v>
@@ -3030,10 +3030,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -3059,10 +3059,10 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27">
         <v>10000</v>
@@ -3088,10 +3088,10 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>10000</v>
@@ -3117,10 +3117,10 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D29">
         <v>10000</v>
@@ -3146,10 +3146,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -3175,10 +3175,10 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D31">
         <v>10000</v>
@@ -3204,10 +3204,10 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D32">
         <v>10000</v>
@@ -3233,10 +3233,10 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <v>10000</v>
@@ -3262,10 +3262,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D34">
         <v>10000</v>
@@ -3291,10 +3291,10 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D35">
         <v>10000</v>
@@ -3320,10 +3320,10 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D36">
         <v>10000</v>
@@ -3349,10 +3349,10 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>10000</v>
@@ -3378,10 +3378,10 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D38">
         <v>10000</v>
@@ -3407,10 +3407,10 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D39">
         <v>10000</v>
@@ -3436,10 +3436,10 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>10000</v>
@@ -3465,10 +3465,10 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D41">
         <v>10000</v>
@@ -3494,10 +3494,10 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D42">
         <v>10000</v>
@@ -3523,7 +3523,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
         <v>16</v>
@@ -3552,10 +3552,10 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D44">
         <v>140.52500000000001</v>
@@ -3584,7 +3584,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D45">
         <v>293.24099999999999</v>
@@ -3613,7 +3613,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D46">
         <v>120.88800000000001</v>
@@ -3642,7 +3642,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D47">
         <v>117.81104999999999</v>
@@ -3697,7 +3697,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
         <v>16</v>
@@ -3726,10 +3726,10 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D50">
         <v>702.90714500000001</v>
@@ -3755,7 +3755,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
@@ -3784,10 +3784,10 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D52">
         <v>594.33059500000013</v>
@@ -3813,10 +3813,10 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D53">
         <v>125.65051999999997</v>
@@ -3842,10 +3842,10 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D54">
         <v>119.72</v>
@@ -3871,7 +3871,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
@@ -3900,10 +3900,10 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D56">
         <v>49.680879999999995</v>
@@ -3929,10 +3929,10 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>85.227500000000006</v>
@@ -3958,10 +3958,10 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>658.37605000000008</v>
@@ -3987,10 +3987,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D59">
         <v>9.7491500000000002</v>
@@ -4016,10 +4016,10 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D60">
         <v>124.08832</v>
@@ -4045,10 +4045,10 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61">
         <v>419.75</v>
@@ -4074,10 +4074,10 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D62">
         <v>41.0625</v>
@@ -4103,10 +4103,10 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D63">
         <v>89.972499999999997</v>
@@ -4132,10 +4132,10 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D64">
         <v>55.881500000000003</v>
@@ -4161,10 +4161,10 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D65">
         <v>70.627499999999998</v>
@@ -4190,10 +4190,10 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D66">
         <v>157.46100000000001</v>
@@ -4219,10 +4219,10 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D67">
         <v>10.4025</v>
@@ -4248,10 +4248,10 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D68">
         <v>63.07200000000001</v>
@@ -4277,10 +4277,10 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D69">
         <v>233.74600000000001</v>
@@ -4306,7 +4306,7 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C70" t="s">
         <v>18</v>
@@ -4335,10 +4335,10 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D71">
         <v>7.8475000000000001</v>
@@ -4364,10 +4364,10 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72">
         <v>19.6005</v>
@@ -4393,10 +4393,10 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D73">
         <v>2.8105000000000002</v>
@@ -4422,10 +4422,10 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D74">
         <v>17.72805</v>
@@ -4483,7 +4483,7 @@
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D76">
         <v>81.394999999999996</v>
@@ -4512,7 +4512,7 @@
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D77">
         <v>60.068779999999997</v>
@@ -4538,10 +4538,10 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" t="s">
         <v>40</v>
-      </c>
-      <c r="C78" t="s">
-        <v>42</v>
       </c>
       <c r="D78">
         <v>1.5034349999999999</v>
@@ -4567,10 +4567,10 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D79">
         <v>340.03399999999999</v>
@@ -4596,10 +4596,10 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D80">
         <v>449.59203500000001</v>
@@ -4625,10 +4625,10 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>10.220000000000001</v>
@@ -4654,10 +4654,10 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C82" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D82">
         <v>454.93600000000004</v>
@@ -4683,10 +4683,10 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D83">
         <v>573.19600000000003</v>
@@ -4712,10 +4712,10 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D84">
         <v>167.024</v>
@@ -4741,10 +4741,10 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C85" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D85">
         <v>47.048499999999997</v>
@@ -4770,10 +4770,10 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D86">
         <v>151.84</v>
@@ -4799,10 +4799,10 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D87">
         <v>28.251000000000005</v>
@@ -4828,10 +4828,10 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C88" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D88">
         <v>18.572295</v>
@@ -4857,10 +4857,10 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D89">
         <v>51.83</v>
@@ -4886,10 +4886,10 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D90">
         <v>28.287500000000001</v>
@@ -4915,10 +4915,10 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C91" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D91">
         <v>122.3699</v>
@@ -4944,10 +4944,10 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" t="s">
         <v>67</v>
-      </c>
-      <c r="C92" t="s">
-        <v>69</v>
       </c>
       <c r="D92">
         <v>6.5626999999999995</v>
@@ -4973,10 +4973,10 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C93" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D93">
         <v>170.63749999999999</v>
@@ -5002,10 +5002,10 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D94">
         <v>42.997</v>
@@ -5031,10 +5031,10 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C95" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D95">
         <v>54.074750000000002</v>
@@ -5060,10 +5060,10 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D96">
         <v>181.46340000000004</v>
@@ -5089,10 +5089,10 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C97" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D97">
         <v>23.659299999999998</v>
@@ -5118,10 +5118,10 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D98">
         <v>18.359500000000001</v>
@@ -5147,10 +5147,10 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C99" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D99">
         <v>294.09875000000005</v>
@@ -5176,10 +5176,10 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C100" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D100">
         <v>44.603000000000002</v>
@@ -5205,10 +5205,10 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C101" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D101">
         <v>20.330500000000001</v>
@@ -5234,10 +5234,10 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D102">
         <v>24.673999999999996</v>
@@ -5263,10 +5263,10 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D103">
         <v>41.683</v>
@@ -5292,10 +5292,10 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D104">
         <v>23.761499999999998</v>
@@ -5321,10 +5321,10 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C105" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D105">
         <v>31.024999999999999</v>
@@ -5350,7 +5350,7 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
@@ -5379,10 +5379,10 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D107">
         <v>52.56</v>
@@ -5408,10 +5408,10 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" t="s">
         <v>32</v>
-      </c>
-      <c r="C108" t="s">
-        <v>34</v>
       </c>
       <c r="D108">
         <v>29.2</v>
@@ -5437,10 +5437,10 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D109">
         <v>49.494</v>
@@ -5466,10 +5466,10 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D110">
         <v>816.06700000000012</v>
@@ -5495,10 +5495,10 @@
         <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C111" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D111">
         <v>188.88749999999999</v>
@@ -5524,10 +5524,10 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D112">
         <v>424.64100000000008</v>
@@ -5553,10 +5553,10 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C113" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D113">
         <v>0.80300000000000016</v>
@@ -5582,10 +5582,10 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D114">
         <v>635.83000000000004</v>
@@ -5611,10 +5611,10 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C115" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D115">
         <v>61.32</v>
@@ -5640,10 +5640,10 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D116">
         <v>80.3</v>
@@ -5669,10 +5669,10 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C117" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D117">
         <v>200.71350000000001</v>
@@ -5698,10 +5698,10 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C118" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D118">
         <v>256.15699999999998</v>
@@ -5727,10 +5727,10 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D119">
         <v>145.489</v>
@@ -5756,10 +5756,10 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C120" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D120">
         <v>161.62200000000001</v>
@@ -5785,10 +5785,10 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D121">
         <v>439.27749999999992</v>
@@ -5814,10 +5814,10 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D122">
         <v>439.27749999999992</v>
@@ -5843,10 +5843,10 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D123">
         <v>118.77099999999999</v>
@@ -5872,10 +5872,10 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C124" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D124">
         <v>486.91</v>
@@ -5901,10 +5901,10 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D125">
         <v>144.17500000000001</v>
@@ -5930,10 +5930,10 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C126" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D126">
         <v>89.716999999999999</v>
@@ -5959,10 +5959,10 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
+        <v>66</v>
+      </c>
+      <c r="C127" t="s">
         <v>68</v>
-      </c>
-      <c r="C127" t="s">
-        <v>70</v>
       </c>
       <c r="D127">
         <v>12.1837</v>
@@ -5988,10 +5988,10 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C128" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D128">
         <v>180.20050000000001</v>
@@ -6017,10 +6017,10 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C129" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D129">
         <v>421.21</v>
@@ -6046,10 +6046,10 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D130">
         <v>123.04150000000001</v>
@@ -6075,10 +6075,10 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C131" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D131">
         <v>455.15499999999997</v>
@@ -6104,10 +6104,10 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D132">
         <v>351.714</v>
@@ -6133,7 +6133,7 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C133" t="s">
         <v>16</v>
@@ -6162,7 +6162,7 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -6191,10 +6191,10 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C135" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D135">
         <v>513.19000000000005</v>
@@ -6220,10 +6220,10 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D136">
         <v>67.451999999999998</v>
@@ -6249,10 +6249,10 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C137" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D137">
         <v>200.71350000000001</v>
@@ -6278,10 +6278,10 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D138">
         <v>144.17500000000001</v>
@@ -6307,10 +6307,10 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C139" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D139">
         <v>123.04150000000001</v>
@@ -6336,10 +6336,10 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C140" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D140">
         <v>421.21</v>
@@ -6365,10 +6365,10 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C141" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D141">
         <v>14.965</v>
@@ -6394,10 +6394,10 @@
         <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C142" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D142">
         <v>24.424999999999997</v>
@@ -6423,10 +6423,10 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C143" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D143">
         <v>24.424999999999997</v>
@@ -6510,10 +6510,10 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C146" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D146">
         <v>10000</v>
@@ -6539,10 +6539,10 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C147" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D147">
         <v>10000</v>
@@ -6568,10 +6568,10 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C148" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D148">
         <v>10000</v>
@@ -6597,10 +6597,10 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C149" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D149">
         <v>10000</v>
@@ -6626,10 +6626,10 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C150" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D150">
         <v>10000</v>
@@ -6655,10 +6655,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C151" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D151">
         <v>10000</v>
@@ -6684,10 +6684,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C152" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D152">
         <v>10000</v>
@@ -6713,10 +6713,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C153" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D153">
         <v>10000</v>
@@ -6742,10 +6742,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C154" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D154">
         <v>10000</v>
@@ -6771,10 +6771,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C155" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D155">
         <v>10000</v>
@@ -6800,10 +6800,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C156" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -6829,10 +6829,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C157" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D157">
         <v>10000</v>
@@ -6858,10 +6858,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C158" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D158">
         <v>10000</v>
@@ -6887,10 +6887,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C159" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D159">
         <v>10000</v>
@@ -6916,10 +6916,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C160" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D160">
         <v>10000</v>
@@ -6945,10 +6945,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D161">
         <v>10000</v>
@@ -6974,10 +6974,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C162" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D162">
         <v>10000</v>
@@ -7003,10 +7003,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C163" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D163">
         <v>10000</v>
@@ -7032,10 +7032,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C164" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D164">
         <v>10000</v>
@@ -7061,10 +7061,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C165" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D165">
         <v>10000</v>
@@ -7090,10 +7090,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C166" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D166">
         <v>10000</v>
@@ -7119,10 +7119,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C167" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D167">
         <v>10000</v>
@@ -7148,10 +7148,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C168" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D168">
         <v>10000</v>
@@ -7177,7 +7177,7 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C169" t="s">
         <v>16</v>
@@ -7206,10 +7206,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C170" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D170">
         <v>10000</v>
@@ -7238,7 +7238,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D171">
         <v>10000</v>
@@ -7267,7 +7267,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D172">
         <v>10000</v>
@@ -7296,7 +7296,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D173">
         <v>10000</v>
@@ -7351,7 +7351,7 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C175" t="s">
         <v>16</v>
@@ -7380,10 +7380,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C176" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D176">
         <v>10000</v>
@@ -7409,7 +7409,7 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C177" t="s">
         <v>16</v>
@@ -7438,10 +7438,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C178" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D178">
         <v>10000</v>
@@ -7467,10 +7467,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C179" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D179">
         <v>10000</v>
@@ -7496,10 +7496,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C180" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D180">
         <v>10000</v>
@@ -7525,7 +7525,7 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C181" t="s">
         <v>18</v>
@@ -7554,10 +7554,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C182" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D182">
         <v>10000</v>
@@ -7583,10 +7583,10 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C183" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D183">
         <v>10000</v>
@@ -7612,10 +7612,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C184" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D184">
         <v>10000</v>
@@ -7641,10 +7641,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C185" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D185">
         <v>10000</v>
@@ -7670,10 +7670,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C186" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D186">
         <v>10000</v>
@@ -7699,10 +7699,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D187">
         <v>10000</v>
@@ -7728,10 +7728,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C188" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D188">
         <v>10000</v>
@@ -7757,10 +7757,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C189" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D189">
         <v>10000</v>
@@ -7786,10 +7786,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C190" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D190">
         <v>10000</v>
@@ -7815,10 +7815,10 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D191">
         <v>10000</v>
@@ -7844,10 +7844,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D192">
         <v>10000</v>
@@ -7873,10 +7873,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C193" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D193">
         <v>10000</v>
@@ -7902,10 +7902,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C194" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D194">
         <v>10000</v>
@@ -7931,10 +7931,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D195">
         <v>10000</v>
@@ -7960,7 +7960,7 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
@@ -7989,10 +7989,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C197" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D197">
         <v>10000</v>
@@ -8018,10 +8018,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D198">
         <v>10000</v>
@@ -8047,10 +8047,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D199">
         <v>10000</v>
@@ -8076,10 +8076,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D200">
         <v>10000</v>
@@ -8137,7 +8137,7 @@
         <v>18</v>
       </c>
       <c r="C202" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D202">
         <v>10000</v>
@@ -8166,7 +8166,7 @@
         <v>18</v>
       </c>
       <c r="C203" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D203">
         <v>10000</v>
@@ -8192,10 +8192,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
+        <v>38</v>
+      </c>
+      <c r="C204" t="s">
         <v>40</v>
-      </c>
-      <c r="C204" t="s">
-        <v>42</v>
       </c>
       <c r="D204">
         <v>10000</v>
@@ -8221,10 +8221,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C205" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D205">
         <v>10000</v>
@@ -8250,10 +8250,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C206" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D206">
         <v>10000</v>
@@ -8279,10 +8279,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C207" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D207">
         <v>10000</v>
@@ -8308,10 +8308,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C208" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D208">
         <v>10000</v>
@@ -8337,10 +8337,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C209" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D209">
         <v>10000</v>
@@ -8366,10 +8366,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C210" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D210">
         <v>10000</v>
@@ -8395,10 +8395,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C211" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D211">
         <v>10000</v>
@@ -8424,10 +8424,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C212" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D212">
         <v>10000</v>
@@ -8453,10 +8453,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C213" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D213">
         <v>10000</v>
@@ -8482,10 +8482,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C214" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D214">
         <v>10000</v>
@@ -8511,10 +8511,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C215" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D215">
         <v>10000</v>
@@ -8540,10 +8540,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C216" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D216">
         <v>10000</v>
@@ -8569,10 +8569,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C217" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D217">
         <v>10000</v>
@@ -8598,10 +8598,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
+        <v>65</v>
+      </c>
+      <c r="C218" t="s">
         <v>67</v>
-      </c>
-      <c r="C218" t="s">
-        <v>69</v>
       </c>
       <c r="D218">
         <v>10000</v>
@@ -8627,10 +8627,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C219" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D219">
         <v>10000</v>
@@ -8656,10 +8656,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C220" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -8685,10 +8685,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C221" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D221">
         <v>10000</v>
@@ -8714,10 +8714,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
+        <v>66</v>
+      </c>
+      <c r="C222" t="s">
         <v>68</v>
-      </c>
-      <c r="C222" t="s">
-        <v>70</v>
       </c>
       <c r="D222">
         <v>10000</v>
@@ -8743,10 +8743,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C223" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D223">
         <v>10000</v>
@@ -8772,10 +8772,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C224" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D224">
         <v>10000</v>
@@ -8801,10 +8801,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C225" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D225">
         <v>10000</v>
@@ -8830,10 +8830,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C226" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D226">
         <v>10000</v>
@@ -8859,10 +8859,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C227" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D227">
         <v>10000</v>
@@ -8888,10 +8888,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C228" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D228">
         <v>10000</v>
@@ -8917,10 +8917,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C229" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D229">
         <v>10000</v>
@@ -8946,10 +8946,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C230" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D230">
         <v>10000</v>
@@ -8975,10 +8975,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C231" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D231">
         <v>10000</v>
@@ -9004,10 +9004,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C232" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D232">
         <v>10000</v>
@@ -9033,7 +9033,7 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C233" t="s">
         <v>18</v>
@@ -9062,10 +9062,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C234" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D234">
         <v>10000</v>
@@ -9091,10 +9091,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
+        <v>30</v>
+      </c>
+      <c r="C235" t="s">
         <v>32</v>
-      </c>
-      <c r="C235" t="s">
-        <v>34</v>
       </c>
       <c r="D235">
         <v>10000</v>
@@ -9120,10 +9120,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C236" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D236">
         <v>10000</v>
@@ -9149,10 +9149,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C237" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D237">
         <v>10000</v>
@@ -9178,10 +9178,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C238" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D238">
         <v>10000</v>
@@ -9207,10 +9207,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C239" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D239">
         <v>10000</v>
@@ -9236,10 +9236,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C240" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D240">
         <v>10000</v>
@@ -9265,10 +9265,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C241" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D241">
         <v>10000</v>
@@ -9294,10 +9294,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C242" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D242">
         <v>10000</v>
@@ -9323,10 +9323,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C243" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D243">
         <v>10000</v>
@@ -9352,10 +9352,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C244" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D244">
         <v>10000</v>
@@ -9381,10 +9381,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C245" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D245">
         <v>10000</v>
@@ -9410,10 +9410,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C246" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9439,10 +9439,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C247" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D247">
         <v>10000</v>
@@ -9468,10 +9468,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D248">
         <v>10000</v>
@@ -9497,10 +9497,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C249" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D249">
         <v>10000</v>
@@ -9526,10 +9526,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C250" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D250">
         <v>10000</v>
@@ -9555,10 +9555,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C251" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D251">
         <v>10000</v>
@@ -9584,10 +9584,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C252" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D252">
         <v>10000</v>
@@ -9613,10 +9613,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C253" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D253">
         <v>10000</v>
@@ -9642,10 +9642,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C254" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D254">
         <v>10000</v>
@@ -9671,10 +9671,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D255">
         <v>10000</v>
@@ -9700,10 +9700,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C256" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D256">
         <v>10000</v>
@@ -9729,10 +9729,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C257" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D257">
         <v>10000</v>
@@ -9758,7 +9758,7 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C258" t="s">
         <v>16</v>
@@ -9787,7 +9787,7 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C259" t="s">
         <v>18</v>
@@ -9816,10 +9816,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C260" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D260">
         <v>10000</v>
@@ -9845,10 +9845,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C261" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D261">
         <v>10000</v>
@@ -9874,10 +9874,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C262" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D262">
         <v>10000</v>
@@ -9903,10 +9903,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C263" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -9932,10 +9932,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C264" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D264">
         <v>10000</v>
@@ -9961,10 +9961,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C265" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -9990,10 +9990,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C266" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D266">
         <v>10000</v>
@@ -10019,10 +10019,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C267" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10048,10 +10048,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D268">
         <v>10000</v>
@@ -10077,7 +10077,7 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C269" t="s">
         <v>16</v>
@@ -10106,10 +10106,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C270" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D270">
         <v>10000</v>
@@ -10135,10 +10135,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C271" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D271">
         <v>10000</v>
@@ -10164,10 +10164,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C272" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D272">
         <v>10000</v>
@@ -10193,7 +10193,7 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C273" t="s">
         <v>18</v>
@@ -10222,10 +10222,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C274" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10251,10 +10251,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C275" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D275">
         <v>10000</v>
@@ -10280,10 +10280,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C276" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D276">
         <v>10000</v>
@@ -10309,10 +10309,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C277" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D277">
         <v>10000</v>
@@ -10338,10 +10338,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C278" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D278">
         <v>10000</v>
@@ -10367,10 +10367,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C279" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D279">
         <v>10000</v>
@@ -10396,10 +10396,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C280" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D280">
         <v>10000</v>
@@ -10425,10 +10425,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C281" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D281">
         <v>10000</v>
@@ -10454,10 +10454,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C282" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D282">
         <v>10000</v>
@@ -10483,10 +10483,10 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C283" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D283">
         <v>10000</v>
@@ -10512,10 +10512,10 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C284" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D284">
         <v>10000</v>
@@ -10541,10 +10541,10 @@
         <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C285" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D285">
         <v>10000</v>
@@ -10614,7 +10614,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C4">
         <v>73.274999999999991</v>
@@ -10625,7 +10625,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>155.83149999999998</v>
@@ -10636,7 +10636,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>25.402000000000001</v>
@@ -10647,7 +10647,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>39.08</v>
@@ -10658,7 +10658,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>122.125</v>
@@ -10669,7 +10669,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>60.573999999999998</v>
@@ -10680,7 +10680,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>74.251999999999995</v>
@@ -10691,7 +10691,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>655.56699999999989</v>
@@ -10702,7 +10702,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>425.97199999999998</v>
@@ -10713,7 +10713,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>510.97099999999995</v>
@@ -10724,7 +10724,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>0.55586415</v>
@@ -10746,7 +10746,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C16">
         <v>796.255</v>
@@ -10757,7 +10757,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17">
         <v>7.5617455199999997</v>
@@ -10768,7 +10768,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18">
         <v>5.7643000000000007E-2</v>
@@ -10779,7 +10779,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19">
         <v>0.53100926999999998</v>
@@ -10790,7 +10790,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20">
         <v>8.6795214499999993</v>
@@ -10801,7 +10801,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>1.9156527500000002</v>
@@ -10812,7 +10812,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22">
         <v>0.16949973000000002</v>
@@ -10823,7 +10823,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C23">
         <v>6.3309600000000021E-2</v>
@@ -10834,7 +10834,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>16.46245</v>
@@ -10845,7 +10845,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>19.829690269999997</v>
@@ -10856,7 +10856,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>3.9959299999999995</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>0.6516687699999999</v>
@@ -10878,7 +10878,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>5.2113180000000002E-2</v>
@@ -10889,7 +10889,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29">
         <v>4.2744726999999996</v>
@@ -10900,7 +10900,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C30">
         <v>0.44941999999999999</v>
@@ -10911,7 +10911,7 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>13.947075569999997</v>
@@ -10922,7 +10922,7 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>47.618979999999993</v>
@@ -10933,7 +10933,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>38.415639999999996</v>
@@ -10944,7 +10944,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>129.941</v>
@@ -10955,7 +10955,7 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35">
         <v>234.14902171</v>
@@ -10966,7 +10966,7 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36">
         <v>1135.3337630899998</v>
@@ -10977,7 +10977,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C37">
         <v>54.642437600000001</v>
@@ -10988,7 +10988,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C38">
         <v>88.09608999999999</v>
@@ -10999,7 +10999,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39">
         <v>6238.1449999999995</v>
@@ -11010,7 +11010,7 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C40">
         <v>18.562999999999999</v>
@@ -11021,7 +11021,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41">
         <v>320.81311303999996</v>
@@ -11032,7 +11032,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C42">
         <v>190.67131999999998</v>
@@ -11043,7 +11043,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C43">
         <v>-708.32499999999993</v>
@@ -11065,7 +11065,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C45">
         <v>-357.58199999999999</v>
@@ -11076,7 +11076,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C46">
         <v>-845.10500000000002</v>
@@ -11087,7 +11087,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C47">
         <v>-83.045000000000002</v>
@@ -11098,7 +11098,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C48">
         <v>-661.42899999999997</v>
@@ -11109,7 +11109,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C49">
         <v>-31.263999999999999</v>
@@ -11120,7 +11120,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C50">
         <v>-10.498540930309094</v>
@@ -11131,7 +11131,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C51">
         <v>-20.327868125092017</v>
@@ -11153,7 +11153,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C53">
         <v>-29.166899245671924</v>
@@ -11164,7 +11164,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C54">
         <v>-6.6570737613344075</v>
@@ -11175,7 +11175,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C55">
         <v>-211.03200000000001</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C56">
         <v>-83.045000000000002</v>
@@ -11197,7 +11197,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C57">
         <v>-27.339084185091842</v>
@@ -11208,7 +11208,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C58">
         <v>-99.653999999999982</v>
@@ -11219,7 +11219,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C59">
         <v>-34.696428008002286</v>
@@ -11230,7 +11230,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C60">
         <v>-19.54</v>
@@ -11241,7 +11241,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61">
         <v>-34.820653312201756</v>
@@ -11252,7 +11252,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C62">
         <v>-55.689</v>
@@ -11263,7 +11263,7 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>-110.401</v>
@@ -11274,7 +11274,7 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C64">
         <v>-13.995883970311864</v>
@@ -11285,7 +11285,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C65">
         <v>-9.5558311621502252</v>
@@ -11296,7 +11296,7 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C66">
         <v>-316.54799999999994</v>
@@ -11307,7 +11307,7 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C67">
         <v>-58.62</v>
@@ -11318,7 +11318,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C68">
         <v>-286.26099999999997</v>
@@ -11329,7 +11329,7 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C69">
         <v>-12.918429819775348</v>
@@ -11340,7 +11340,7 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -11351,7 +11351,7 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -11362,7 +11362,7 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C72">
         <v>-453.32799999999997</v>
@@ -11373,7 +11373,7 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C73">
         <v>-42.988</v>
@@ -11384,7 +11384,7 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -11395,7 +11395,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -11406,7 +11406,7 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -11417,7 +11417,7 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -11428,7 +11428,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C79">
         <v>-10.747</v>
@@ -11450,7 +11450,7 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C80">
         <v>-3.1361880225518983</v>
@@ -11461,7 +11461,7 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C81">
         <v>-24.864095362311311</v>
@@ -11472,7 +11472,7 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C82">
         <v>-10.40036286731274</v>
@@ -11505,7 +11505,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -11549,7 +11549,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -11560,7 +11560,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11571,7 +11571,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11582,7 +11582,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -11593,7 +11593,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11604,7 +11604,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11615,7 +11615,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -11626,7 +11626,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -11637,7 +11637,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -11670,7 +11670,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -11681,7 +11681,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -11692,7 +11692,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -11703,7 +11703,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -11714,7 +11714,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -11725,7 +11725,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -11736,7 +11736,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -11747,7 +11747,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -11758,7 +11758,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -11780,7 +11780,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -11791,7 +11791,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -11802,7 +11802,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11813,7 +11813,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -11835,7 +11835,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11846,7 +11846,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11868,7 +11868,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11879,7 +11879,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11890,7 +11890,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11901,7 +11901,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11923,7 +11923,7 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11934,7 +11934,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11945,7 +11945,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -11956,7 +11956,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -11967,7 +11967,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -11978,7 +11978,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -11989,7 +11989,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -12000,7 +12000,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -12011,7 +12011,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -12022,7 +12022,7 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -12033,7 +12033,7 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12044,7 +12044,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12055,7 +12055,7 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -12066,7 +12066,7 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12077,7 +12077,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12088,7 +12088,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12099,7 +12099,7 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12110,7 +12110,7 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -12121,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12132,7 +12132,7 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12154,7 +12154,7 @@
         <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C144">
         <v>-5</v>
@@ -12165,7 +12165,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12176,7 +12176,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12187,7 +12187,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12198,7 +12198,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12209,7 +12209,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12231,7 +12231,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12242,7 +12242,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12264,7 +12264,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12275,7 +12275,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12286,7 +12286,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12297,7 +12297,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12308,7 +12308,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12319,7 +12319,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12330,7 +12330,7 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12341,7 +12341,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -12352,7 +12352,7 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -12396,7 +12396,7 @@
         <v>11</v>
       </c>
       <c r="B166" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -12407,7 +12407,7 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -12418,7 +12418,7 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -12429,7 +12429,7 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -12440,7 +12440,7 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C170">
         <v>0</v>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7CE7E8-146D-4101-B7C4-1C8222EA1E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F9548E-9359-4B54-9505-316583751CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -1151,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B148"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2288,6 +2288,54 @@
       </c>
       <c r="B142" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>69</v>
+      </c>
+      <c r="B143" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>56</v>
+      </c>
+      <c r="B144" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>73</v>
+      </c>
+      <c r="B145" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>66</v>
+      </c>
+      <c r="B146" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>71</v>
+      </c>
+      <c r="B147" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>94</v>
+      </c>
+      <c r="B148" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F9548E-9359-4B54-9505-316583751CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A6B20C-BACF-4324-B31E-9F596ECC2FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-4590" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B146" t="s">
         <v>61</v>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A6B20C-BACF-4324-B31E-9F596ECC2FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C173888F-F51F-4B80-A114-3EF0BCFD2697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4590" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -1151,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B149"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2336,6 +2336,14 @@
       </c>
       <c r="B148" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>51</v>
+      </c>
+      <c r="B149" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C173888F-F51F-4B80-A114-3EF0BCFD2697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89C1AB0-EB9C-4A68-81BA-2451B45FE05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4590" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-4590" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="134">
   <si>
     <t>Commodities</t>
   </si>
@@ -334,6 +334,114 @@
   </si>
   <si>
     <t>EL_Prod</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>USA_Prod</t>
+  </si>
+  <si>
+    <t>USA_LNG</t>
+  </si>
+  <si>
+    <t>NA_prod</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NA_LNG</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>SA_Prod</t>
+  </si>
+  <si>
+    <t>SA_LNG</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>TT_Prod</t>
+  </si>
+  <si>
+    <t>TT_LNG</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>ME_Prod</t>
+  </si>
+  <si>
+    <t>ME_LNG</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QA_Prod</t>
+  </si>
+  <si>
+    <t>QA_LNG</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AF_Prod</t>
+  </si>
+  <si>
+    <t>AF_LNG</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>AU_Prod</t>
+  </si>
+  <si>
+    <t>AU_LNG</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>CN_Prod</t>
+  </si>
+  <si>
+    <t>CN_LNG</t>
+  </si>
+  <si>
+    <t>JS</t>
+  </si>
+  <si>
+    <t>JS_Prod</t>
+  </si>
+  <si>
+    <t>JS_LNG</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>IN_Prod</t>
+  </si>
+  <si>
+    <t>IN_LNG</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>AS_Prod</t>
+  </si>
+  <si>
+    <t>AS_LNG</t>
   </si>
 </sst>
 </file>
@@ -691,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A121"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1117,6 +1225,186 @@
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1151,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B149"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2344,6 +2632,126 @@
       </c>
       <c r="B149" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>100</v>
+      </c>
+      <c r="B150" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>99</v>
+      </c>
+      <c r="B151" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>98</v>
+      </c>
+      <c r="B152" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>100</v>
+      </c>
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>100</v>
+      </c>
+      <c r="B154" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>100</v>
+      </c>
+      <c r="B155" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>100</v>
+      </c>
+      <c r="B156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>100</v>
+      </c>
+      <c r="B157" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>100</v>
+      </c>
+      <c r="B158" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>100</v>
+      </c>
+      <c r="B159" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>100</v>
+      </c>
+      <c r="B160" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>100</v>
+      </c>
+      <c r="B161" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>100</v>
+      </c>
+      <c r="B162" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>100</v>
+      </c>
+      <c r="B163" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>100</v>
+      </c>
+      <c r="B164" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2353,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I285"/>
+  <dimension ref="A1:I329"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -10618,6 +11026,1282 @@
         <v>1000</v>
       </c>
       <c r="I285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>11</v>
+      </c>
+      <c r="B286" t="s">
+        <v>100</v>
+      </c>
+      <c r="C286" t="s">
+        <v>31</v>
+      </c>
+      <c r="D286">
+        <v>10000</v>
+      </c>
+      <c r="E286">
+        <v>10000</v>
+      </c>
+      <c r="F286">
+        <v>20</v>
+      </c>
+      <c r="G286">
+        <v>10000000</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>11</v>
+      </c>
+      <c r="B287" t="s">
+        <v>99</v>
+      </c>
+      <c r="C287" t="s">
+        <v>98</v>
+      </c>
+      <c r="D287">
+        <v>10000</v>
+      </c>
+      <c r="E287">
+        <v>10000</v>
+      </c>
+      <c r="F287">
+        <v>100</v>
+      </c>
+      <c r="G287">
+        <v>10000000</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>11</v>
+      </c>
+      <c r="B288" t="s">
+        <v>98</v>
+      </c>
+      <c r="C288" t="s">
+        <v>100</v>
+      </c>
+      <c r="D288">
+        <v>10000</v>
+      </c>
+      <c r="E288">
+        <v>10000</v>
+      </c>
+      <c r="F288">
+        <v>100</v>
+      </c>
+      <c r="G288">
+        <v>10000000</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>12</v>
+      </c>
+      <c r="B289" t="s">
+        <v>100</v>
+      </c>
+      <c r="C289" t="s">
+        <v>31</v>
+      </c>
+      <c r="D289">
+        <v>10000</v>
+      </c>
+      <c r="E289">
+        <v>10000</v>
+      </c>
+      <c r="F289">
+        <v>100</v>
+      </c>
+      <c r="G289">
+        <v>10000000</v>
+      </c>
+      <c r="H289">
+        <v>1000</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" t="s">
+        <v>99</v>
+      </c>
+      <c r="C290" t="s">
+        <v>98</v>
+      </c>
+      <c r="D290">
+        <v>10000</v>
+      </c>
+      <c r="E290">
+        <v>10000</v>
+      </c>
+      <c r="F290">
+        <v>100</v>
+      </c>
+      <c r="G290">
+        <v>10000000</v>
+      </c>
+      <c r="H290">
+        <v>1000</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>12</v>
+      </c>
+      <c r="B291" t="s">
+        <v>98</v>
+      </c>
+      <c r="C291" t="s">
+        <v>100</v>
+      </c>
+      <c r="D291">
+        <v>10000</v>
+      </c>
+      <c r="E291">
+        <v>10000</v>
+      </c>
+      <c r="F291">
+        <v>100</v>
+      </c>
+      <c r="G291">
+        <v>10000000</v>
+      </c>
+      <c r="H291">
+        <v>1000</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>11</v>
+      </c>
+      <c r="B292" t="s">
+        <v>69</v>
+      </c>
+      <c r="C292" t="s">
+        <v>56</v>
+      </c>
+      <c r="D292">
+        <v>10000</v>
+      </c>
+      <c r="E292">
+        <v>10000</v>
+      </c>
+      <c r="F292">
+        <v>100</v>
+      </c>
+      <c r="G292">
+        <v>10000000</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>11</v>
+      </c>
+      <c r="B293" t="s">
+        <v>56</v>
+      </c>
+      <c r="C293" t="s">
+        <v>69</v>
+      </c>
+      <c r="D293">
+        <v>10000</v>
+      </c>
+      <c r="E293">
+        <v>10000</v>
+      </c>
+      <c r="F293">
+        <v>100</v>
+      </c>
+      <c r="G293">
+        <v>10000000</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>11</v>
+      </c>
+      <c r="B294" t="s">
+        <v>73</v>
+      </c>
+      <c r="C294" t="s">
+        <v>56</v>
+      </c>
+      <c r="D294">
+        <v>10000</v>
+      </c>
+      <c r="E294">
+        <v>10000</v>
+      </c>
+      <c r="F294">
+        <v>100</v>
+      </c>
+      <c r="G294">
+        <v>10000000</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>11</v>
+      </c>
+      <c r="B295" t="s">
+        <v>16</v>
+      </c>
+      <c r="C295" t="s">
+        <v>61</v>
+      </c>
+      <c r="D295">
+        <v>10000</v>
+      </c>
+      <c r="E295">
+        <v>10000</v>
+      </c>
+      <c r="F295">
+        <v>100</v>
+      </c>
+      <c r="G295">
+        <v>10000000</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>11</v>
+      </c>
+      <c r="B296" t="s">
+        <v>71</v>
+      </c>
+      <c r="C296" t="s">
+        <v>94</v>
+      </c>
+      <c r="D296">
+        <v>10000</v>
+      </c>
+      <c r="E296">
+        <v>10000</v>
+      </c>
+      <c r="F296">
+        <v>100</v>
+      </c>
+      <c r="G296">
+        <v>10000000</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>11</v>
+      </c>
+      <c r="B297" t="s">
+        <v>94</v>
+      </c>
+      <c r="C297" t="s">
+        <v>71</v>
+      </c>
+      <c r="D297">
+        <v>10000</v>
+      </c>
+      <c r="E297">
+        <v>10000</v>
+      </c>
+      <c r="F297">
+        <v>100</v>
+      </c>
+      <c r="G297">
+        <v>10000000</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>11</v>
+      </c>
+      <c r="B298" t="s">
+        <v>51</v>
+      </c>
+      <c r="C298" t="s">
+        <v>34</v>
+      </c>
+      <c r="D298">
+        <v>10000</v>
+      </c>
+      <c r="E298">
+        <v>10000</v>
+      </c>
+      <c r="F298">
+        <v>100</v>
+      </c>
+      <c r="G298">
+        <v>10000000</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" t="s">
+        <v>69</v>
+      </c>
+      <c r="C299" t="s">
+        <v>56</v>
+      </c>
+      <c r="D299">
+        <v>10000</v>
+      </c>
+      <c r="E299">
+        <v>10000</v>
+      </c>
+      <c r="F299">
+        <v>100</v>
+      </c>
+      <c r="G299">
+        <v>10000000</v>
+      </c>
+      <c r="H299">
+        <v>1000</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>12</v>
+      </c>
+      <c r="B300" t="s">
+        <v>56</v>
+      </c>
+      <c r="C300" t="s">
+        <v>69</v>
+      </c>
+      <c r="D300">
+        <v>10000</v>
+      </c>
+      <c r="E300">
+        <v>10000</v>
+      </c>
+      <c r="F300">
+        <v>100</v>
+      </c>
+      <c r="G300">
+        <v>10000000</v>
+      </c>
+      <c r="H300">
+        <v>1000</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>12</v>
+      </c>
+      <c r="B301" t="s">
+        <v>73</v>
+      </c>
+      <c r="C301" t="s">
+        <v>56</v>
+      </c>
+      <c r="D301">
+        <v>10000</v>
+      </c>
+      <c r="E301">
+        <v>10000</v>
+      </c>
+      <c r="F301">
+        <v>100</v>
+      </c>
+      <c r="G301">
+        <v>10000000</v>
+      </c>
+      <c r="H301">
+        <v>1000</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>12</v>
+      </c>
+      <c r="B302" t="s">
+        <v>16</v>
+      </c>
+      <c r="C302" t="s">
+        <v>61</v>
+      </c>
+      <c r="D302">
+        <v>10000</v>
+      </c>
+      <c r="E302">
+        <v>10000</v>
+      </c>
+      <c r="F302">
+        <v>100</v>
+      </c>
+      <c r="G302">
+        <v>10000000</v>
+      </c>
+      <c r="H302">
+        <v>1000</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>12</v>
+      </c>
+      <c r="B303" t="s">
+        <v>71</v>
+      </c>
+      <c r="C303" t="s">
+        <v>94</v>
+      </c>
+      <c r="D303">
+        <v>10000</v>
+      </c>
+      <c r="E303">
+        <v>10000</v>
+      </c>
+      <c r="F303">
+        <v>100</v>
+      </c>
+      <c r="G303">
+        <v>10000000</v>
+      </c>
+      <c r="H303">
+        <v>1000</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>12</v>
+      </c>
+      <c r="B304" t="s">
+        <v>94</v>
+      </c>
+      <c r="C304" t="s">
+        <v>71</v>
+      </c>
+      <c r="D304">
+        <v>10000</v>
+      </c>
+      <c r="E304">
+        <v>10000</v>
+      </c>
+      <c r="F304">
+        <v>100</v>
+      </c>
+      <c r="G304">
+        <v>10000000</v>
+      </c>
+      <c r="H304">
+        <v>1000</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>12</v>
+      </c>
+      <c r="B305" t="s">
+        <v>51</v>
+      </c>
+      <c r="C305" t="s">
+        <v>34</v>
+      </c>
+      <c r="D305">
+        <v>10000</v>
+      </c>
+      <c r="E305">
+        <v>10000</v>
+      </c>
+      <c r="F305">
+        <v>100</v>
+      </c>
+      <c r="G305">
+        <v>10000000</v>
+      </c>
+      <c r="H305">
+        <v>1000</v>
+      </c>
+      <c r="I305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>11</v>
+      </c>
+      <c r="B306" t="s">
+        <v>100</v>
+      </c>
+      <c r="C306" t="s">
+        <v>15</v>
+      </c>
+      <c r="D306">
+        <v>10000</v>
+      </c>
+      <c r="E306">
+        <v>10000</v>
+      </c>
+      <c r="F306">
+        <v>20</v>
+      </c>
+      <c r="G306">
+        <v>10000000</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>11</v>
+      </c>
+      <c r="B307" t="s">
+        <v>100</v>
+      </c>
+      <c r="C307" t="s">
+        <v>17</v>
+      </c>
+      <c r="D307">
+        <v>10000</v>
+      </c>
+      <c r="E307">
+        <v>10000</v>
+      </c>
+      <c r="F307">
+        <v>20</v>
+      </c>
+      <c r="G307">
+        <v>10000000</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>11</v>
+      </c>
+      <c r="B308" t="s">
+        <v>100</v>
+      </c>
+      <c r="C308" t="s">
+        <v>95</v>
+      </c>
+      <c r="D308">
+        <v>10000</v>
+      </c>
+      <c r="E308">
+        <v>10000</v>
+      </c>
+      <c r="F308">
+        <v>20</v>
+      </c>
+      <c r="G308">
+        <v>10000000</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>11</v>
+      </c>
+      <c r="B309" t="s">
+        <v>100</v>
+      </c>
+      <c r="C309" t="s">
+        <v>19</v>
+      </c>
+      <c r="D309">
+        <v>10000</v>
+      </c>
+      <c r="E309">
+        <v>10000</v>
+      </c>
+      <c r="F309">
+        <v>20</v>
+      </c>
+      <c r="G309">
+        <v>10000000</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>11</v>
+      </c>
+      <c r="B310" t="s">
+        <v>100</v>
+      </c>
+      <c r="C310" t="s">
+        <v>21</v>
+      </c>
+      <c r="D310">
+        <v>10000</v>
+      </c>
+      <c r="E310">
+        <v>10000</v>
+      </c>
+      <c r="F310">
+        <v>20</v>
+      </c>
+      <c r="G310">
+        <v>10000000</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>11</v>
+      </c>
+      <c r="B311" t="s">
+        <v>100</v>
+      </c>
+      <c r="C311" t="s">
+        <v>23</v>
+      </c>
+      <c r="D311">
+        <v>10000</v>
+      </c>
+      <c r="E311">
+        <v>10000</v>
+      </c>
+      <c r="F311">
+        <v>20</v>
+      </c>
+      <c r="G311">
+        <v>10000000</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>11</v>
+      </c>
+      <c r="B312" t="s">
+        <v>100</v>
+      </c>
+      <c r="C312" t="s">
+        <v>25</v>
+      </c>
+      <c r="D312">
+        <v>10000</v>
+      </c>
+      <c r="E312">
+        <v>10000</v>
+      </c>
+      <c r="F312">
+        <v>20</v>
+      </c>
+      <c r="G312">
+        <v>10000000</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>11</v>
+      </c>
+      <c r="B313" t="s">
+        <v>100</v>
+      </c>
+      <c r="C313" t="s">
+        <v>27</v>
+      </c>
+      <c r="D313">
+        <v>10000</v>
+      </c>
+      <c r="E313">
+        <v>10000</v>
+      </c>
+      <c r="F313">
+        <v>20</v>
+      </c>
+      <c r="G313">
+        <v>10000000</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>11</v>
+      </c>
+      <c r="B314" t="s">
+        <v>100</v>
+      </c>
+      <c r="C314" t="s">
+        <v>29</v>
+      </c>
+      <c r="D314">
+        <v>10000</v>
+      </c>
+      <c r="E314">
+        <v>10000</v>
+      </c>
+      <c r="F314">
+        <v>20</v>
+      </c>
+      <c r="G314">
+        <v>10000000</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>11</v>
+      </c>
+      <c r="B315" t="s">
+        <v>100</v>
+      </c>
+      <c r="C315" t="s">
+        <v>31</v>
+      </c>
+      <c r="D315">
+        <v>10000</v>
+      </c>
+      <c r="E315">
+        <v>10000</v>
+      </c>
+      <c r="F315">
+        <v>20</v>
+      </c>
+      <c r="G315">
+        <v>10000000</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>11</v>
+      </c>
+      <c r="B316" t="s">
+        <v>100</v>
+      </c>
+      <c r="C316" t="s">
+        <v>33</v>
+      </c>
+      <c r="D316">
+        <v>10000</v>
+      </c>
+      <c r="E316">
+        <v>10000</v>
+      </c>
+      <c r="F316">
+        <v>20</v>
+      </c>
+      <c r="G316">
+        <v>10000000</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>11</v>
+      </c>
+      <c r="B317" t="s">
+        <v>100</v>
+      </c>
+      <c r="C317" t="s">
+        <v>35</v>
+      </c>
+      <c r="D317">
+        <v>10000</v>
+      </c>
+      <c r="E317">
+        <v>10000</v>
+      </c>
+      <c r="F317">
+        <v>20</v>
+      </c>
+      <c r="G317">
+        <v>10000000</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>12</v>
+      </c>
+      <c r="B318" t="s">
+        <v>100</v>
+      </c>
+      <c r="C318" t="s">
+        <v>15</v>
+      </c>
+      <c r="D318">
+        <v>10000</v>
+      </c>
+      <c r="E318">
+        <v>10000</v>
+      </c>
+      <c r="F318">
+        <v>100</v>
+      </c>
+      <c r="G318">
+        <v>10000000</v>
+      </c>
+      <c r="H318">
+        <v>1000</v>
+      </c>
+      <c r="I318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>12</v>
+      </c>
+      <c r="B319" t="s">
+        <v>100</v>
+      </c>
+      <c r="C319" t="s">
+        <v>17</v>
+      </c>
+      <c r="D319">
+        <v>10000</v>
+      </c>
+      <c r="E319">
+        <v>10000</v>
+      </c>
+      <c r="F319">
+        <v>100</v>
+      </c>
+      <c r="G319">
+        <v>10000000</v>
+      </c>
+      <c r="H319">
+        <v>1000</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>12</v>
+      </c>
+      <c r="B320" t="s">
+        <v>100</v>
+      </c>
+      <c r="C320" t="s">
+        <v>95</v>
+      </c>
+      <c r="D320">
+        <v>10000</v>
+      </c>
+      <c r="E320">
+        <v>10000</v>
+      </c>
+      <c r="F320">
+        <v>100</v>
+      </c>
+      <c r="G320">
+        <v>10000000</v>
+      </c>
+      <c r="H320">
+        <v>1000</v>
+      </c>
+      <c r="I320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>12</v>
+      </c>
+      <c r="B321" t="s">
+        <v>100</v>
+      </c>
+      <c r="C321" t="s">
+        <v>19</v>
+      </c>
+      <c r="D321">
+        <v>10000</v>
+      </c>
+      <c r="E321">
+        <v>10000</v>
+      </c>
+      <c r="F321">
+        <v>100</v>
+      </c>
+      <c r="G321">
+        <v>10000000</v>
+      </c>
+      <c r="H321">
+        <v>1000</v>
+      </c>
+      <c r="I321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>12</v>
+      </c>
+      <c r="B322" t="s">
+        <v>100</v>
+      </c>
+      <c r="C322" t="s">
+        <v>21</v>
+      </c>
+      <c r="D322">
+        <v>10000</v>
+      </c>
+      <c r="E322">
+        <v>10000</v>
+      </c>
+      <c r="F322">
+        <v>100</v>
+      </c>
+      <c r="G322">
+        <v>10000000</v>
+      </c>
+      <c r="H322">
+        <v>1000</v>
+      </c>
+      <c r="I322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>12</v>
+      </c>
+      <c r="B323" t="s">
+        <v>100</v>
+      </c>
+      <c r="C323" t="s">
+        <v>23</v>
+      </c>
+      <c r="D323">
+        <v>10000</v>
+      </c>
+      <c r="E323">
+        <v>10000</v>
+      </c>
+      <c r="F323">
+        <v>100</v>
+      </c>
+      <c r="G323">
+        <v>10000000</v>
+      </c>
+      <c r="H323">
+        <v>1000</v>
+      </c>
+      <c r="I323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>12</v>
+      </c>
+      <c r="B324" t="s">
+        <v>100</v>
+      </c>
+      <c r="C324" t="s">
+        <v>25</v>
+      </c>
+      <c r="D324">
+        <v>10000</v>
+      </c>
+      <c r="E324">
+        <v>10000</v>
+      </c>
+      <c r="F324">
+        <v>100</v>
+      </c>
+      <c r="G324">
+        <v>10000000</v>
+      </c>
+      <c r="H324">
+        <v>1000</v>
+      </c>
+      <c r="I324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>12</v>
+      </c>
+      <c r="B325" t="s">
+        <v>100</v>
+      </c>
+      <c r="C325" t="s">
+        <v>27</v>
+      </c>
+      <c r="D325">
+        <v>10000</v>
+      </c>
+      <c r="E325">
+        <v>10000</v>
+      </c>
+      <c r="F325">
+        <v>100</v>
+      </c>
+      <c r="G325">
+        <v>10000000</v>
+      </c>
+      <c r="H325">
+        <v>1000</v>
+      </c>
+      <c r="I325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>12</v>
+      </c>
+      <c r="B326" t="s">
+        <v>100</v>
+      </c>
+      <c r="C326" t="s">
+        <v>29</v>
+      </c>
+      <c r="D326">
+        <v>10000</v>
+      </c>
+      <c r="E326">
+        <v>10000</v>
+      </c>
+      <c r="F326">
+        <v>100</v>
+      </c>
+      <c r="G326">
+        <v>10000000</v>
+      </c>
+      <c r="H326">
+        <v>1000</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>12</v>
+      </c>
+      <c r="B327" t="s">
+        <v>100</v>
+      </c>
+      <c r="C327" t="s">
+        <v>31</v>
+      </c>
+      <c r="D327">
+        <v>10000</v>
+      </c>
+      <c r="E327">
+        <v>10000</v>
+      </c>
+      <c r="F327">
+        <v>100</v>
+      </c>
+      <c r="G327">
+        <v>10000000</v>
+      </c>
+      <c r="H327">
+        <v>1000</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>12</v>
+      </c>
+      <c r="B328" t="s">
+        <v>100</v>
+      </c>
+      <c r="C328" t="s">
+        <v>33</v>
+      </c>
+      <c r="D328">
+        <v>10000</v>
+      </c>
+      <c r="E328">
+        <v>10000</v>
+      </c>
+      <c r="F328">
+        <v>100</v>
+      </c>
+      <c r="G328">
+        <v>10000000</v>
+      </c>
+      <c r="H328">
+        <v>1000</v>
+      </c>
+      <c r="I328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>12</v>
+      </c>
+      <c r="B329" t="s">
+        <v>100</v>
+      </c>
+      <c r="C329" t="s">
+        <v>35</v>
+      </c>
+      <c r="D329">
+        <v>10000</v>
+      </c>
+      <c r="E329">
+        <v>10000</v>
+      </c>
+      <c r="F329">
+        <v>100</v>
+      </c>
+      <c r="G329">
+        <v>10000000</v>
+      </c>
+      <c r="H329">
+        <v>1000</v>
+      </c>
+      <c r="I329">
         <v>1</v>
       </c>
     </row>
@@ -10629,7 +12313,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C170"/>
+  <dimension ref="A1:C242"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -10651,7 +12335,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>111.378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -10662,7 +12346,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>322.40999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -10673,7 +12357,7 @@
         <v>95</v>
       </c>
       <c r="C4">
-        <v>73.274999999999991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -10684,7 +12368,7 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>155.83149999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -10695,7 +12379,7 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>25.402000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -10706,7 +12390,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>39.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -10717,7 +12401,7 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>122.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -10728,7 +12412,7 @@
         <v>27</v>
       </c>
       <c r="C9">
-        <v>60.573999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -10739,7 +12423,7 @@
         <v>29</v>
       </c>
       <c r="C10">
-        <v>74.251999999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -10750,7 +12434,7 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>655.56699999999989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -10761,7 +12445,7 @@
         <v>33</v>
       </c>
       <c r="C12">
-        <v>425.97199999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -10772,7 +12456,7 @@
         <v>35</v>
       </c>
       <c r="C13">
-        <v>510.97099999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -12499,6 +14183,699 @@
         <v>68</v>
       </c>
       <c r="C170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" t="s">
+        <v>99</v>
+      </c>
+      <c r="C171">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" t="s">
+        <v>98</v>
+      </c>
+      <c r="C172">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" t="s">
+        <v>100</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>12</v>
+      </c>
+      <c r="B174" t="s">
+        <v>99</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>12</v>
+      </c>
+      <c r="B175" t="s">
+        <v>98</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>12</v>
+      </c>
+      <c r="B176" t="s">
+        <v>100</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>11</v>
+      </c>
+      <c r="B178" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>11</v>
+      </c>
+      <c r="B184" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>11</v>
+      </c>
+      <c r="B186" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>11</v>
+      </c>
+      <c r="B188" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>11</v>
+      </c>
+      <c r="B193" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>11</v>
+      </c>
+      <c r="B194" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>11</v>
+      </c>
+      <c r="B197" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>11</v>
+      </c>
+      <c r="B199" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>11</v>
+      </c>
+      <c r="B200" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>11</v>
+      </c>
+      <c r="B201" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>11</v>
+      </c>
+      <c r="B202" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>11</v>
+      </c>
+      <c r="B203" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>11</v>
+      </c>
+      <c r="B204" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>11</v>
+      </c>
+      <c r="B205" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>11</v>
+      </c>
+      <c r="B206" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>11</v>
+      </c>
+      <c r="B207" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>11</v>
+      </c>
+      <c r="B208" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>11</v>
+      </c>
+      <c r="B209" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>12</v>
+      </c>
+      <c r="B210" t="s">
+        <v>102</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>12</v>
+      </c>
+      <c r="B211" t="s">
+        <v>101</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>12</v>
+      </c>
+      <c r="B212" t="s">
+        <v>103</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>12</v>
+      </c>
+      <c r="B213" t="s">
+        <v>104</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>12</v>
+      </c>
+      <c r="B214" t="s">
+        <v>105</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>12</v>
+      </c>
+      <c r="B215" t="s">
+        <v>106</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216" t="s">
+        <v>107</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B217" t="s">
+        <v>108</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218" t="s">
+        <v>109</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>12</v>
+      </c>
+      <c r="B219" t="s">
+        <v>110</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>12</v>
+      </c>
+      <c r="B220" t="s">
+        <v>111</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>12</v>
+      </c>
+      <c r="B221" t="s">
+        <v>112</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222" t="s">
+        <v>113</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>12</v>
+      </c>
+      <c r="B223" t="s">
+        <v>114</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224" t="s">
+        <v>115</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225" t="s">
+        <v>116</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226" t="s">
+        <v>117</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" t="s">
+        <v>118</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" t="s">
+        <v>119</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>12</v>
+      </c>
+      <c r="B229" t="s">
+        <v>120</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>12</v>
+      </c>
+      <c r="B230" t="s">
+        <v>121</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>12</v>
+      </c>
+      <c r="B231" t="s">
+        <v>122</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>12</v>
+      </c>
+      <c r="B232" t="s">
+        <v>123</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>12</v>
+      </c>
+      <c r="B233" t="s">
+        <v>124</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>12</v>
+      </c>
+      <c r="B234" t="s">
+        <v>125</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>12</v>
+      </c>
+      <c r="B235" t="s">
+        <v>126</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>127</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>12</v>
+      </c>
+      <c r="B237" t="s">
+        <v>128</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>12</v>
+      </c>
+      <c r="B238" t="s">
+        <v>129</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>12</v>
+      </c>
+      <c r="B239" t="s">
+        <v>130</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B240" t="s">
+        <v>131</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B241" t="s">
+        <v>132</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242" t="s">
+        <v>133</v>
+      </c>
+      <c r="C242">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89C1AB0-EB9C-4A68-81BA-2451B45FE05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F583D3E9-C160-4143-9F6A-2FB17FE50570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4590" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -264,9 +264,6 @@
     <t>BY</t>
   </si>
   <si>
-    <t>AZ</t>
-  </si>
-  <si>
     <t>MA</t>
   </si>
   <si>
@@ -442,6 +439,9 @@
   </si>
   <si>
     <t>AS_LNG</t>
+  </si>
+  <si>
+    <t>CR</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
@@ -869,7 +869,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
@@ -989,7 +989,7 @@
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
@@ -1084,7 +1084,7 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
@@ -1114,92 +1114,92 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
@@ -1229,182 +1229,182 @@
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
         <v>95</v>
-      </c>
-      <c r="B4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -2063,7 +2063,7 @@
         <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -2092,7 +2092,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B82" t="s">
         <v>66</v>
@@ -2271,12 +2271,12 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B105" t="s">
         <v>32</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B111" t="s">
         <v>34</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B113" t="s">
         <v>32</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B120" t="s">
         <v>72</v>
@@ -2404,15 +2404,15 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B122" t="s">
         <v>53</v>
@@ -2423,7 +2423,7 @@
         <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -2436,7 +2436,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B125" t="s">
         <v>70</v>
@@ -2447,12 +2447,12 @@
         <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B127" t="s">
         <v>72</v>
@@ -2460,15 +2460,15 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>78</v>
+      </c>
+      <c r="B128" t="s">
         <v>79</v>
-      </c>
-      <c r="B128" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B129" t="s">
         <v>58</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B131" t="s">
         <v>66</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B132" t="s">
         <v>22</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B133" t="s">
         <v>60</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s">
         <v>18</v>
@@ -2516,15 +2516,15 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B135" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B136" t="s">
         <v>64</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B137" t="s">
         <v>57</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B138" t="s">
         <v>65</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B139" t="s">
         <v>63</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B140" t="s">
         <v>62</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B141" t="s">
         <v>34</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B142" t="s">
         <v>32</v>
@@ -2615,12 +2615,12 @@
         <v>71</v>
       </c>
       <c r="B147" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B148" t="s">
         <v>71</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B150" t="s">
         <v>31</v>
@@ -2644,23 +2644,23 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B151" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B152" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B154" t="s">
         <v>17</v>
@@ -2676,15 +2676,15 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B155" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B156" t="s">
         <v>19</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B157" t="s">
         <v>21</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B158" t="s">
         <v>23</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B159" t="s">
         <v>25</v>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B160" t="s">
         <v>27</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B161" t="s">
         <v>29</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B162" t="s">
         <v>31</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B163" t="s">
         <v>33</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B164" t="s">
         <v>35</v>
@@ -2856,10 +2856,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
-      </c>
-      <c r="C4" t="s">
-        <v>96</v>
       </c>
       <c r="D4">
         <v>73.274999999999991</v>
@@ -3146,7 +3146,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
         <v>72</v>
@@ -3175,10 +3175,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s">
         <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
       </c>
       <c r="D15">
         <v>10000</v>
@@ -3204,7 +3204,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -3233,7 +3233,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -3262,7 +3262,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
         <v>66</v>
@@ -3291,7 +3291,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -3320,7 +3320,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
         <v>60</v>
@@ -3349,7 +3349,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -3378,10 +3378,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22">
         <v>10000</v>
@@ -3407,7 +3407,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
         <v>64</v>
@@ -3436,7 +3436,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
         <v>57</v>
@@ -3465,7 +3465,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
@@ -3494,7 +3494,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
         <v>63</v>
@@ -3523,7 +3523,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
         <v>62</v>
@@ -3552,7 +3552,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
         <v>34</v>
@@ -3581,7 +3581,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -3610,10 +3610,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -5469,7 +5469,7 @@
         <v>66</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D94">
         <v>42.997</v>
@@ -5553,7 +5553,7 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C97" t="s">
         <v>66</v>
@@ -6194,7 +6194,7 @@
         <v>34</v>
       </c>
       <c r="C119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119">
         <v>145.489</v>
@@ -6220,7 +6220,7 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C120" t="s">
         <v>32</v>
@@ -6365,7 +6365,7 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="C125" t="s">
         <v>34</v>
@@ -6510,7 +6510,7 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C130" t="s">
         <v>32</v>
@@ -6713,7 +6713,7 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C137" t="s">
         <v>72</v>
@@ -6745,7 +6745,7 @@
         <v>34</v>
       </c>
       <c r="C138" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D138">
         <v>144.17500000000001</v>
@@ -6771,10 +6771,10 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C139" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D139">
         <v>123.04150000000001</v>
@@ -6800,7 +6800,7 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C140" t="s">
         <v>53</v>
@@ -6832,7 +6832,7 @@
         <v>38</v>
       </c>
       <c r="C141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D141">
         <v>14.965</v>
@@ -6858,7 +6858,7 @@
         <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C142" t="s">
         <v>70</v>
@@ -6890,7 +6890,7 @@
         <v>70</v>
       </c>
       <c r="C143" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D143">
         <v>24.424999999999997</v>
@@ -6974,10 +6974,10 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
+        <v>94</v>
+      </c>
+      <c r="C146" t="s">
         <v>95</v>
-      </c>
-      <c r="C146" t="s">
-        <v>96</v>
       </c>
       <c r="D146">
         <v>10000</v>
@@ -7264,10 +7264,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C156" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -9123,7 +9123,7 @@
         <v>66</v>
       </c>
       <c r="C220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -9236,7 +9236,7 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C224" t="s">
         <v>66</v>
@@ -9877,7 +9877,7 @@
         <v>34</v>
       </c>
       <c r="C246" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9903,7 +9903,7 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C247" t="s">
         <v>32</v>
@@ -10077,7 +10077,7 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="C253" t="s">
         <v>34</v>
@@ -10135,7 +10135,7 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C255" t="s">
         <v>32</v>
@@ -10338,7 +10338,7 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C262" t="s">
         <v>72</v>
@@ -10367,10 +10367,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C263" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -10396,7 +10396,7 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C264" t="s">
         <v>53</v>
@@ -10428,7 +10428,7 @@
         <v>38</v>
       </c>
       <c r="C265" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -10454,7 +10454,7 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C266" t="s">
         <v>72</v>
@@ -10483,10 +10483,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
+        <v>78</v>
+      </c>
+      <c r="C267" t="s">
         <v>79</v>
-      </c>
-      <c r="C267" t="s">
-        <v>80</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10512,7 +10512,7 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C268" t="s">
         <v>58</v>
@@ -10541,7 +10541,7 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C269" t="s">
         <v>16</v>
@@ -10570,7 +10570,7 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C270" t="s">
         <v>66</v>
@@ -10599,7 +10599,7 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C271" t="s">
         <v>22</v>
@@ -10628,7 +10628,7 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C272" t="s">
         <v>60</v>
@@ -10657,7 +10657,7 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C273" t="s">
         <v>18</v>
@@ -10686,10 +10686,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C274" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10715,7 +10715,7 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C275" t="s">
         <v>64</v>
@@ -10744,7 +10744,7 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C276" t="s">
         <v>57</v>
@@ -10773,7 +10773,7 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C277" t="s">
         <v>65</v>
@@ -10802,7 +10802,7 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C278" t="s">
         <v>63</v>
@@ -10831,7 +10831,7 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C279" t="s">
         <v>62</v>
@@ -10860,7 +10860,7 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C280" t="s">
         <v>34</v>
@@ -10889,7 +10889,7 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C281" t="s">
         <v>32</v>
@@ -10976,7 +10976,7 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C284" t="s">
         <v>70</v>
@@ -11008,7 +11008,7 @@
         <v>70</v>
       </c>
       <c r="C285" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D285">
         <v>10000</v>
@@ -11034,7 +11034,7 @@
         <v>11</v>
       </c>
       <c r="B286" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C286" t="s">
         <v>31</v>
@@ -11063,10 +11063,10 @@
         <v>11</v>
       </c>
       <c r="B287" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C287" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D287">
         <v>10000</v>
@@ -11092,10 +11092,10 @@
         <v>11</v>
       </c>
       <c r="B288" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C288" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D288">
         <v>10000</v>
@@ -11121,7 +11121,7 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C289" t="s">
         <v>31</v>
@@ -11150,10 +11150,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C290" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D290">
         <v>10000</v>
@@ -11179,10 +11179,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C291" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D291">
         <v>10000</v>
@@ -11327,7 +11327,7 @@
         <v>71</v>
       </c>
       <c r="C296" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D296">
         <v>10000</v>
@@ -11353,7 +11353,7 @@
         <v>11</v>
       </c>
       <c r="B297" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C297" t="s">
         <v>71</v>
@@ -11530,7 +11530,7 @@
         <v>71</v>
       </c>
       <c r="C303" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D303">
         <v>10000</v>
@@ -11556,7 +11556,7 @@
         <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C304" t="s">
         <v>71</v>
@@ -11614,7 +11614,7 @@
         <v>11</v>
       </c>
       <c r="B306" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C306" t="s">
         <v>15</v>
@@ -11643,7 +11643,7 @@
         <v>11</v>
       </c>
       <c r="B307" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C307" t="s">
         <v>17</v>
@@ -11672,10 +11672,10 @@
         <v>11</v>
       </c>
       <c r="B308" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C308" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D308">
         <v>10000</v>
@@ -11701,7 +11701,7 @@
         <v>11</v>
       </c>
       <c r="B309" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C309" t="s">
         <v>19</v>
@@ -11730,7 +11730,7 @@
         <v>11</v>
       </c>
       <c r="B310" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C310" t="s">
         <v>21</v>
@@ -11759,7 +11759,7 @@
         <v>11</v>
       </c>
       <c r="B311" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C311" t="s">
         <v>23</v>
@@ -11788,7 +11788,7 @@
         <v>11</v>
       </c>
       <c r="B312" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C312" t="s">
         <v>25</v>
@@ -11817,7 +11817,7 @@
         <v>11</v>
       </c>
       <c r="B313" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C313" t="s">
         <v>27</v>
@@ -11846,7 +11846,7 @@
         <v>11</v>
       </c>
       <c r="B314" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C314" t="s">
         <v>29</v>
@@ -11875,7 +11875,7 @@
         <v>11</v>
       </c>
       <c r="B315" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C315" t="s">
         <v>31</v>
@@ -11904,7 +11904,7 @@
         <v>11</v>
       </c>
       <c r="B316" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -11933,7 +11933,7 @@
         <v>11</v>
       </c>
       <c r="B317" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C317" t="s">
         <v>35</v>
@@ -11962,7 +11962,7 @@
         <v>12</v>
       </c>
       <c r="B318" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C318" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="B319" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C319" t="s">
         <v>17</v>
@@ -12020,10 +12020,10 @@
         <v>12</v>
       </c>
       <c r="B320" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C320" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D320">
         <v>10000</v>
@@ -12049,7 +12049,7 @@
         <v>12</v>
       </c>
       <c r="B321" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C321" t="s">
         <v>19</v>
@@ -12078,7 +12078,7 @@
         <v>12</v>
       </c>
       <c r="B322" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C322" t="s">
         <v>21</v>
@@ -12107,7 +12107,7 @@
         <v>12</v>
       </c>
       <c r="B323" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C323" t="s">
         <v>23</v>
@@ -12136,7 +12136,7 @@
         <v>12</v>
       </c>
       <c r="B324" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C324" t="s">
         <v>25</v>
@@ -12165,7 +12165,7 @@
         <v>12</v>
       </c>
       <c r="B325" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C325" t="s">
         <v>27</v>
@@ -12194,7 +12194,7 @@
         <v>12</v>
       </c>
       <c r="B326" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C326" t="s">
         <v>29</v>
@@ -12223,7 +12223,7 @@
         <v>12</v>
       </c>
       <c r="B327" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C327" t="s">
         <v>31</v>
@@ -12252,7 +12252,7 @@
         <v>12</v>
       </c>
       <c r="B328" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C328" t="s">
         <v>33</v>
@@ -12281,7 +12281,7 @@
         <v>12</v>
       </c>
       <c r="B329" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C329" t="s">
         <v>35</v>
@@ -12354,7 +12354,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -12464,7 +12464,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -12475,7 +12475,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>0.55586415</v>
@@ -12486,7 +12486,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>796.255</v>
@@ -12497,7 +12497,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17">
         <v>7.5617455199999997</v>
@@ -12508,7 +12508,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18">
         <v>5.7643000000000007E-2</v>
@@ -12519,7 +12519,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19">
         <v>0.53100926999999998</v>
@@ -12530,7 +12530,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>8.6795214499999993</v>
@@ -12541,7 +12541,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21">
         <v>1.9156527500000002</v>
@@ -12552,7 +12552,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <v>0.16949973000000002</v>
@@ -12563,7 +12563,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C23">
         <v>6.3309600000000021E-2</v>
@@ -12574,7 +12574,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <v>16.46245</v>
@@ -12585,7 +12585,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>19.829690269999997</v>
@@ -12596,7 +12596,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>3.9959299999999995</v>
@@ -12607,7 +12607,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27">
         <v>0.6516687699999999</v>
@@ -12618,7 +12618,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <v>5.2113180000000002E-2</v>
@@ -12629,7 +12629,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C29">
         <v>4.2744726999999996</v>
@@ -12640,7 +12640,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C30">
         <v>0.44941999999999999</v>
@@ -12904,7 +12904,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54">
         <v>-6.6570737613344075</v>
@@ -12992,7 +12992,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C62">
         <v>-55.689</v>
@@ -13124,7 +13124,7 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -13168,7 +13168,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -13179,7 +13179,7 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C79">
         <v>-10.747</v>
@@ -13245,7 +13245,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -13619,7 +13619,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -13696,7 +13696,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -13828,7 +13828,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -13872,7 +13872,7 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -13927,7 +13927,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -13949,7 +13949,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -13960,7 +13960,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -13971,7 +13971,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -13982,7 +13982,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -13993,7 +13993,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -14004,7 +14004,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -14015,7 +14015,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -14026,7 +14026,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -14037,7 +14037,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -14048,7 +14048,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -14059,7 +14059,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -14070,7 +14070,7 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -14081,7 +14081,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -14103,7 +14103,7 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -14114,7 +14114,7 @@
         <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -14125,7 +14125,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>11</v>
       </c>
       <c r="B171" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C171">
         <v>6000</v>
@@ -14202,7 +14202,7 @@
         <v>11</v>
       </c>
       <c r="B172" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C172">
         <v>-1000</v>
@@ -14213,7 +14213,7 @@
         <v>11</v>
       </c>
       <c r="B173" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -14224,7 +14224,7 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -14235,7 +14235,7 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -14257,7 +14257,7 @@
         <v>11</v>
       </c>
       <c r="B177" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -14265,7 +14265,7 @@
         <v>11</v>
       </c>
       <c r="B178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -14273,7 +14273,7 @@
         <v>11</v>
       </c>
       <c r="B179" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -14281,7 +14281,7 @@
         <v>11</v>
       </c>
       <c r="B180" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -14289,7 +14289,7 @@
         <v>11</v>
       </c>
       <c r="B181" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -14297,7 +14297,7 @@
         <v>11</v>
       </c>
       <c r="B182" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -14305,7 +14305,7 @@
         <v>11</v>
       </c>
       <c r="B183" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -14313,7 +14313,7 @@
         <v>11</v>
       </c>
       <c r="B184" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -14321,7 +14321,7 @@
         <v>11</v>
       </c>
       <c r="B185" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -14329,7 +14329,7 @@
         <v>11</v>
       </c>
       <c r="B186" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -14337,7 +14337,7 @@
         <v>11</v>
       </c>
       <c r="B187" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -14345,7 +14345,7 @@
         <v>11</v>
       </c>
       <c r="B188" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -14353,7 +14353,7 @@
         <v>11</v>
       </c>
       <c r="B189" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -14361,7 +14361,7 @@
         <v>11</v>
       </c>
       <c r="B190" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -14369,7 +14369,7 @@
         <v>11</v>
       </c>
       <c r="B191" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -14377,7 +14377,7 @@
         <v>11</v>
       </c>
       <c r="B192" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -14385,7 +14385,7 @@
         <v>11</v>
       </c>
       <c r="B193" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -14393,7 +14393,7 @@
         <v>11</v>
       </c>
       <c r="B194" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -14401,7 +14401,7 @@
         <v>11</v>
       </c>
       <c r="B195" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -14409,7 +14409,7 @@
         <v>11</v>
       </c>
       <c r="B196" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -14417,7 +14417,7 @@
         <v>11</v>
       </c>
       <c r="B197" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -14425,7 +14425,7 @@
         <v>11</v>
       </c>
       <c r="B198" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -14433,7 +14433,7 @@
         <v>11</v>
       </c>
       <c r="B199" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -14441,7 +14441,7 @@
         <v>11</v>
       </c>
       <c r="B200" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -14449,7 +14449,7 @@
         <v>11</v>
       </c>
       <c r="B201" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -14457,7 +14457,7 @@
         <v>11</v>
       </c>
       <c r="B202" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -14465,7 +14465,7 @@
         <v>11</v>
       </c>
       <c r="B203" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -14473,7 +14473,7 @@
         <v>11</v>
       </c>
       <c r="B204" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -14481,7 +14481,7 @@
         <v>11</v>
       </c>
       <c r="B205" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -14489,7 +14489,7 @@
         <v>11</v>
       </c>
       <c r="B206" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -14497,7 +14497,7 @@
         <v>11</v>
       </c>
       <c r="B207" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -14505,7 +14505,7 @@
         <v>11</v>
       </c>
       <c r="B208" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
@@ -14513,7 +14513,7 @@
         <v>11</v>
       </c>
       <c r="B209" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
@@ -14521,7 +14521,7 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -14532,7 +14532,7 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -14543,7 +14543,7 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -14554,7 +14554,7 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -14565,7 +14565,7 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -14576,7 +14576,7 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -14587,7 +14587,7 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -14598,7 +14598,7 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -14609,7 +14609,7 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -14620,7 +14620,7 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -14631,7 +14631,7 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -14642,7 +14642,7 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -14686,7 +14686,7 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -14697,7 +14697,7 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -14708,7 +14708,7 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -14719,7 +14719,7 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -14730,7 +14730,7 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -14752,7 +14752,7 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -14763,7 +14763,7 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -14774,7 +14774,7 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -14785,7 +14785,7 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -14796,7 +14796,7 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -14807,7 +14807,7 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -14818,7 +14818,7 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -14829,7 +14829,7 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -14851,7 +14851,7 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -14862,7 +14862,7 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -14873,7 +14873,7 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C242">
         <v>0</v>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9678F43D-8C85-443C-B84E-489DF979BD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0A911C-4B9C-4937-A18E-1EF9B0FF13A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4590" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Edges" sheetId="3" r:id="rId3"/>
     <sheet name="Parameters" sheetId="4" r:id="rId4"/>
     <sheet name="Supply" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="142">
   <si>
     <t>Commodities</t>
   </si>
@@ -468,9 +467,6 @@
   <si>
     <t>CM_Prod</t>
   </si>
-  <si>
-    <t>CM_prod</t>
-  </si>
 </sst>
 </file>
 
@@ -528,27 +524,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DFD5A1F0-17EE-4641-AA87-3712C2DAEDBF}" name="Table1" displayName="Table1" ref="A1:C258" totalsRowShown="0">
-  <autoFilter ref="A1:C258" xr:uid="{DFD5A1F0-17EE-4641-AA87-3712C2DAEDBF}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Methane"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C258">
-    <sortCondition ref="B1:B258"/>
-  </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0608215F-997B-41D1-87B3-FE2E64A82554}" name="Commodity"/>
-    <tableColumn id="2" xr3:uid="{139933EE-A1B5-4254-B3A7-54EEE2638174}" name="Node"/>
-    <tableColumn id="3" xr3:uid="{E9E29D62-9F49-4606-8D34-5AAACB132FBC}" name="Supply"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4517,7 +4492,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I747"/>
+  <dimension ref="A1:I746"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -12831,7 +12806,7 @@
         <v>10000</v>
       </c>
       <c r="F287">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G287">
         <v>10000000</v>
@@ -13382,7 +13357,7 @@
         <v>10000</v>
       </c>
       <c r="F306">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G306">
         <v>10000000</v>
@@ -13411,7 +13386,7 @@
         <v>10000</v>
       </c>
       <c r="F307">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G307">
         <v>10000000</v>
@@ -13440,7 +13415,7 @@
         <v>10000</v>
       </c>
       <c r="F308">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G308">
         <v>10000000</v>
@@ -13469,7 +13444,7 @@
         <v>10000</v>
       </c>
       <c r="F309">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G309">
         <v>10000000</v>
@@ -13498,7 +13473,7 @@
         <v>10000</v>
       </c>
       <c r="F310">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G310">
         <v>10000000</v>
@@ -13527,7 +13502,7 @@
         <v>10000</v>
       </c>
       <c r="F311">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G311">
         <v>10000000</v>
@@ -13556,7 +13531,7 @@
         <v>10000</v>
       </c>
       <c r="F312">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G312">
         <v>10000000</v>
@@ -13585,7 +13560,7 @@
         <v>10000</v>
       </c>
       <c r="F313">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G313">
         <v>10000000</v>
@@ -13614,7 +13589,7 @@
         <v>10000</v>
       </c>
       <c r="F314">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G314">
         <v>10000000</v>
@@ -13643,7 +13618,7 @@
         <v>10000</v>
       </c>
       <c r="F315">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G315">
         <v>10000000</v>
@@ -13672,7 +13647,7 @@
         <v>10000</v>
       </c>
       <c r="F316">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G316">
         <v>10000000</v>
@@ -13701,7 +13676,7 @@
         <v>10000</v>
       </c>
       <c r="F317">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G317">
         <v>10000000</v>
@@ -14078,7 +14053,7 @@
         <v>10000</v>
       </c>
       <c r="F330">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G330">
         <v>10000000</v>
@@ -14107,7 +14082,7 @@
         <v>10000</v>
       </c>
       <c r="F331">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G331">
         <v>10000000</v>
@@ -14136,7 +14111,7 @@
         <v>10000</v>
       </c>
       <c r="F332">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G332">
         <v>10000000</v>
@@ -14165,7 +14140,7 @@
         <v>10000</v>
       </c>
       <c r="F333">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G333">
         <v>10000000</v>
@@ -14194,7 +14169,7 @@
         <v>10000</v>
       </c>
       <c r="F334">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G334">
         <v>10000000</v>
@@ -14223,7 +14198,7 @@
         <v>10000</v>
       </c>
       <c r="F335">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G335">
         <v>10000000</v>
@@ -14252,7 +14227,7 @@
         <v>10000</v>
       </c>
       <c r="F336">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G336">
         <v>10000000</v>
@@ -14281,7 +14256,7 @@
         <v>10000</v>
       </c>
       <c r="F337">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G337">
         <v>10000000</v>
@@ -14310,7 +14285,7 @@
         <v>10000</v>
       </c>
       <c r="F338">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G338">
         <v>10000000</v>
@@ -14339,7 +14314,7 @@
         <v>10000</v>
       </c>
       <c r="F339">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G339">
         <v>10000000</v>
@@ -14368,7 +14343,7 @@
         <v>10000</v>
       </c>
       <c r="F340">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G340">
         <v>10000000</v>
@@ -14397,7 +14372,7 @@
         <v>10000</v>
       </c>
       <c r="F341">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G341">
         <v>10000000</v>
@@ -14426,7 +14401,7 @@
         <v>10000</v>
       </c>
       <c r="F342">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G342">
         <v>10000000</v>
@@ -14455,7 +14430,7 @@
         <v>10000</v>
       </c>
       <c r="F343">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G343">
         <v>10000000</v>
@@ -14484,7 +14459,7 @@
         <v>10000</v>
       </c>
       <c r="F344">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G344">
         <v>10000000</v>
@@ -14513,7 +14488,7 @@
         <v>10000</v>
       </c>
       <c r="F345">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G345">
         <v>10000000</v>
@@ -14542,7 +14517,7 @@
         <v>10000</v>
       </c>
       <c r="F346">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G346">
         <v>10000000</v>
@@ -14571,7 +14546,7 @@
         <v>10000</v>
       </c>
       <c r="F347">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G347">
         <v>10000000</v>
@@ -14600,7 +14575,7 @@
         <v>10000</v>
       </c>
       <c r="F348">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G348">
         <v>10000000</v>
@@ -14629,7 +14604,7 @@
         <v>10000</v>
       </c>
       <c r="F349">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G349">
         <v>10000000</v>
@@ -14658,7 +14633,7 @@
         <v>10000</v>
       </c>
       <c r="F350">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G350">
         <v>10000000</v>
@@ -14687,7 +14662,7 @@
         <v>10000</v>
       </c>
       <c r="F351">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G351">
         <v>10000000</v>
@@ -14716,7 +14691,7 @@
         <v>10000</v>
       </c>
       <c r="F352">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G352">
         <v>10000000</v>
@@ -14745,7 +14720,7 @@
         <v>10000</v>
       </c>
       <c r="F353">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G353">
         <v>10000000</v>
@@ -14774,7 +14749,7 @@
         <v>10000</v>
       </c>
       <c r="F354">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G354">
         <v>10000000</v>
@@ -14803,7 +14778,7 @@
         <v>10000</v>
       </c>
       <c r="F355">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G355">
         <v>10000000</v>
@@ -14832,7 +14807,7 @@
         <v>10000</v>
       </c>
       <c r="F356">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G356">
         <v>10000000</v>
@@ -14861,7 +14836,7 @@
         <v>10000</v>
       </c>
       <c r="F357">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G357">
         <v>10000000</v>
@@ -14890,7 +14865,7 @@
         <v>10000</v>
       </c>
       <c r="F358">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G358">
         <v>10000000</v>
@@ -14919,7 +14894,7 @@
         <v>10000</v>
       </c>
       <c r="F359">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G359">
         <v>10000000</v>
@@ -14948,7 +14923,7 @@
         <v>10000</v>
       </c>
       <c r="F360">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G360">
         <v>10000000</v>
@@ -14977,7 +14952,7 @@
         <v>10000</v>
       </c>
       <c r="F361">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G361">
         <v>10000000</v>
@@ -15006,7 +14981,7 @@
         <v>10000</v>
       </c>
       <c r="F362">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G362">
         <v>10000000</v>
@@ -15035,7 +15010,7 @@
         <v>10000</v>
       </c>
       <c r="F363">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G363">
         <v>10000000</v>
@@ -15064,7 +15039,7 @@
         <v>10000</v>
       </c>
       <c r="F364">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G364">
         <v>10000000</v>
@@ -15093,7 +15068,7 @@
         <v>10000</v>
       </c>
       <c r="F365">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G365">
         <v>10000000</v>
@@ -15122,7 +15097,7 @@
         <v>10000</v>
       </c>
       <c r="F366">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G366">
         <v>10000000</v>
@@ -15151,7 +15126,7 @@
         <v>10000</v>
       </c>
       <c r="F367">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G367">
         <v>10000000</v>
@@ -15180,7 +15155,7 @@
         <v>10000</v>
       </c>
       <c r="F368">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G368">
         <v>10000000</v>
@@ -15209,7 +15184,7 @@
         <v>10000</v>
       </c>
       <c r="F369">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G369">
         <v>10000000</v>
@@ -15238,7 +15213,7 @@
         <v>10000</v>
       </c>
       <c r="F370">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G370">
         <v>10000000</v>
@@ -15267,7 +15242,7 @@
         <v>10000</v>
       </c>
       <c r="F371">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G371">
         <v>10000000</v>
@@ -15296,7 +15271,7 @@
         <v>10000</v>
       </c>
       <c r="F372">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G372">
         <v>10000000</v>
@@ -15325,7 +15300,7 @@
         <v>10000</v>
       </c>
       <c r="F373">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G373">
         <v>10000000</v>
@@ -15354,7 +15329,7 @@
         <v>10000</v>
       </c>
       <c r="F374">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G374">
         <v>10000000</v>
@@ -15383,7 +15358,7 @@
         <v>10000</v>
       </c>
       <c r="F375">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G375">
         <v>10000000</v>
@@ -15412,7 +15387,7 @@
         <v>10000</v>
       </c>
       <c r="F376">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G376">
         <v>10000000</v>
@@ -15441,7 +15416,7 @@
         <v>10000</v>
       </c>
       <c r="F377">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G377">
         <v>10000000</v>
@@ -15470,7 +15445,7 @@
         <v>10000</v>
       </c>
       <c r="F378">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G378">
         <v>10000000</v>
@@ -15499,7 +15474,7 @@
         <v>10000</v>
       </c>
       <c r="F379">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G379">
         <v>10000000</v>
@@ -15528,7 +15503,7 @@
         <v>10000</v>
       </c>
       <c r="F380">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G380">
         <v>10000000</v>
@@ -15557,7 +15532,7 @@
         <v>10000</v>
       </c>
       <c r="F381">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G381">
         <v>10000000</v>
@@ -15586,7 +15561,7 @@
         <v>10000</v>
       </c>
       <c r="F382">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G382">
         <v>10000000</v>
@@ -15615,7 +15590,7 @@
         <v>10000</v>
       </c>
       <c r="F383">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G383">
         <v>10000000</v>
@@ -15644,7 +15619,7 @@
         <v>10000</v>
       </c>
       <c r="F384">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G384">
         <v>10000000</v>
@@ -15673,7 +15648,7 @@
         <v>10000</v>
       </c>
       <c r="F385">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G385">
         <v>10000000</v>
@@ -15702,7 +15677,7 @@
         <v>10000</v>
       </c>
       <c r="F386">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G386">
         <v>10000000</v>
@@ -15731,7 +15706,7 @@
         <v>10000</v>
       </c>
       <c r="F387">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G387">
         <v>10000000</v>
@@ -15760,7 +15735,7 @@
         <v>10000</v>
       </c>
       <c r="F388">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G388">
         <v>10000000</v>
@@ -15789,7 +15764,7 @@
         <v>10000</v>
       </c>
       <c r="F389">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G389">
         <v>10000000</v>
@@ -15818,7 +15793,7 @@
         <v>10000</v>
       </c>
       <c r="F390">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G390">
         <v>10000000</v>
@@ -15847,7 +15822,7 @@
         <v>10000</v>
       </c>
       <c r="F391">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G391">
         <v>10000000</v>
@@ -15876,7 +15851,7 @@
         <v>10000</v>
       </c>
       <c r="F392">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G392">
         <v>10000000</v>
@@ -15905,7 +15880,7 @@
         <v>10000</v>
       </c>
       <c r="F393">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G393">
         <v>10000000</v>
@@ -15934,7 +15909,7 @@
         <v>10000</v>
       </c>
       <c r="F394">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G394">
         <v>10000000</v>
@@ -15963,7 +15938,7 @@
         <v>10000</v>
       </c>
       <c r="F395">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G395">
         <v>10000000</v>
@@ -15992,7 +15967,7 @@
         <v>10000</v>
       </c>
       <c r="F396">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G396">
         <v>10000000</v>
@@ -16021,7 +15996,7 @@
         <v>10000</v>
       </c>
       <c r="F397">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G397">
         <v>10000000</v>
@@ -16050,7 +16025,7 @@
         <v>10000</v>
       </c>
       <c r="F398">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G398">
         <v>10000000</v>
@@ -16079,7 +16054,7 @@
         <v>10000</v>
       </c>
       <c r="F399">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G399">
         <v>10000000</v>
@@ -16108,7 +16083,7 @@
         <v>10000</v>
       </c>
       <c r="F400">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G400">
         <v>10000000</v>
@@ -16137,7 +16112,7 @@
         <v>10000</v>
       </c>
       <c r="F401">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G401">
         <v>10000000</v>
@@ -16166,7 +16141,7 @@
         <v>10000</v>
       </c>
       <c r="F402">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G402">
         <v>10000000</v>
@@ -16195,7 +16170,7 @@
         <v>10000</v>
       </c>
       <c r="F403">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G403">
         <v>10000000</v>
@@ -16224,7 +16199,7 @@
         <v>10000</v>
       </c>
       <c r="F404">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G404">
         <v>10000000</v>
@@ -16253,7 +16228,7 @@
         <v>10000</v>
       </c>
       <c r="F405">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G405">
         <v>10000000</v>
@@ -16282,7 +16257,7 @@
         <v>10000</v>
       </c>
       <c r="F406">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G406">
         <v>10000000</v>
@@ -16311,7 +16286,7 @@
         <v>10000</v>
       </c>
       <c r="F407">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G407">
         <v>10000000</v>
@@ -16340,7 +16315,7 @@
         <v>10000</v>
       </c>
       <c r="F408">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G408">
         <v>10000000</v>
@@ -16369,7 +16344,7 @@
         <v>10000</v>
       </c>
       <c r="F409">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G409">
         <v>10000000</v>
@@ -16398,7 +16373,7 @@
         <v>10000</v>
       </c>
       <c r="F410">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G410">
         <v>10000000</v>
@@ -16427,7 +16402,7 @@
         <v>10000</v>
       </c>
       <c r="F411">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G411">
         <v>10000000</v>
@@ -16456,7 +16431,7 @@
         <v>10000</v>
       </c>
       <c r="F412">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G412">
         <v>10000000</v>
@@ -16485,7 +16460,7 @@
         <v>10000</v>
       </c>
       <c r="F413">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G413">
         <v>10000000</v>
@@ -16514,7 +16489,7 @@
         <v>10000</v>
       </c>
       <c r="F414">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G414">
         <v>10000000</v>
@@ -16543,7 +16518,7 @@
         <v>10000</v>
       </c>
       <c r="F415">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G415">
         <v>10000000</v>
@@ -16572,7 +16547,7 @@
         <v>10000</v>
       </c>
       <c r="F416">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G416">
         <v>10000000</v>
@@ -16601,7 +16576,7 @@
         <v>10000</v>
       </c>
       <c r="F417">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G417">
         <v>10000000</v>
@@ -16630,7 +16605,7 @@
         <v>10000</v>
       </c>
       <c r="F418">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G418">
         <v>10000000</v>
@@ -16659,7 +16634,7 @@
         <v>10000</v>
       </c>
       <c r="F419">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G419">
         <v>10000000</v>
@@ -16688,7 +16663,7 @@
         <v>10000</v>
       </c>
       <c r="F420">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G420">
         <v>10000000</v>
@@ -16717,7 +16692,7 @@
         <v>10000</v>
       </c>
       <c r="F421">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G421">
         <v>10000000</v>
@@ -16746,7 +16721,7 @@
         <v>10000</v>
       </c>
       <c r="F422">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G422">
         <v>10000000</v>
@@ -16775,7 +16750,7 @@
         <v>10000</v>
       </c>
       <c r="F423">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G423">
         <v>10000000</v>
@@ -16804,7 +16779,7 @@
         <v>10000</v>
       </c>
       <c r="F424">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G424">
         <v>10000000</v>
@@ -16833,7 +16808,7 @@
         <v>10000</v>
       </c>
       <c r="F425">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G425">
         <v>10000000</v>
@@ -16862,7 +16837,7 @@
         <v>10000</v>
       </c>
       <c r="F426">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G426">
         <v>10000000</v>
@@ -16891,7 +16866,7 @@
         <v>10000</v>
       </c>
       <c r="F427">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G427">
         <v>10000000</v>
@@ -16920,7 +16895,7 @@
         <v>10000</v>
       </c>
       <c r="F428">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G428">
         <v>10000000</v>
@@ -16949,7 +16924,7 @@
         <v>10000</v>
       </c>
       <c r="F429">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G429">
         <v>10000000</v>
@@ -16978,7 +16953,7 @@
         <v>10000</v>
       </c>
       <c r="F430">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G430">
         <v>10000000</v>
@@ -17007,7 +16982,7 @@
         <v>10000</v>
       </c>
       <c r="F431">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G431">
         <v>10000000</v>
@@ -17036,7 +17011,7 @@
         <v>10000</v>
       </c>
       <c r="F432">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G432">
         <v>10000000</v>
@@ -17065,7 +17040,7 @@
         <v>10000</v>
       </c>
       <c r="F433">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G433">
         <v>10000000</v>
@@ -17094,7 +17069,7 @@
         <v>10000</v>
       </c>
       <c r="F434">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G434">
         <v>10000000</v>
@@ -17123,7 +17098,7 @@
         <v>10000</v>
       </c>
       <c r="F435">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G435">
         <v>10000000</v>
@@ -17152,7 +17127,7 @@
         <v>10000</v>
       </c>
       <c r="F436">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G436">
         <v>10000000</v>
@@ -17181,7 +17156,7 @@
         <v>10000</v>
       </c>
       <c r="F437">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G437">
         <v>10000000</v>
@@ -17210,7 +17185,7 @@
         <v>10000</v>
       </c>
       <c r="F438">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G438">
         <v>10000000</v>
@@ -17239,7 +17214,7 @@
         <v>10000</v>
       </c>
       <c r="F439">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G439">
         <v>10000000</v>
@@ -17256,10 +17231,10 @@
         <v>11</v>
       </c>
       <c r="B440" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C440" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="D440">
         <v>10000</v>
@@ -17285,10 +17260,10 @@
         <v>11</v>
       </c>
       <c r="B441" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C441" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="D441">
         <v>10000</v>
@@ -17317,7 +17292,7 @@
         <v>137</v>
       </c>
       <c r="C442" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D442">
         <v>10000</v>
@@ -17346,7 +17321,7 @@
         <v>137</v>
       </c>
       <c r="C443" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D443">
         <v>10000</v>
@@ -17375,7 +17350,7 @@
         <v>137</v>
       </c>
       <c r="C444" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D444">
         <v>10000</v>
@@ -17404,7 +17379,7 @@
         <v>137</v>
       </c>
       <c r="C445" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D445">
         <v>10000</v>
@@ -17433,7 +17408,7 @@
         <v>137</v>
       </c>
       <c r="C446" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D446">
         <v>10000</v>
@@ -17462,7 +17437,7 @@
         <v>137</v>
       </c>
       <c r="C447" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D447">
         <v>10000</v>
@@ -17491,7 +17466,7 @@
         <v>137</v>
       </c>
       <c r="C448" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D448">
         <v>10000</v>
@@ -17520,7 +17495,7 @@
         <v>137</v>
       </c>
       <c r="C449" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D449">
         <v>10000</v>
@@ -17549,7 +17524,7 @@
         <v>137</v>
       </c>
       <c r="C450" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D450">
         <v>10000</v>
@@ -17578,7 +17553,7 @@
         <v>137</v>
       </c>
       <c r="C451" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D451">
         <v>10000</v>
@@ -17607,7 +17582,7 @@
         <v>137</v>
       </c>
       <c r="C452" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D452">
         <v>10000</v>
@@ -17636,7 +17611,7 @@
         <v>137</v>
       </c>
       <c r="C453" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D453">
         <v>10000</v>
@@ -17665,7 +17640,7 @@
         <v>137</v>
       </c>
       <c r="C454" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D454">
         <v>10000</v>
@@ -17694,7 +17669,7 @@
         <v>137</v>
       </c>
       <c r="C455" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D455">
         <v>10000</v>
@@ -17723,7 +17698,7 @@
         <v>137</v>
       </c>
       <c r="C456" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D456">
         <v>10000</v>
@@ -17752,7 +17727,7 @@
         <v>137</v>
       </c>
       <c r="C457" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D457">
         <v>10000</v>
@@ -17781,7 +17756,7 @@
         <v>137</v>
       </c>
       <c r="C458" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D458">
         <v>10000</v>
@@ -17810,7 +17785,7 @@
         <v>137</v>
       </c>
       <c r="C459" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D459">
         <v>10000</v>
@@ -17839,7 +17814,7 @@
         <v>137</v>
       </c>
       <c r="C460" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D460">
         <v>10000</v>
@@ -17865,10 +17840,10 @@
         <v>11</v>
       </c>
       <c r="B461" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C461" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D461">
         <v>10000</v>
@@ -17894,10 +17869,10 @@
         <v>11</v>
       </c>
       <c r="B462" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C462" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D462">
         <v>10000</v>
@@ -17923,10 +17898,10 @@
         <v>11</v>
       </c>
       <c r="B463" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C463" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="D463">
         <v>10000</v>
@@ -17955,7 +17930,7 @@
         <v>135</v>
       </c>
       <c r="C464" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D464">
         <v>10000</v>
@@ -17984,7 +17959,7 @@
         <v>135</v>
       </c>
       <c r="C465" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D465">
         <v>10000</v>
@@ -18013,7 +17988,7 @@
         <v>135</v>
       </c>
       <c r="C466" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D466">
         <v>10000</v>
@@ -18042,7 +18017,7 @@
         <v>135</v>
       </c>
       <c r="C467" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D467">
         <v>10000</v>
@@ -18071,7 +18046,7 @@
         <v>135</v>
       </c>
       <c r="C468" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D468">
         <v>10000</v>
@@ -18100,7 +18075,7 @@
         <v>135</v>
       </c>
       <c r="C469" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D469">
         <v>10000</v>
@@ -18129,7 +18104,7 @@
         <v>135</v>
       </c>
       <c r="C470" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D470">
         <v>10000</v>
@@ -18158,7 +18133,7 @@
         <v>135</v>
       </c>
       <c r="C471" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D471">
         <v>10000</v>
@@ -18187,7 +18162,7 @@
         <v>135</v>
       </c>
       <c r="C472" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D472">
         <v>10000</v>
@@ -18216,7 +18191,7 @@
         <v>135</v>
       </c>
       <c r="C473" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D473">
         <v>10000</v>
@@ -18245,7 +18220,7 @@
         <v>135</v>
       </c>
       <c r="C474" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D474">
         <v>10000</v>
@@ -18274,7 +18249,7 @@
         <v>135</v>
       </c>
       <c r="C475" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D475">
         <v>10000</v>
@@ -18303,7 +18278,7 @@
         <v>135</v>
       </c>
       <c r="C476" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D476">
         <v>10000</v>
@@ -18332,7 +18307,7 @@
         <v>135</v>
       </c>
       <c r="C477" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D477">
         <v>10000</v>
@@ -18361,7 +18336,7 @@
         <v>135</v>
       </c>
       <c r="C478" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D478">
         <v>10000</v>
@@ -18390,7 +18365,7 @@
         <v>135</v>
       </c>
       <c r="C479" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D479">
         <v>10000</v>
@@ -18419,7 +18394,7 @@
         <v>135</v>
       </c>
       <c r="C480" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D480">
         <v>10000</v>
@@ -18448,7 +18423,7 @@
         <v>135</v>
       </c>
       <c r="C481" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D481">
         <v>10000</v>
@@ -18474,10 +18449,10 @@
         <v>11</v>
       </c>
       <c r="B482" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C482" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D482">
         <v>10000</v>
@@ -18503,10 +18478,10 @@
         <v>11</v>
       </c>
       <c r="B483" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C483" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D483">
         <v>10000</v>
@@ -18532,10 +18507,10 @@
         <v>11</v>
       </c>
       <c r="B484" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C484" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="D484">
         <v>10000</v>
@@ -18564,7 +18539,7 @@
         <v>136</v>
       </c>
       <c r="C485" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D485">
         <v>10000</v>
@@ -18593,7 +18568,7 @@
         <v>136</v>
       </c>
       <c r="C486" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D486">
         <v>10000</v>
@@ -18622,7 +18597,7 @@
         <v>136</v>
       </c>
       <c r="C487" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D487">
         <v>10000</v>
@@ -18651,7 +18626,7 @@
         <v>136</v>
       </c>
       <c r="C488" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D488">
         <v>10000</v>
@@ -18680,7 +18655,7 @@
         <v>136</v>
       </c>
       <c r="C489" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D489">
         <v>10000</v>
@@ -18709,7 +18684,7 @@
         <v>136</v>
       </c>
       <c r="C490" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D490">
         <v>10000</v>
@@ -18738,7 +18713,7 @@
         <v>136</v>
       </c>
       <c r="C491" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D491">
         <v>10000</v>
@@ -18767,7 +18742,7 @@
         <v>136</v>
       </c>
       <c r="C492" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D492">
         <v>10000</v>
@@ -18796,7 +18771,7 @@
         <v>136</v>
       </c>
       <c r="C493" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D493">
         <v>10000</v>
@@ -18825,7 +18800,7 @@
         <v>136</v>
       </c>
       <c r="C494" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D494">
         <v>10000</v>
@@ -18854,7 +18829,7 @@
         <v>136</v>
       </c>
       <c r="C495" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D495">
         <v>10000</v>
@@ -18883,7 +18858,7 @@
         <v>136</v>
       </c>
       <c r="C496" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D496">
         <v>10000</v>
@@ -18912,7 +18887,7 @@
         <v>136</v>
       </c>
       <c r="C497" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D497">
         <v>10000</v>
@@ -18941,7 +18916,7 @@
         <v>136</v>
       </c>
       <c r="C498" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D498">
         <v>10000</v>
@@ -18970,7 +18945,7 @@
         <v>136</v>
       </c>
       <c r="C499" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D499">
         <v>10000</v>
@@ -18999,7 +18974,7 @@
         <v>136</v>
       </c>
       <c r="C500" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D500">
         <v>10000</v>
@@ -19028,7 +19003,7 @@
         <v>136</v>
       </c>
       <c r="C501" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D501">
         <v>10000</v>
@@ -19057,7 +19032,7 @@
         <v>136</v>
       </c>
       <c r="C502" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D502">
         <v>10000</v>
@@ -19086,7 +19061,7 @@
         <v>136</v>
       </c>
       <c r="C503" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D503">
         <v>10000</v>
@@ -19109,13 +19084,13 @@
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B504" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C504" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D504">
         <v>10000</v>
@@ -19124,7 +19099,7 @@
         <v>10000</v>
       </c>
       <c r="F504">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G504">
         <v>10000000</v>
@@ -19141,10 +19116,10 @@
         <v>12</v>
       </c>
       <c r="B505" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C505" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D505">
         <v>10000</v>
@@ -19170,10 +19145,10 @@
         <v>12</v>
       </c>
       <c r="B506" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C506" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D506">
         <v>10000</v>
@@ -19202,7 +19177,7 @@
         <v>105</v>
       </c>
       <c r="C507" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D507">
         <v>10000</v>
@@ -19231,7 +19206,7 @@
         <v>105</v>
       </c>
       <c r="C508" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D508">
         <v>10000</v>
@@ -19260,7 +19235,7 @@
         <v>105</v>
       </c>
       <c r="C509" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D509">
         <v>10000</v>
@@ -19289,7 +19264,7 @@
         <v>105</v>
       </c>
       <c r="C510" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D510">
         <v>10000</v>
@@ -19318,7 +19293,7 @@
         <v>105</v>
       </c>
       <c r="C511" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D511">
         <v>10000</v>
@@ -19347,7 +19322,7 @@
         <v>105</v>
       </c>
       <c r="C512" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D512">
         <v>10000</v>
@@ -19376,7 +19351,7 @@
         <v>105</v>
       </c>
       <c r="C513" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D513">
         <v>10000</v>
@@ -19405,7 +19380,7 @@
         <v>105</v>
       </c>
       <c r="C514" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D514">
         <v>10000</v>
@@ -19434,7 +19409,7 @@
         <v>105</v>
       </c>
       <c r="C515" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D515">
         <v>10000</v>
@@ -19463,7 +19438,7 @@
         <v>105</v>
       </c>
       <c r="C516" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D516">
         <v>10000</v>
@@ -19492,7 +19467,7 @@
         <v>105</v>
       </c>
       <c r="C517" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D517">
         <v>10000</v>
@@ -19521,7 +19496,7 @@
         <v>105</v>
       </c>
       <c r="C518" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D518">
         <v>10000</v>
@@ -19550,7 +19525,7 @@
         <v>105</v>
       </c>
       <c r="C519" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D519">
         <v>10000</v>
@@ -19579,7 +19554,7 @@
         <v>105</v>
       </c>
       <c r="C520" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D520">
         <v>10000</v>
@@ -19608,7 +19583,7 @@
         <v>105</v>
       </c>
       <c r="C521" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D521">
         <v>10000</v>
@@ -19637,7 +19612,7 @@
         <v>105</v>
       </c>
       <c r="C522" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D522">
         <v>10000</v>
@@ -19666,7 +19641,7 @@
         <v>105</v>
       </c>
       <c r="C523" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D523">
         <v>10000</v>
@@ -19695,7 +19670,7 @@
         <v>105</v>
       </c>
       <c r="C524" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D524">
         <v>10000</v>
@@ -19724,7 +19699,7 @@
         <v>105</v>
       </c>
       <c r="C525" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D525">
         <v>10000</v>
@@ -19750,10 +19725,10 @@
         <v>12</v>
       </c>
       <c r="B526" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C526" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D526">
         <v>10000</v>
@@ -19779,10 +19754,10 @@
         <v>12</v>
       </c>
       <c r="B527" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C527" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D527">
         <v>10000</v>
@@ -19808,10 +19783,10 @@
         <v>12</v>
       </c>
       <c r="B528" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C528" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="D528">
         <v>10000</v>
@@ -19840,7 +19815,7 @@
         <v>108</v>
       </c>
       <c r="C529" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D529">
         <v>10000</v>
@@ -19869,7 +19844,7 @@
         <v>108</v>
       </c>
       <c r="C530" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D530">
         <v>10000</v>
@@ -19898,7 +19873,7 @@
         <v>108</v>
       </c>
       <c r="C531" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D531">
         <v>10000</v>
@@ -19927,7 +19902,7 @@
         <v>108</v>
       </c>
       <c r="C532" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D532">
         <v>10000</v>
@@ -19956,7 +19931,7 @@
         <v>108</v>
       </c>
       <c r="C533" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D533">
         <v>10000</v>
@@ -19985,7 +19960,7 @@
         <v>108</v>
       </c>
       <c r="C534" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D534">
         <v>10000</v>
@@ -20014,7 +19989,7 @@
         <v>108</v>
       </c>
       <c r="C535" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D535">
         <v>10000</v>
@@ -20043,7 +20018,7 @@
         <v>108</v>
       </c>
       <c r="C536" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D536">
         <v>10000</v>
@@ -20072,7 +20047,7 @@
         <v>108</v>
       </c>
       <c r="C537" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D537">
         <v>10000</v>
@@ -20101,7 +20076,7 @@
         <v>108</v>
       </c>
       <c r="C538" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D538">
         <v>10000</v>
@@ -20130,7 +20105,7 @@
         <v>108</v>
       </c>
       <c r="C539" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D539">
         <v>10000</v>
@@ -20159,7 +20134,7 @@
         <v>108</v>
       </c>
       <c r="C540" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D540">
         <v>10000</v>
@@ -20188,7 +20163,7 @@
         <v>108</v>
       </c>
       <c r="C541" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D541">
         <v>10000</v>
@@ -20217,7 +20192,7 @@
         <v>108</v>
       </c>
       <c r="C542" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D542">
         <v>10000</v>
@@ -20246,7 +20221,7 @@
         <v>108</v>
       </c>
       <c r="C543" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D543">
         <v>10000</v>
@@ -20275,7 +20250,7 @@
         <v>108</v>
       </c>
       <c r="C544" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D544">
         <v>10000</v>
@@ -20304,7 +20279,7 @@
         <v>108</v>
       </c>
       <c r="C545" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D545">
         <v>10000</v>
@@ -20333,7 +20308,7 @@
         <v>108</v>
       </c>
       <c r="C546" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D546">
         <v>10000</v>
@@ -20362,7 +20337,7 @@
         <v>108</v>
       </c>
       <c r="C547" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D547">
         <v>10000</v>
@@ -20388,10 +20363,10 @@
         <v>12</v>
       </c>
       <c r="B548" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C548" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="D548">
         <v>10000</v>
@@ -20417,10 +20392,10 @@
         <v>12</v>
       </c>
       <c r="B549" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C549" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D549">
         <v>10000</v>
@@ -20446,10 +20421,10 @@
         <v>12</v>
       </c>
       <c r="B550" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C550" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="D550">
         <v>10000</v>
@@ -20478,7 +20453,7 @@
         <v>111</v>
       </c>
       <c r="C551" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D551">
         <v>10000</v>
@@ -20507,7 +20482,7 @@
         <v>111</v>
       </c>
       <c r="C552" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D552">
         <v>10000</v>
@@ -20536,7 +20511,7 @@
         <v>111</v>
       </c>
       <c r="C553" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D553">
         <v>10000</v>
@@ -20565,7 +20540,7 @@
         <v>111</v>
       </c>
       <c r="C554" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D554">
         <v>10000</v>
@@ -20594,7 +20569,7 @@
         <v>111</v>
       </c>
       <c r="C555" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D555">
         <v>10000</v>
@@ -20623,7 +20598,7 @@
         <v>111</v>
       </c>
       <c r="C556" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D556">
         <v>10000</v>
@@ -20652,7 +20627,7 @@
         <v>111</v>
       </c>
       <c r="C557" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D557">
         <v>10000</v>
@@ -20681,7 +20656,7 @@
         <v>111</v>
       </c>
       <c r="C558" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D558">
         <v>10000</v>
@@ -20710,7 +20685,7 @@
         <v>111</v>
       </c>
       <c r="C559" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D559">
         <v>10000</v>
@@ -20739,7 +20714,7 @@
         <v>111</v>
       </c>
       <c r="C560" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D560">
         <v>10000</v>
@@ -20768,7 +20743,7 @@
         <v>111</v>
       </c>
       <c r="C561" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D561">
         <v>10000</v>
@@ -20797,7 +20772,7 @@
         <v>111</v>
       </c>
       <c r="C562" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D562">
         <v>10000</v>
@@ -20826,7 +20801,7 @@
         <v>111</v>
       </c>
       <c r="C563" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D563">
         <v>10000</v>
@@ -20855,7 +20830,7 @@
         <v>111</v>
       </c>
       <c r="C564" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D564">
         <v>10000</v>
@@ -20884,7 +20859,7 @@
         <v>111</v>
       </c>
       <c r="C565" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D565">
         <v>10000</v>
@@ -20913,7 +20888,7 @@
         <v>111</v>
       </c>
       <c r="C566" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D566">
         <v>10000</v>
@@ -20942,7 +20917,7 @@
         <v>111</v>
       </c>
       <c r="C567" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D567">
         <v>10000</v>
@@ -20971,7 +20946,7 @@
         <v>111</v>
       </c>
       <c r="C568" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D568">
         <v>10000</v>
@@ -21000,7 +20975,7 @@
         <v>111</v>
       </c>
       <c r="C569" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D569">
         <v>10000</v>
@@ -21026,10 +21001,10 @@
         <v>12</v>
       </c>
       <c r="B570" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C570" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D570">
         <v>10000</v>
@@ -21055,10 +21030,10 @@
         <v>12</v>
       </c>
       <c r="B571" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C571" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D571">
         <v>10000</v>
@@ -21084,10 +21059,10 @@
         <v>12</v>
       </c>
       <c r="B572" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C572" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="D572">
         <v>10000</v>
@@ -21116,7 +21091,7 @@
         <v>114</v>
       </c>
       <c r="C573" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D573">
         <v>10000</v>
@@ -21145,7 +21120,7 @@
         <v>114</v>
       </c>
       <c r="C574" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D574">
         <v>10000</v>
@@ -21174,7 +21149,7 @@
         <v>114</v>
       </c>
       <c r="C575" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D575">
         <v>10000</v>
@@ -21203,7 +21178,7 @@
         <v>114</v>
       </c>
       <c r="C576" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D576">
         <v>10000</v>
@@ -21232,7 +21207,7 @@
         <v>114</v>
       </c>
       <c r="C577" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D577">
         <v>10000</v>
@@ -21261,7 +21236,7 @@
         <v>114</v>
       </c>
       <c r="C578" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D578">
         <v>10000</v>
@@ -21290,7 +21265,7 @@
         <v>114</v>
       </c>
       <c r="C579" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D579">
         <v>10000</v>
@@ -21319,7 +21294,7 @@
         <v>114</v>
       </c>
       <c r="C580" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D580">
         <v>10000</v>
@@ -21348,7 +21323,7 @@
         <v>114</v>
       </c>
       <c r="C581" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D581">
         <v>10000</v>
@@ -21377,7 +21352,7 @@
         <v>114</v>
       </c>
       <c r="C582" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D582">
         <v>10000</v>
@@ -21406,7 +21381,7 @@
         <v>114</v>
       </c>
       <c r="C583" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D583">
         <v>10000</v>
@@ -21435,7 +21410,7 @@
         <v>114</v>
       </c>
       <c r="C584" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D584">
         <v>10000</v>
@@ -21464,7 +21439,7 @@
         <v>114</v>
       </c>
       <c r="C585" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D585">
         <v>10000</v>
@@ -21493,7 +21468,7 @@
         <v>114</v>
       </c>
       <c r="C586" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D586">
         <v>10000</v>
@@ -21522,7 +21497,7 @@
         <v>114</v>
       </c>
       <c r="C587" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D587">
         <v>10000</v>
@@ -21551,7 +21526,7 @@
         <v>114</v>
       </c>
       <c r="C588" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D588">
         <v>10000</v>
@@ -21580,7 +21555,7 @@
         <v>114</v>
       </c>
       <c r="C589" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D589">
         <v>10000</v>
@@ -21609,7 +21584,7 @@
         <v>114</v>
       </c>
       <c r="C590" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D590">
         <v>10000</v>
@@ -21638,7 +21613,7 @@
         <v>114</v>
       </c>
       <c r="C591" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D591">
         <v>10000</v>
@@ -21664,10 +21639,10 @@
         <v>12</v>
       </c>
       <c r="B592" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C592" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D592">
         <v>10000</v>
@@ -21693,10 +21668,10 @@
         <v>12</v>
       </c>
       <c r="B593" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C593" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D593">
         <v>10000</v>
@@ -21722,10 +21697,10 @@
         <v>12</v>
       </c>
       <c r="B594" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C594" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D594">
         <v>10000</v>
@@ -21754,7 +21729,7 @@
         <v>117</v>
       </c>
       <c r="C595" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D595">
         <v>10000</v>
@@ -21783,7 +21758,7 @@
         <v>117</v>
       </c>
       <c r="C596" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D596">
         <v>10000</v>
@@ -21812,7 +21787,7 @@
         <v>117</v>
       </c>
       <c r="C597" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D597">
         <v>10000</v>
@@ -21841,7 +21816,7 @@
         <v>117</v>
       </c>
       <c r="C598" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D598">
         <v>10000</v>
@@ -21870,7 +21845,7 @@
         <v>117</v>
       </c>
       <c r="C599" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D599">
         <v>10000</v>
@@ -21899,7 +21874,7 @@
         <v>117</v>
       </c>
       <c r="C600" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D600">
         <v>10000</v>
@@ -21928,7 +21903,7 @@
         <v>117</v>
       </c>
       <c r="C601" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D601">
         <v>10000</v>
@@ -21957,7 +21932,7 @@
         <v>117</v>
       </c>
       <c r="C602" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D602">
         <v>10000</v>
@@ -21986,7 +21961,7 @@
         <v>117</v>
       </c>
       <c r="C603" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D603">
         <v>10000</v>
@@ -22015,7 +21990,7 @@
         <v>117</v>
       </c>
       <c r="C604" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D604">
         <v>10000</v>
@@ -22044,7 +22019,7 @@
         <v>117</v>
       </c>
       <c r="C605" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D605">
         <v>10000</v>
@@ -22073,7 +22048,7 @@
         <v>117</v>
       </c>
       <c r="C606" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D606">
         <v>10000</v>
@@ -22102,7 +22077,7 @@
         <v>117</v>
       </c>
       <c r="C607" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D607">
         <v>10000</v>
@@ -22131,7 +22106,7 @@
         <v>117</v>
       </c>
       <c r="C608" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D608">
         <v>10000</v>
@@ -22160,7 +22135,7 @@
         <v>117</v>
       </c>
       <c r="C609" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D609">
         <v>10000</v>
@@ -22189,7 +22164,7 @@
         <v>117</v>
       </c>
       <c r="C610" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D610">
         <v>10000</v>
@@ -22218,7 +22193,7 @@
         <v>117</v>
       </c>
       <c r="C611" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D611">
         <v>10000</v>
@@ -22247,7 +22222,7 @@
         <v>117</v>
       </c>
       <c r="C612" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D612">
         <v>10000</v>
@@ -22276,7 +22251,7 @@
         <v>117</v>
       </c>
       <c r="C613" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D613">
         <v>10000</v>
@@ -22302,10 +22277,10 @@
         <v>12</v>
       </c>
       <c r="B614" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="C614" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="D614">
         <v>10000</v>
@@ -22331,10 +22306,10 @@
         <v>12</v>
       </c>
       <c r="B615" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C615" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="D615">
         <v>10000</v>
@@ -22360,10 +22335,10 @@
         <v>12</v>
       </c>
       <c r="B616" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C616" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="D616">
         <v>10000</v>
@@ -22392,7 +22367,7 @@
         <v>137</v>
       </c>
       <c r="C617" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D617">
         <v>10000</v>
@@ -22421,7 +22396,7 @@
         <v>137</v>
       </c>
       <c r="C618" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D618">
         <v>10000</v>
@@ -22450,7 +22425,7 @@
         <v>137</v>
       </c>
       <c r="C619" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D619">
         <v>10000</v>
@@ -22479,7 +22454,7 @@
         <v>137</v>
       </c>
       <c r="C620" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D620">
         <v>10000</v>
@@ -22508,7 +22483,7 @@
         <v>137</v>
       </c>
       <c r="C621" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D621">
         <v>10000</v>
@@ -22537,7 +22512,7 @@
         <v>137</v>
       </c>
       <c r="C622" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D622">
         <v>10000</v>
@@ -22566,7 +22541,7 @@
         <v>137</v>
       </c>
       <c r="C623" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D623">
         <v>10000</v>
@@ -22595,7 +22570,7 @@
         <v>137</v>
       </c>
       <c r="C624" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D624">
         <v>10000</v>
@@ -22624,7 +22599,7 @@
         <v>137</v>
       </c>
       <c r="C625" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D625">
         <v>10000</v>
@@ -22653,7 +22628,7 @@
         <v>137</v>
       </c>
       <c r="C626" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D626">
         <v>10000</v>
@@ -22682,7 +22657,7 @@
         <v>137</v>
       </c>
       <c r="C627" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D627">
         <v>10000</v>
@@ -22711,7 +22686,7 @@
         <v>137</v>
       </c>
       <c r="C628" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D628">
         <v>10000</v>
@@ -22740,7 +22715,7 @@
         <v>137</v>
       </c>
       <c r="C629" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D629">
         <v>10000</v>
@@ -22769,7 +22744,7 @@
         <v>137</v>
       </c>
       <c r="C630" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D630">
         <v>10000</v>
@@ -22798,7 +22773,7 @@
         <v>137</v>
       </c>
       <c r="C631" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D631">
         <v>10000</v>
@@ -22827,7 +22802,7 @@
         <v>137</v>
       </c>
       <c r="C632" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D632">
         <v>10000</v>
@@ -22856,7 +22831,7 @@
         <v>137</v>
       </c>
       <c r="C633" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D633">
         <v>10000</v>
@@ -22885,7 +22860,7 @@
         <v>137</v>
       </c>
       <c r="C634" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D634">
         <v>10000</v>
@@ -22914,7 +22889,7 @@
         <v>137</v>
       </c>
       <c r="C635" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D635">
         <v>10000</v>
@@ -22940,10 +22915,10 @@
         <v>12</v>
       </c>
       <c r="B636" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C636" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D636">
         <v>10000</v>
@@ -22969,10 +22944,10 @@
         <v>12</v>
       </c>
       <c r="B637" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C637" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D637">
         <v>10000</v>
@@ -22998,10 +22973,10 @@
         <v>12</v>
       </c>
       <c r="B638" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C638" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="D638">
         <v>10000</v>
@@ -23030,7 +23005,7 @@
         <v>135</v>
       </c>
       <c r="C639" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D639">
         <v>10000</v>
@@ -23059,7 +23034,7 @@
         <v>135</v>
       </c>
       <c r="C640" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D640">
         <v>10000</v>
@@ -23088,7 +23063,7 @@
         <v>135</v>
       </c>
       <c r="C641" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D641">
         <v>10000</v>
@@ -23117,7 +23092,7 @@
         <v>135</v>
       </c>
       <c r="C642" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D642">
         <v>10000</v>
@@ -23146,7 +23121,7 @@
         <v>135</v>
       </c>
       <c r="C643" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D643">
         <v>10000</v>
@@ -23175,7 +23150,7 @@
         <v>135</v>
       </c>
       <c r="C644" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D644">
         <v>10000</v>
@@ -23204,7 +23179,7 @@
         <v>135</v>
       </c>
       <c r="C645" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D645">
         <v>10000</v>
@@ -23233,7 +23208,7 @@
         <v>135</v>
       </c>
       <c r="C646" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D646">
         <v>10000</v>
@@ -23262,7 +23237,7 @@
         <v>135</v>
       </c>
       <c r="C647" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D647">
         <v>10000</v>
@@ -23291,7 +23266,7 @@
         <v>135</v>
       </c>
       <c r="C648" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D648">
         <v>10000</v>
@@ -23320,7 +23295,7 @@
         <v>135</v>
       </c>
       <c r="C649" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D649">
         <v>10000</v>
@@ -23349,7 +23324,7 @@
         <v>135</v>
       </c>
       <c r="C650" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D650">
         <v>10000</v>
@@ -23378,7 +23353,7 @@
         <v>135</v>
       </c>
       <c r="C651" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D651">
         <v>10000</v>
@@ -23407,7 +23382,7 @@
         <v>135</v>
       </c>
       <c r="C652" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D652">
         <v>10000</v>
@@ -23436,7 +23411,7 @@
         <v>135</v>
       </c>
       <c r="C653" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D653">
         <v>10000</v>
@@ -23465,7 +23440,7 @@
         <v>135</v>
       </c>
       <c r="C654" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D654">
         <v>10000</v>
@@ -23494,7 +23469,7 @@
         <v>135</v>
       </c>
       <c r="C655" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D655">
         <v>10000</v>
@@ -23523,7 +23498,7 @@
         <v>135</v>
       </c>
       <c r="C656" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D656">
         <v>10000</v>
@@ -23549,10 +23524,10 @@
         <v>12</v>
       </c>
       <c r="B657" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C657" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D657">
         <v>10000</v>
@@ -23578,10 +23553,10 @@
         <v>12</v>
       </c>
       <c r="B658" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C658" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D658">
         <v>10000</v>
@@ -23607,10 +23582,10 @@
         <v>12</v>
       </c>
       <c r="B659" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C659" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="D659">
         <v>10000</v>
@@ -23639,7 +23614,7 @@
         <v>136</v>
       </c>
       <c r="C660" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D660">
         <v>10000</v>
@@ -23668,7 +23643,7 @@
         <v>136</v>
       </c>
       <c r="C661" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D661">
         <v>10000</v>
@@ -23697,7 +23672,7 @@
         <v>136</v>
       </c>
       <c r="C662" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D662">
         <v>10000</v>
@@ -23726,7 +23701,7 @@
         <v>136</v>
       </c>
       <c r="C663" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D663">
         <v>10000</v>
@@ -23755,7 +23730,7 @@
         <v>136</v>
       </c>
       <c r="C664" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D664">
         <v>10000</v>
@@ -23784,7 +23759,7 @@
         <v>136</v>
       </c>
       <c r="C665" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D665">
         <v>10000</v>
@@ -23813,7 +23788,7 @@
         <v>136</v>
       </c>
       <c r="C666" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D666">
         <v>10000</v>
@@ -23842,7 +23817,7 @@
         <v>136</v>
       </c>
       <c r="C667" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D667">
         <v>10000</v>
@@ -23871,7 +23846,7 @@
         <v>136</v>
       </c>
       <c r="C668" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D668">
         <v>10000</v>
@@ -23900,7 +23875,7 @@
         <v>136</v>
       </c>
       <c r="C669" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D669">
         <v>10000</v>
@@ -23929,7 +23904,7 @@
         <v>136</v>
       </c>
       <c r="C670" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D670">
         <v>10000</v>
@@ -23958,7 +23933,7 @@
         <v>136</v>
       </c>
       <c r="C671" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D671">
         <v>10000</v>
@@ -23987,7 +23962,7 @@
         <v>136</v>
       </c>
       <c r="C672" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D672">
         <v>10000</v>
@@ -24016,7 +23991,7 @@
         <v>136</v>
       </c>
       <c r="C673" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D673">
         <v>10000</v>
@@ -24045,7 +24020,7 @@
         <v>136</v>
       </c>
       <c r="C674" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D674">
         <v>10000</v>
@@ -24074,7 +24049,7 @@
         <v>136</v>
       </c>
       <c r="C675" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D675">
         <v>10000</v>
@@ -24103,7 +24078,7 @@
         <v>136</v>
       </c>
       <c r="C676" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D676">
         <v>10000</v>
@@ -24132,7 +24107,7 @@
         <v>136</v>
       </c>
       <c r="C677" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D677">
         <v>10000</v>
@@ -24161,7 +24136,7 @@
         <v>136</v>
       </c>
       <c r="C678" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D678">
         <v>10000</v>
@@ -24184,13 +24159,13 @@
     </row>
     <row r="679" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B679" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="C679" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D679">
         <v>10000</v>
@@ -24199,7 +24174,7 @@
         <v>10000</v>
       </c>
       <c r="F679">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G679">
         <v>10000000</v>
@@ -24216,10 +24191,10 @@
         <v>11</v>
       </c>
       <c r="B680" t="s">
+        <v>139</v>
+      </c>
+      <c r="C680" t="s">
         <v>97</v>
-      </c>
-      <c r="C680" t="s">
-        <v>139</v>
       </c>
       <c r="D680">
         <v>10000</v>
@@ -24245,10 +24220,10 @@
         <v>11</v>
       </c>
       <c r="B681" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C681" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D681">
         <v>10000</v>
@@ -24274,10 +24249,10 @@
         <v>11</v>
       </c>
       <c r="B682" t="s">
+        <v>109</v>
+      </c>
+      <c r="C682" t="s">
         <v>106</v>
-      </c>
-      <c r="C682" t="s">
-        <v>109</v>
       </c>
       <c r="D682">
         <v>10000</v>
@@ -24303,10 +24278,10 @@
         <v>11</v>
       </c>
       <c r="B683" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="C683" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D683">
         <v>10000</v>
@@ -24332,7 +24307,7 @@
         <v>11</v>
       </c>
       <c r="B684" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="C684" t="s">
         <v>118</v>
@@ -24361,7 +24336,7 @@
         <v>11</v>
       </c>
       <c r="B685" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C685" t="s">
         <v>118</v>
@@ -24390,10 +24365,10 @@
         <v>11</v>
       </c>
       <c r="B686" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="C686" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D686">
         <v>10000</v>
@@ -24419,10 +24394,10 @@
         <v>11</v>
       </c>
       <c r="B687" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="C687" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D687">
         <v>10000</v>
@@ -24448,10 +24423,10 @@
         <v>11</v>
       </c>
       <c r="B688" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C688" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="D688">
         <v>10000</v>
@@ -24477,10 +24452,10 @@
         <v>11</v>
       </c>
       <c r="B689" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C689" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D689">
         <v>10000</v>
@@ -24506,10 +24481,10 @@
         <v>11</v>
       </c>
       <c r="B690" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C690" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D690">
         <v>10000</v>
@@ -24535,10 +24510,10 @@
         <v>11</v>
       </c>
       <c r="B691" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C691" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D691">
         <v>10000</v>
@@ -24564,10 +24539,10 @@
         <v>11</v>
       </c>
       <c r="B692" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C692" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D692">
         <v>10000</v>
@@ -24593,10 +24568,10 @@
         <v>11</v>
       </c>
       <c r="B693" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C693" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D693">
         <v>10000</v>
@@ -24622,10 +24597,10 @@
         <v>11</v>
       </c>
       <c r="B694" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C694" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D694">
         <v>10000</v>
@@ -24648,13 +24623,13 @@
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B695" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C695" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D695">
         <v>10000</v>
@@ -24663,7 +24638,7 @@
         <v>10000</v>
       </c>
       <c r="F695">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G695">
         <v>10000000</v>
@@ -24680,10 +24655,10 @@
         <v>12</v>
       </c>
       <c r="B696" t="s">
+        <v>139</v>
+      </c>
+      <c r="C696" t="s">
         <v>97</v>
-      </c>
-      <c r="C696" t="s">
-        <v>139</v>
       </c>
       <c r="D696">
         <v>10000</v>
@@ -24709,10 +24684,10 @@
         <v>12</v>
       </c>
       <c r="B697" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C697" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D697">
         <v>10000</v>
@@ -24738,10 +24713,10 @@
         <v>12</v>
       </c>
       <c r="B698" t="s">
+        <v>109</v>
+      </c>
+      <c r="C698" t="s">
         <v>106</v>
-      </c>
-      <c r="C698" t="s">
-        <v>109</v>
       </c>
       <c r="D698">
         <v>10000</v>
@@ -24767,10 +24742,10 @@
         <v>12</v>
       </c>
       <c r="B699" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="C699" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D699">
         <v>10000</v>
@@ -24796,7 +24771,7 @@
         <v>12</v>
       </c>
       <c r="B700" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="C700" t="s">
         <v>118</v>
@@ -24825,7 +24800,7 @@
         <v>12</v>
       </c>
       <c r="B701" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C701" t="s">
         <v>118</v>
@@ -24854,10 +24829,10 @@
         <v>12</v>
       </c>
       <c r="B702" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="C702" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D702">
         <v>10000</v>
@@ -24883,10 +24858,10 @@
         <v>12</v>
       </c>
       <c r="B703" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="C703" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D703">
         <v>10000</v>
@@ -24912,10 +24887,10 @@
         <v>12</v>
       </c>
       <c r="B704" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C704" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="D704">
         <v>10000</v>
@@ -24941,10 +24916,10 @@
         <v>12</v>
       </c>
       <c r="B705" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C705" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D705">
         <v>10000</v>
@@ -24970,10 +24945,10 @@
         <v>12</v>
       </c>
       <c r="B706" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C706" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D706">
         <v>10000</v>
@@ -24999,10 +24974,10 @@
         <v>12</v>
       </c>
       <c r="B707" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C707" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D707">
         <v>10000</v>
@@ -25028,10 +25003,10 @@
         <v>12</v>
       </c>
       <c r="B708" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C708" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D708">
         <v>10000</v>
@@ -25057,10 +25032,10 @@
         <v>12</v>
       </c>
       <c r="B709" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C709" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D709">
         <v>10000</v>
@@ -25086,10 +25061,10 @@
         <v>12</v>
       </c>
       <c r="B710" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C710" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D710">
         <v>10000</v>
@@ -25112,13 +25087,13 @@
     </row>
     <row r="711" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B711" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C711" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D711">
         <v>10000</v>
@@ -25127,7 +25102,7 @@
         <v>10000</v>
       </c>
       <c r="F711">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G711">
         <v>10000000</v>
@@ -25144,10 +25119,10 @@
         <v>11</v>
       </c>
       <c r="B712" t="s">
+        <v>97</v>
+      </c>
+      <c r="C712" t="s">
         <v>99</v>
-      </c>
-      <c r="C712" t="s">
-        <v>97</v>
       </c>
       <c r="D712">
         <v>10000</v>
@@ -25173,10 +25148,10 @@
         <v>11</v>
       </c>
       <c r="B713" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C713" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D713">
         <v>10000</v>
@@ -25202,10 +25177,10 @@
         <v>11</v>
       </c>
       <c r="B714" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C714" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D714">
         <v>10000</v>
@@ -25231,10 +25206,10 @@
         <v>11</v>
       </c>
       <c r="B715" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C715" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D715">
         <v>10000</v>
@@ -25260,10 +25235,10 @@
         <v>11</v>
       </c>
       <c r="B716" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C716" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D716">
         <v>10000</v>
@@ -25289,10 +25264,10 @@
         <v>11</v>
       </c>
       <c r="B717" t="s">
+        <v>114</v>
+      </c>
+      <c r="C717" t="s">
         <v>112</v>
-      </c>
-      <c r="C717" t="s">
-        <v>114</v>
       </c>
       <c r="D717">
         <v>10000</v>
@@ -25318,10 +25293,10 @@
         <v>11</v>
       </c>
       <c r="B718" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C718" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D718">
         <v>10000</v>
@@ -25347,10 +25322,10 @@
         <v>11</v>
       </c>
       <c r="B719" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="C719" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="D719">
         <v>10000</v>
@@ -25376,10 +25351,10 @@
         <v>11</v>
       </c>
       <c r="B720" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="C720" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D720">
         <v>10000</v>
@@ -25405,10 +25380,10 @@
         <v>11</v>
       </c>
       <c r="B721" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C721" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D721">
         <v>10000</v>
@@ -25434,10 +25409,10 @@
         <v>11</v>
       </c>
       <c r="B722" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C722" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D722">
         <v>10000</v>
@@ -25463,10 +25438,10 @@
         <v>11</v>
       </c>
       <c r="B723" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C723" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D723">
         <v>10000</v>
@@ -25492,10 +25467,10 @@
         <v>11</v>
       </c>
       <c r="B724" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C724" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D724">
         <v>10000</v>
@@ -25521,10 +25496,10 @@
         <v>11</v>
       </c>
       <c r="B725" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C725" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D725">
         <v>10000</v>
@@ -25550,10 +25525,10 @@
         <v>11</v>
       </c>
       <c r="B726" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="C726" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="D726">
         <v>10000</v>
@@ -25579,10 +25554,10 @@
         <v>11</v>
       </c>
       <c r="B727" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C727" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D727">
         <v>10000</v>
@@ -25608,10 +25583,10 @@
         <v>11</v>
       </c>
       <c r="B728" t="s">
+        <v>140</v>
+      </c>
+      <c r="C728" t="s">
         <v>139</v>
-      </c>
-      <c r="C728" t="s">
-        <v>140</v>
       </c>
       <c r="D728">
         <v>10000</v>
@@ -25634,13 +25609,13 @@
     </row>
     <row r="729" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B729" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="C729" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="D729">
         <v>10000</v>
@@ -25649,7 +25624,7 @@
         <v>10000</v>
       </c>
       <c r="F729">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G729">
         <v>10000000</v>
@@ -25666,10 +25641,10 @@
         <v>12</v>
       </c>
       <c r="B730" t="s">
+        <v>97</v>
+      </c>
+      <c r="C730" t="s">
         <v>99</v>
-      </c>
-      <c r="C730" t="s">
-        <v>97</v>
       </c>
       <c r="D730">
         <v>10000</v>
@@ -25695,10 +25670,10 @@
         <v>12</v>
       </c>
       <c r="B731" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C731" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D731">
         <v>10000</v>
@@ -25724,10 +25699,10 @@
         <v>12</v>
       </c>
       <c r="B732" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C732" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D732">
         <v>10000</v>
@@ -25753,10 +25728,10 @@
         <v>12</v>
       </c>
       <c r="B733" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C733" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D733">
         <v>10000</v>
@@ -25782,10 +25757,10 @@
         <v>12</v>
       </c>
       <c r="B734" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C734" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D734">
         <v>10000</v>
@@ -25811,10 +25786,10 @@
         <v>12</v>
       </c>
       <c r="B735" t="s">
+        <v>114</v>
+      </c>
+      <c r="C735" t="s">
         <v>112</v>
-      </c>
-      <c r="C735" t="s">
-        <v>114</v>
       </c>
       <c r="D735">
         <v>10000</v>
@@ -25840,10 +25815,10 @@
         <v>12</v>
       </c>
       <c r="B736" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C736" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D736">
         <v>10000</v>
@@ -25869,10 +25844,10 @@
         <v>12</v>
       </c>
       <c r="B737" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="C737" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="D737">
         <v>10000</v>
@@ -25898,10 +25873,10 @@
         <v>12</v>
       </c>
       <c r="B738" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="C738" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D738">
         <v>10000</v>
@@ -25927,10 +25902,10 @@
         <v>12</v>
       </c>
       <c r="B739" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C739" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D739">
         <v>10000</v>
@@ -25956,10 +25931,10 @@
         <v>12</v>
       </c>
       <c r="B740" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C740" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D740">
         <v>10000</v>
@@ -25985,10 +25960,10 @@
         <v>12</v>
       </c>
       <c r="B741" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C741" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D741">
         <v>10000</v>
@@ -26014,10 +25989,10 @@
         <v>12</v>
       </c>
       <c r="B742" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C742" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D742">
         <v>10000</v>
@@ -26043,10 +26018,10 @@
         <v>12</v>
       </c>
       <c r="B743" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C743" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D743">
         <v>10000</v>
@@ -26072,10 +26047,10 @@
         <v>12</v>
       </c>
       <c r="B744" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="C744" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="D744">
         <v>10000</v>
@@ -26101,10 +26076,10 @@
         <v>12</v>
       </c>
       <c r="B745" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C745" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D745">
         <v>10000</v>
@@ -26130,11 +26105,11 @@
         <v>12</v>
       </c>
       <c r="B746" t="s">
+        <v>140</v>
+      </c>
+      <c r="C746" t="s">
         <v>139</v>
       </c>
-      <c r="C746" t="s">
-        <v>140</v>
-      </c>
       <c r="D746">
         <v>10000</v>
       </c>
@@ -26151,35 +26126,6 @@
         <v>0</v>
       </c>
       <c r="I746">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A747" t="s">
-        <v>12</v>
-      </c>
-      <c r="B747" t="s">
-        <v>140</v>
-      </c>
-      <c r="C747" t="s">
-        <v>139</v>
-      </c>
-      <c r="D747">
-        <v>10000</v>
-      </c>
-      <c r="E747">
-        <v>10000</v>
-      </c>
-      <c r="F747">
-        <v>100</v>
-      </c>
-      <c r="G747">
-        <v>10000000</v>
-      </c>
-      <c r="H747">
-        <v>0</v>
-      </c>
-      <c r="I747">
         <v>1</v>
       </c>
     </row>
@@ -26961,7 +26907,7 @@
         <v>51</v>
       </c>
       <c r="C70">
-        <v>-4429.4341224188802</v>
+        <v>-4137.432887168141</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -26972,7 +26918,7 @@
         <v>72</v>
       </c>
       <c r="C71">
-        <v>-491.80958750000002</v>
+        <v>-7.7179334425266708</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -27005,7 +26951,7 @@
         <v>74</v>
       </c>
       <c r="C74">
-        <v>-2.1757375189927202</v>
+        <v>-7.6856810427436644</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -27016,7 +26962,7 @@
         <v>53</v>
       </c>
       <c r="C75">
-        <v>-35.078727272727299</v>
+        <v>-35.078727272727271</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
@@ -27027,7 +26973,7 @@
         <v>43</v>
       </c>
       <c r="C76">
-        <v>-98.677000000000007</v>
+        <v>-75.228999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -27038,7 +26984,7 @@
         <v>73</v>
       </c>
       <c r="C77">
-        <v>-173.42735646017701</v>
+        <v>-173.42735646017678</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -27049,7 +26995,7 @@
         <v>130</v>
       </c>
       <c r="C78">
-        <v>-1393.6572657239899</v>
+        <v>-1111.0529491422999</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -27995,7 +27941,7 @@
         <v>79</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>-423.52986637499998</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -28072,7 +28018,7 @@
         <v>98</v>
       </c>
       <c r="C171">
-        <v>9035.4222937216473</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -28083,7 +28029,7 @@
         <v>97</v>
       </c>
       <c r="C172">
-        <v>-8660.7846598998203</v>
+        <v>-8153.5498638127028</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -28138,7 +28084,7 @@
         <v>139</v>
       </c>
       <c r="C177">
-        <v>-2132.7907642308801</v>
+        <v>-2027.6204220686873</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -28171,7 +28117,7 @@
         <v>100</v>
       </c>
       <c r="C180">
-        <v>-1438.1396047190799</v>
+        <v>-1303.1657124974754</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -28204,7 +28150,7 @@
         <v>103</v>
       </c>
       <c r="C183">
-        <v>-141.703638160309</v>
+        <v>-148.36377291714354</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -28237,7 +28183,7 @@
         <v>106</v>
       </c>
       <c r="C186">
-        <v>-5212.4455255534303</v>
+        <v>-5026.5112714781217</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
@@ -28270,7 +28216,7 @@
         <v>109</v>
       </c>
       <c r="C189">
-        <v>-431.84687643593901</v>
+        <v>-375.297303107483</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
@@ -28336,7 +28282,7 @@
         <v>115</v>
       </c>
       <c r="C195">
-        <v>-391.98708472127601</v>
+        <v>-413.44041012725421</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -28369,7 +28315,7 @@
         <v>118</v>
       </c>
       <c r="C198">
-        <v>-4002.6213997252298</v>
+        <v>-3288.7505973451316</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -28402,7 +28348,7 @@
         <v>121</v>
       </c>
       <c r="C201">
-        <v>-1489.88099670054</v>
+        <v>-1579.465226022091</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -28435,7 +28381,7 @@
         <v>124</v>
       </c>
       <c r="C204">
-        <v>-611.70270126686103</v>
+        <v>-589.71838532941092</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -28468,7 +28414,7 @@
         <v>127</v>
       </c>
       <c r="C207">
-        <v>-1748.3915086808199</v>
+        <v>-1854.2239789296088</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -28523,7 +28469,7 @@
         <v>131</v>
       </c>
       <c r="C212">
-        <v>-586.63367669240597</v>
+        <v>-569.66841625963582</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
@@ -28556,7 +28502,7 @@
         <v>132</v>
       </c>
       <c r="C215">
-        <v>-894.11611117837504</v>
+        <v>-842.11728647519499</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
@@ -29035,2858 +28981,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9E04D-D9A2-4E10-A943-E70AD7BBD3D4}">
-  <dimension ref="A1:C258"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2">
-        <v>-458.533406625542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6">
-        <v>756.38900431332877</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8">
-        <v>-491.80958750000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>0.55586415</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12">
-        <v>-1748.3915086808199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16">
-        <v>1514.3217349843551</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18">
-        <v>-83.045000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20">
-        <v>7.5617455199999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22">
-        <v>-391.98708472127601</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26">
-        <v>1423.6490345613581</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30">
-        <v>-166.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34">
-        <v>5.7643000000000007E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36">
-        <v>-34.820653312201756</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38">
-        <v>0.53100926999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40">
-        <v>-173.42735646017701</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44">
-        <v>-31.263999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46">
-        <v>-4002.6213997252298</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" t="s">
-        <v>120</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" t="s">
-        <v>119</v>
-      </c>
-      <c r="C50">
-        <v>1895.4700626843651</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" t="s">
-        <v>130</v>
-      </c>
-      <c r="C52">
-        <v>-1393.6572657239899</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" t="s">
-        <v>130</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54">
-        <v>1660.0284595680205</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" t="s">
-        <v>133</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56">
-        <v>-83.045000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58">
-        <v>1.9156527500000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" t="s">
-        <v>40</v>
-      </c>
-      <c r="C60">
-        <v>-845.10500000000002</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" t="s">
-        <v>39</v>
-      </c>
-      <c r="C62">
-        <v>47.618979999999993</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" t="s">
-        <v>38</v>
-      </c>
-      <c r="C64">
-        <v>-29.166899245671924</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" t="s">
-        <v>37</v>
-      </c>
-      <c r="C66">
-        <v>13.947075569999997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" t="s">
-        <v>79</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70">
-        <v>796.255</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s">
-        <v>93</v>
-      </c>
-      <c r="C72">
-        <v>-6.6570737613344075</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" t="s">
-        <v>93</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" t="s">
-        <v>131</v>
-      </c>
-      <c r="C74">
-        <v>-586.63367669240597</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" t="s">
-        <v>131</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76" t="s">
-        <v>135</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" t="s">
-        <v>135</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" t="s">
-        <v>134</v>
-      </c>
-      <c r="C78">
-        <v>571.20475152087397</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>12</v>
-      </c>
-      <c r="B79" t="s">
-        <v>134</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>11</v>
-      </c>
-      <c r="B80" t="s">
-        <v>95</v>
-      </c>
-      <c r="C80">
-        <v>-55.689</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>11</v>
-      </c>
-      <c r="B82" t="s">
-        <v>94</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>12</v>
-      </c>
-      <c r="B83" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>11</v>
-      </c>
-      <c r="B84" t="s">
-        <v>96</v>
-      </c>
-      <c r="C84">
-        <v>6.3309600000000021E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B86" t="s">
-        <v>32</v>
-      </c>
-      <c r="C86">
-        <v>-316.54799999999994</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B87" t="s">
-        <v>32</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>11</v>
-      </c>
-      <c r="B88" t="s">
-        <v>31</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" t="s">
-        <v>31</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90">
-        <v>0.44941999999999999</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>11</v>
-      </c>
-      <c r="B92" t="s">
-        <v>71</v>
-      </c>
-      <c r="C92">
-        <v>-19.54</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" t="s">
-        <v>71</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B94" t="s">
-        <v>18</v>
-      </c>
-      <c r="C94">
-        <v>-397.63900000000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" t="s">
-        <v>18</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>11</v>
-      </c>
-      <c r="B96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>12</v>
-      </c>
-      <c r="B97" t="s">
-        <v>17</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>11</v>
-      </c>
-      <c r="B98" t="s">
-        <v>85</v>
-      </c>
-      <c r="C98">
-        <v>0.16949973000000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>12</v>
-      </c>
-      <c r="B99" t="s">
-        <v>85</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>11</v>
-      </c>
-      <c r="B100" t="s">
-        <v>22</v>
-      </c>
-      <c r="C100">
-        <v>-20.327868125092017</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>12</v>
-      </c>
-      <c r="B101" t="s">
-        <v>22</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>11</v>
-      </c>
-      <c r="B102" t="s">
-        <v>21</v>
-      </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>12</v>
-      </c>
-      <c r="B103" t="s">
-        <v>21</v>
-      </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>11</v>
-      </c>
-      <c r="B104" t="s">
-        <v>83</v>
-      </c>
-      <c r="C104">
-        <v>8.6795214499999993</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>12</v>
-      </c>
-      <c r="B105" t="s">
-        <v>83</v>
-      </c>
-      <c r="C105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>11</v>
-      </c>
-      <c r="B106" t="s">
-        <v>64</v>
-      </c>
-      <c r="C106">
-        <v>-99.653999999999982</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107" t="s">
-        <v>64</v>
-      </c>
-      <c r="C107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>11</v>
-      </c>
-      <c r="B108" t="s">
-        <v>86</v>
-      </c>
-      <c r="C108">
-        <v>16.46245</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>11</v>
-      </c>
-      <c r="B110" t="s">
-        <v>57</v>
-      </c>
-      <c r="C110">
-        <v>-24.864095362311311</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>12</v>
-      </c>
-      <c r="B111" t="s">
-        <v>57</v>
-      </c>
-      <c r="C111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>11</v>
-      </c>
-      <c r="B112" t="s">
-        <v>87</v>
-      </c>
-      <c r="C112">
-        <v>19.829690269999997</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>12</v>
-      </c>
-      <c r="B113" t="s">
-        <v>87</v>
-      </c>
-      <c r="C113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>11</v>
-      </c>
-      <c r="B114" t="s">
-        <v>132</v>
-      </c>
-      <c r="C114">
-        <v>-894.11611117837504</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>12</v>
-      </c>
-      <c r="B115" t="s">
-        <v>132</v>
-      </c>
-      <c r="C115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>11</v>
-      </c>
-      <c r="B116" t="s">
-        <v>136</v>
-      </c>
-      <c r="C116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>12</v>
-      </c>
-      <c r="B117" t="s">
-        <v>136</v>
-      </c>
-      <c r="C117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>11</v>
-      </c>
-      <c r="B118" t="s">
-        <v>138</v>
-      </c>
-      <c r="C118">
-        <v>1346.2104383089134</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>12</v>
-      </c>
-      <c r="B119" t="s">
-        <v>138</v>
-      </c>
-      <c r="C119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>11</v>
-      </c>
-      <c r="B120" t="s">
-        <v>124</v>
-      </c>
-      <c r="C120">
-        <v>-611.70270126686103</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>12</v>
-      </c>
-      <c r="B121" t="s">
-        <v>124</v>
-      </c>
-      <c r="C121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>11</v>
-      </c>
-      <c r="B122" t="s">
-        <v>126</v>
-      </c>
-      <c r="C122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>12</v>
-      </c>
-      <c r="B123" t="s">
-        <v>126</v>
-      </c>
-      <c r="C123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>11</v>
-      </c>
-      <c r="B124" t="s">
-        <v>125</v>
-      </c>
-      <c r="C124">
-        <v>232.14132144332223</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>12</v>
-      </c>
-      <c r="B125" t="s">
-        <v>125</v>
-      </c>
-      <c r="C125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>11</v>
-      </c>
-      <c r="B126" t="s">
-        <v>20</v>
-      </c>
-      <c r="C126">
-        <v>-661.42899999999997</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>12</v>
-      </c>
-      <c r="B127" t="s">
-        <v>20</v>
-      </c>
-      <c r="C127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>11</v>
-      </c>
-      <c r="B128" t="s">
-        <v>19</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129" t="s">
-        <v>19</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>11</v>
-      </c>
-      <c r="B130" t="s">
-        <v>41</v>
-      </c>
-      <c r="C130">
-        <v>38.415639999999996</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>12</v>
-      </c>
-      <c r="B131" t="s">
-        <v>41</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>11</v>
-      </c>
-      <c r="B132" t="s">
-        <v>121</v>
-      </c>
-      <c r="C132">
-        <v>-1489.88099670054</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>12</v>
-      </c>
-      <c r="B133" t="s">
-        <v>121</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>11</v>
-      </c>
-      <c r="B134" t="s">
-        <v>123</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>12</v>
-      </c>
-      <c r="B135" t="s">
-        <v>123</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>11</v>
-      </c>
-      <c r="B136" t="s">
-        <v>122</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>12</v>
-      </c>
-      <c r="B137" t="s">
-        <v>122</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>11</v>
-      </c>
-      <c r="B138" t="s">
-        <v>24</v>
-      </c>
-      <c r="C138">
-        <v>-13.995883970311864</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>12</v>
-      </c>
-      <c r="B139" t="s">
-        <v>24</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>11</v>
-      </c>
-      <c r="B140" t="s">
-        <v>23</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>12</v>
-      </c>
-      <c r="B141" t="s">
-        <v>23</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>11</v>
-      </c>
-      <c r="B142" t="s">
-        <v>61</v>
-      </c>
-      <c r="C142">
-        <v>-3.1361880225518983</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>12</v>
-      </c>
-      <c r="B143" t="s">
-        <v>61</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>11</v>
-      </c>
-      <c r="B144" t="s">
-        <v>70</v>
-      </c>
-      <c r="C144">
-        <v>-9.5558311621502252</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>12</v>
-      </c>
-      <c r="B145" t="s">
-        <v>70</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>11</v>
-      </c>
-      <c r="B146" t="s">
-        <v>43</v>
-      </c>
-      <c r="C146">
-        <v>-98.677000000000007</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>12</v>
-      </c>
-      <c r="B147" t="s">
-        <v>43</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>11</v>
-      </c>
-      <c r="B148" t="s">
-        <v>42</v>
-      </c>
-      <c r="C148">
-        <v>129.941</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>12</v>
-      </c>
-      <c r="B149" t="s">
-        <v>42</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>11</v>
-      </c>
-      <c r="B150" t="s">
-        <v>74</v>
-      </c>
-      <c r="C150">
-        <v>-2.1757375189927202</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>12</v>
-      </c>
-      <c r="B151" t="s">
-        <v>74</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>11</v>
-      </c>
-      <c r="B152" t="s">
-        <v>75</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>12</v>
-      </c>
-      <c r="B153" t="s">
-        <v>75</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>11</v>
-      </c>
-      <c r="B154" t="s">
-        <v>69</v>
-      </c>
-      <c r="C154">
-        <v>-12.918429819775348</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>12</v>
-      </c>
-      <c r="B155" t="s">
-        <v>69</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>11</v>
-      </c>
-      <c r="B156" t="s">
-        <v>106</v>
-      </c>
-      <c r="C156">
-        <v>-5212.4455255534303</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>12</v>
-      </c>
-      <c r="B157" t="s">
-        <v>106</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>11</v>
-      </c>
-      <c r="B158" t="s">
-        <v>108</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>12</v>
-      </c>
-      <c r="B159" t="s">
-        <v>108</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>11</v>
-      </c>
-      <c r="B160" t="s">
-        <v>107</v>
-      </c>
-      <c r="C160">
-        <v>4816.6543745027893</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>12</v>
-      </c>
-      <c r="B161" t="s">
-        <v>107</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>11</v>
-      </c>
-      <c r="B162" t="s">
-        <v>68</v>
-      </c>
-      <c r="C162">
-        <v>-10.40036286731274</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>12</v>
-      </c>
-      <c r="B163" t="s">
-        <v>68</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>11</v>
-      </c>
-      <c r="B164" t="s">
-        <v>139</v>
-      </c>
-      <c r="C164">
-        <v>-2132.7907642308801</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>12</v>
-      </c>
-      <c r="B165" t="s">
-        <v>139</v>
-      </c>
-      <c r="C165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>11</v>
-      </c>
-      <c r="B166" t="s">
-        <v>140</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>12</v>
-      </c>
-      <c r="B167" t="s">
-        <v>140</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>11</v>
-      </c>
-      <c r="B168" t="s">
-        <v>141</v>
-      </c>
-      <c r="C168">
-        <v>1965.121004492735</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>12</v>
-      </c>
-      <c r="B169" t="s">
-        <v>142</v>
-      </c>
-      <c r="C169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>11</v>
-      </c>
-      <c r="B170" t="s">
-        <v>26</v>
-      </c>
-      <c r="C170">
-        <v>-357.58199999999999</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>12</v>
-      </c>
-      <c r="B171" t="s">
-        <v>26</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>11</v>
-      </c>
-      <c r="B172" t="s">
-        <v>25</v>
-      </c>
-      <c r="C172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>12</v>
-      </c>
-      <c r="B173" t="s">
-        <v>25</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>11</v>
-      </c>
-      <c r="B174" t="s">
-        <v>44</v>
-      </c>
-      <c r="C174">
-        <v>234.14902171</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>12</v>
-      </c>
-      <c r="B175" t="s">
-        <v>44</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>11</v>
-      </c>
-      <c r="B176" t="s">
-        <v>46</v>
-      </c>
-      <c r="C176">
-        <v>-42.988</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>12</v>
-      </c>
-      <c r="B177" t="s">
-        <v>46</v>
-      </c>
-      <c r="C177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>11</v>
-      </c>
-      <c r="B178" t="s">
-        <v>45</v>
-      </c>
-      <c r="C178">
-        <v>1135.3337630899998</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>12</v>
-      </c>
-      <c r="B179" t="s">
-        <v>45</v>
-      </c>
-      <c r="C179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>11</v>
-      </c>
-      <c r="B180" t="s">
-        <v>28</v>
-      </c>
-      <c r="C180">
-        <v>-211.03200000000001</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>12</v>
-      </c>
-      <c r="B181" t="s">
-        <v>28</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>11</v>
-      </c>
-      <c r="B182" t="s">
-        <v>27</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>12</v>
-      </c>
-      <c r="B183" t="s">
-        <v>27</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>11</v>
-      </c>
-      <c r="B184" t="s">
-        <v>47</v>
-      </c>
-      <c r="C184">
-        <v>54.642437600000001</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>12</v>
-      </c>
-      <c r="B185" t="s">
-        <v>47</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>11</v>
-      </c>
-      <c r="B186" t="s">
-        <v>30</v>
-      </c>
-      <c r="C186">
-        <v>-58.62</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>12</v>
-      </c>
-      <c r="B187" t="s">
-        <v>30</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>11</v>
-      </c>
-      <c r="B188" t="s">
-        <v>29</v>
-      </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>12</v>
-      </c>
-      <c r="B189" t="s">
-        <v>29</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>11</v>
-      </c>
-      <c r="B190" t="s">
-        <v>109</v>
-      </c>
-      <c r="C190">
-        <v>-431.84687643593901</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>12</v>
-      </c>
-      <c r="B191" t="s">
-        <v>109</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
-        <v>11</v>
-      </c>
-      <c r="B192" t="s">
-        <v>111</v>
-      </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>12</v>
-      </c>
-      <c r="B193" t="s">
-        <v>111</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
-        <v>11</v>
-      </c>
-      <c r="B194" t="s">
-        <v>110</v>
-      </c>
-      <c r="C194">
-        <v>1709.1133654740438</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>12</v>
-      </c>
-      <c r="B195" t="s">
-        <v>110</v>
-      </c>
-      <c r="C195">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>11</v>
-      </c>
-      <c r="B196" t="s">
-        <v>49</v>
-      </c>
-      <c r="C196">
-        <v>-110.401</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
-        <v>12</v>
-      </c>
-      <c r="B197" t="s">
-        <v>49</v>
-      </c>
-      <c r="C197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
-        <v>11</v>
-      </c>
-      <c r="B198" t="s">
-        <v>48</v>
-      </c>
-      <c r="C198">
-        <v>88.09608999999999</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
-        <v>12</v>
-      </c>
-      <c r="B199" t="s">
-        <v>48</v>
-      </c>
-      <c r="C199">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
-        <v>11</v>
-      </c>
-      <c r="B200" t="s">
-        <v>65</v>
-      </c>
-      <c r="C200">
-        <v>-34.696428008002286</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>12</v>
-      </c>
-      <c r="B201" t="s">
-        <v>65</v>
-      </c>
-      <c r="C201">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>11</v>
-      </c>
-      <c r="B202" t="s">
-        <v>88</v>
-      </c>
-      <c r="C202">
-        <v>3.9959299999999995</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>12</v>
-      </c>
-      <c r="B203" t="s">
-        <v>88</v>
-      </c>
-      <c r="C203">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
-        <v>11</v>
-      </c>
-      <c r="B204" t="s">
-        <v>51</v>
-      </c>
-      <c r="C204">
-        <v>-4429.4341224188802</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
-        <v>12</v>
-      </c>
-      <c r="B205" t="s">
-        <v>51</v>
-      </c>
-      <c r="C205">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>11</v>
-      </c>
-      <c r="B206" t="s">
-        <v>137</v>
-      </c>
-      <c r="C206">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>12</v>
-      </c>
-      <c r="B207" t="s">
-        <v>137</v>
-      </c>
-      <c r="C207">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
-        <v>11</v>
-      </c>
-      <c r="B208" t="s">
-        <v>50</v>
-      </c>
-      <c r="C208">
-        <v>6237.6238294370169</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
-        <v>12</v>
-      </c>
-      <c r="B209" t="s">
-        <v>50</v>
-      </c>
-      <c r="C209">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
-        <v>11</v>
-      </c>
-      <c r="B210" t="s">
-        <v>100</v>
-      </c>
-      <c r="C210">
-        <v>-1438.1396047190799</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>12</v>
-      </c>
-      <c r="B211" t="s">
-        <v>100</v>
-      </c>
-      <c r="C211">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
-        <v>11</v>
-      </c>
-      <c r="B212" t="s">
-        <v>102</v>
-      </c>
-      <c r="C212">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A213" t="s">
-        <v>12</v>
-      </c>
-      <c r="B213" t="s">
-        <v>102</v>
-      </c>
-      <c r="C213">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
-        <v>11</v>
-      </c>
-      <c r="B214" t="s">
-        <v>101</v>
-      </c>
-      <c r="C214">
-        <v>1242.2934195982448</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
-        <v>12</v>
-      </c>
-      <c r="B215" t="s">
-        <v>101</v>
-      </c>
-      <c r="C215">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
-        <v>11</v>
-      </c>
-      <c r="B216" t="s">
-        <v>76</v>
-      </c>
-      <c r="C216">
-        <v>-10.747</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
-        <v>12</v>
-      </c>
-      <c r="B217" t="s">
-        <v>76</v>
-      </c>
-      <c r="C217">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
-        <v>12</v>
-      </c>
-      <c r="B218" t="s">
-        <v>76</v>
-      </c>
-      <c r="C218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
-        <v>11</v>
-      </c>
-      <c r="B219" t="s">
-        <v>62</v>
-      </c>
-      <c r="C219">
-        <v>-10.498540930309094</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>12</v>
-      </c>
-      <c r="B220" t="s">
-        <v>62</v>
-      </c>
-      <c r="C220">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
-        <v>11</v>
-      </c>
-      <c r="B221" t="s">
-        <v>90</v>
-      </c>
-      <c r="C221">
-        <v>5.2113180000000002E-2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>12</v>
-      </c>
-      <c r="B222" t="s">
-        <v>90</v>
-      </c>
-      <c r="C222">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>11</v>
-      </c>
-      <c r="B223" t="s">
-        <v>63</v>
-      </c>
-      <c r="C223">
-        <v>-27.339084185091842</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>12</v>
-      </c>
-      <c r="B224" t="s">
-        <v>63</v>
-      </c>
-      <c r="C224">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
-        <v>11</v>
-      </c>
-      <c r="B225" t="s">
-        <v>89</v>
-      </c>
-      <c r="C225">
-        <v>0.6516687699999999</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>12</v>
-      </c>
-      <c r="B226" t="s">
-        <v>89</v>
-      </c>
-      <c r="C226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>11</v>
-      </c>
-      <c r="B227" t="s">
-        <v>53</v>
-      </c>
-      <c r="C227">
-        <v>-35.078727272727299</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
-        <v>12</v>
-      </c>
-      <c r="B228" t="s">
-        <v>53</v>
-      </c>
-      <c r="C228">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
-        <v>11</v>
-      </c>
-      <c r="B229" t="s">
-        <v>52</v>
-      </c>
-      <c r="C229">
-        <v>18.562999999999999</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
-        <v>12</v>
-      </c>
-      <c r="B230" t="s">
-        <v>52</v>
-      </c>
-      <c r="C230">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
-        <v>11</v>
-      </c>
-      <c r="B231" t="s">
-        <v>34</v>
-      </c>
-      <c r="C231">
-        <v>-453.32799999999997</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
-        <v>12</v>
-      </c>
-      <c r="B232" t="s">
-        <v>34</v>
-      </c>
-      <c r="C232">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
-        <v>11</v>
-      </c>
-      <c r="B233" t="s">
-        <v>33</v>
-      </c>
-      <c r="C233">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
-        <v>12</v>
-      </c>
-      <c r="B234" t="s">
-        <v>33</v>
-      </c>
-      <c r="C234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
-        <v>11</v>
-      </c>
-      <c r="B235" t="s">
-        <v>91</v>
-      </c>
-      <c r="C235">
-        <v>4.2744726999999996</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
-        <v>12</v>
-      </c>
-      <c r="B236" t="s">
-        <v>91</v>
-      </c>
-      <c r="C236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
-        <v>11</v>
-      </c>
-      <c r="B237" t="s">
-        <v>103</v>
-      </c>
-      <c r="C237">
-        <v>-141.703638160309</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A238" t="s">
-        <v>12</v>
-      </c>
-      <c r="B238" t="s">
-        <v>103</v>
-      </c>
-      <c r="C238">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
-        <v>11</v>
-      </c>
-      <c r="B239" t="s">
-        <v>105</v>
-      </c>
-      <c r="C239">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A240" t="s">
-        <v>12</v>
-      </c>
-      <c r="B240" t="s">
-        <v>105</v>
-      </c>
-      <c r="C240">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A241" t="s">
-        <v>11</v>
-      </c>
-      <c r="B241" t="s">
-        <v>104</v>
-      </c>
-      <c r="C241">
-        <v>287.87563085858676</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
-        <v>12</v>
-      </c>
-      <c r="B242" t="s">
-        <v>104</v>
-      </c>
-      <c r="C242">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A243" t="s">
-        <v>11</v>
-      </c>
-      <c r="B243" t="s">
-        <v>56</v>
-      </c>
-      <c r="C243">
-        <v>-286.26099999999997</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
-        <v>12</v>
-      </c>
-      <c r="B244" t="s">
-        <v>56</v>
-      </c>
-      <c r="C244">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A245" t="s">
-        <v>11</v>
-      </c>
-      <c r="B245" t="s">
-        <v>55</v>
-      </c>
-      <c r="C245">
-        <v>190.67131999999998</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
-        <v>12</v>
-      </c>
-      <c r="B246" t="s">
-        <v>55</v>
-      </c>
-      <c r="C246">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
-        <v>11</v>
-      </c>
-      <c r="B247" t="s">
-        <v>36</v>
-      </c>
-      <c r="C247">
-        <v>-708.32499999999993</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A248" t="s">
-        <v>12</v>
-      </c>
-      <c r="B248" t="s">
-        <v>36</v>
-      </c>
-      <c r="C248">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
-        <v>11</v>
-      </c>
-      <c r="B249" t="s">
-        <v>35</v>
-      </c>
-      <c r="C249">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
-        <v>12</v>
-      </c>
-      <c r="B250" t="s">
-        <v>35</v>
-      </c>
-      <c r="C250">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
-        <v>11</v>
-      </c>
-      <c r="B251" t="s">
-        <v>54</v>
-      </c>
-      <c r="C251">
-        <v>320.81311303999996</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
-        <v>12</v>
-      </c>
-      <c r="B252" t="s">
-        <v>54</v>
-      </c>
-      <c r="C252">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
-        <v>11</v>
-      </c>
-      <c r="B253" t="s">
-        <v>97</v>
-      </c>
-      <c r="C253">
-        <v>-8660.7846598998203</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
-        <v>12</v>
-      </c>
-      <c r="B254" t="s">
-        <v>97</v>
-      </c>
-      <c r="C254">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
-        <v>11</v>
-      </c>
-      <c r="B255" t="s">
-        <v>99</v>
-      </c>
-      <c r="C255">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
-        <v>12</v>
-      </c>
-      <c r="B256" t="s">
-        <v>99</v>
-      </c>
-      <c r="C256">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
-        <v>11</v>
-      </c>
-      <c r="B257" t="s">
-        <v>98</v>
-      </c>
-      <c r="C257">
-        <v>9035.4222937216473</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
-        <v>12</v>
-      </c>
-      <c r="B258" t="s">
-        <v>98</v>
-      </c>
-      <c r="C258">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0A911C-4B9C-4937-A18E-1EF9B0FF13A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30414A4-E9C6-4B7B-99D2-B2CD988D8B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-5070" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3635" uniqueCount="142">
   <si>
     <t>Commodities</t>
   </si>
@@ -1506,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3703,18 +3703,18 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B275" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="B276" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -3722,7 +3722,7 @@
         <v>137</v>
       </c>
       <c r="B277" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -3730,7 +3730,7 @@
         <v>137</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -3738,7 +3738,7 @@
         <v>137</v>
       </c>
       <c r="B279" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -3746,7 +3746,7 @@
         <v>137</v>
       </c>
       <c r="B280" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -3754,7 +3754,7 @@
         <v>137</v>
       </c>
       <c r="B281" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -3762,7 +3762,7 @@
         <v>137</v>
       </c>
       <c r="B282" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -3770,7 +3770,7 @@
         <v>137</v>
       </c>
       <c r="B283" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -3778,7 +3778,7 @@
         <v>137</v>
       </c>
       <c r="B284" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -3786,7 +3786,7 @@
         <v>137</v>
       </c>
       <c r="B285" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -3794,7 +3794,7 @@
         <v>137</v>
       </c>
       <c r="B286" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -3802,7 +3802,7 @@
         <v>137</v>
       </c>
       <c r="B287" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -3810,7 +3810,7 @@
         <v>137</v>
       </c>
       <c r="B288" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -3818,7 +3818,7 @@
         <v>137</v>
       </c>
       <c r="B289" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -3826,7 +3826,7 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -3834,7 +3834,7 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -3842,7 +3842,7 @@
         <v>137</v>
       </c>
       <c r="B292" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -3850,7 +3850,7 @@
         <v>137</v>
       </c>
       <c r="B293" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -3858,7 +3858,7 @@
         <v>137</v>
       </c>
       <c r="B294" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -3866,31 +3866,31 @@
         <v>137</v>
       </c>
       <c r="B295" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B296" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B297" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B298" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -3898,7 +3898,7 @@
         <v>135</v>
       </c>
       <c r="B299" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -3906,7 +3906,7 @@
         <v>135</v>
       </c>
       <c r="B300" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -3914,7 +3914,7 @@
         <v>135</v>
       </c>
       <c r="B301" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -3922,7 +3922,7 @@
         <v>135</v>
       </c>
       <c r="B302" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -3930,7 +3930,7 @@
         <v>135</v>
       </c>
       <c r="B303" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -3938,7 +3938,7 @@
         <v>135</v>
       </c>
       <c r="B304" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -3946,7 +3946,7 @@
         <v>135</v>
       </c>
       <c r="B305" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -3954,7 +3954,7 @@
         <v>135</v>
       </c>
       <c r="B306" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -3962,7 +3962,7 @@
         <v>135</v>
       </c>
       <c r="B307" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -3970,7 +3970,7 @@
         <v>135</v>
       </c>
       <c r="B308" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -3978,7 +3978,7 @@
         <v>135</v>
       </c>
       <c r="B309" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -3986,7 +3986,7 @@
         <v>135</v>
       </c>
       <c r="B310" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -3994,7 +3994,7 @@
         <v>135</v>
       </c>
       <c r="B311" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -4002,7 +4002,7 @@
         <v>135</v>
       </c>
       <c r="B312" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -4010,7 +4010,7 @@
         <v>135</v>
       </c>
       <c r="B313" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -4018,7 +4018,7 @@
         <v>135</v>
       </c>
       <c r="B314" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -4026,7 +4026,7 @@
         <v>135</v>
       </c>
       <c r="B315" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -4034,31 +4034,31 @@
         <v>135</v>
       </c>
       <c r="B316" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B317" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B318" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B319" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -4066,7 +4066,7 @@
         <v>136</v>
       </c>
       <c r="B320" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -4074,7 +4074,7 @@
         <v>136</v>
       </c>
       <c r="B321" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
@@ -4082,7 +4082,7 @@
         <v>136</v>
       </c>
       <c r="B322" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -4090,7 +4090,7 @@
         <v>136</v>
       </c>
       <c r="B323" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -4098,7 +4098,7 @@
         <v>136</v>
       </c>
       <c r="B324" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -4106,7 +4106,7 @@
         <v>136</v>
       </c>
       <c r="B325" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -4114,7 +4114,7 @@
         <v>136</v>
       </c>
       <c r="B326" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -4122,7 +4122,7 @@
         <v>136</v>
       </c>
       <c r="B327" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -4130,7 +4130,7 @@
         <v>136</v>
       </c>
       <c r="B328" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -4138,7 +4138,7 @@
         <v>136</v>
       </c>
       <c r="B329" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -4146,7 +4146,7 @@
         <v>136</v>
       </c>
       <c r="B330" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -4154,7 +4154,7 @@
         <v>136</v>
       </c>
       <c r="B331" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -4162,7 +4162,7 @@
         <v>136</v>
       </c>
       <c r="B332" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -4170,7 +4170,7 @@
         <v>136</v>
       </c>
       <c r="B333" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -4178,7 +4178,7 @@
         <v>136</v>
       </c>
       <c r="B334" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -4186,7 +4186,7 @@
         <v>136</v>
       </c>
       <c r="B335" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -4194,7 +4194,7 @@
         <v>136</v>
       </c>
       <c r="B336" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -4202,7 +4202,7 @@
         <v>136</v>
       </c>
       <c r="B337" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
@@ -4210,52 +4210,52 @@
         <v>136</v>
       </c>
       <c r="B338" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="B339" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
+        <v>139</v>
+      </c>
+      <c r="B340" t="s">
         <v>97</v>
-      </c>
-      <c r="B340" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="B341" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
+        <v>109</v>
+      </c>
+      <c r="B342" t="s">
         <v>106</v>
-      </c>
-      <c r="B342" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="B343" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="B344" t="s">
         <v>118</v>
@@ -4263,7 +4263,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B345" t="s">
         <v>118</v>
@@ -4271,217 +4271,209 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="B346" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="B347" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B348" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B349" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B350" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B351" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B352" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B353" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="B354" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B355" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
+        <v>97</v>
+      </c>
+      <c r="B356" t="s">
         <v>99</v>
-      </c>
-      <c r="B356" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B357" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B358" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B359" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
+        <v>114</v>
+      </c>
+      <c r="B360" t="s">
         <v>112</v>
-      </c>
-      <c r="B360" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B361" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="B362" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="B363" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B364" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B365" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B366" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B367" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B368" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="B369" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B370" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B371" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A372" t="s">
-        <v>140</v>
-      </c>
-      <c r="B372" t="s">
         <v>139</v>
       </c>
     </row>
@@ -7470,7 +7462,7 @@
         <v>41.683</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G103">
         <v>10000000</v>
@@ -7528,7 +7520,7 @@
         <v>31.024999999999999</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G105">
         <v>10000000</v>
@@ -12800,10 +12792,10 @@
         <v>97</v>
       </c>
       <c r="D287">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E287">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F287">
         <v>1</v>
@@ -25125,10 +25117,10 @@
         <v>99</v>
       </c>
       <c r="D712">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E712">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F712">
         <v>1</v>
@@ -25212,10 +25204,10 @@
         <v>111</v>
       </c>
       <c r="D715">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E715">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F715">
         <v>1</v>
@@ -25299,10 +25291,10 @@
         <v>117</v>
       </c>
       <c r="D718">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E718">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F718">
         <v>1</v>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30414A4-E9C6-4B7B-99D2-B2CD988D8B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC617E2-61F9-4316-B75B-582595AA4FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5070" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3635" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="142">
   <si>
     <t>Commodities</t>
   </si>
@@ -3482,7 +3482,7 @@
         <v>114</v>
       </c>
       <c r="B247" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -3490,7 +3490,7 @@
         <v>114</v>
       </c>
       <c r="B248" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -3498,7 +3498,7 @@
         <v>114</v>
       </c>
       <c r="B249" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -3506,7 +3506,7 @@
         <v>114</v>
       </c>
       <c r="B250" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -3514,31 +3514,31 @@
         <v>114</v>
       </c>
       <c r="B251" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B252" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B253" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B254" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -3546,7 +3546,7 @@
         <v>117</v>
       </c>
       <c r="B255" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -3554,7 +3554,7 @@
         <v>117</v>
       </c>
       <c r="B256" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -3562,7 +3562,7 @@
         <v>117</v>
       </c>
       <c r="B257" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -3570,7 +3570,7 @@
         <v>117</v>
       </c>
       <c r="B258" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -3578,7 +3578,7 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -3586,7 +3586,7 @@
         <v>117</v>
       </c>
       <c r="B260" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -3594,7 +3594,7 @@
         <v>117</v>
       </c>
       <c r="B261" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -3602,7 +3602,7 @@
         <v>117</v>
       </c>
       <c r="B262" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -3610,7 +3610,7 @@
         <v>117</v>
       </c>
       <c r="B263" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -3618,7 +3618,7 @@
         <v>117</v>
       </c>
       <c r="B264" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -3626,7 +3626,7 @@
         <v>117</v>
       </c>
       <c r="B265" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -3634,7 +3634,7 @@
         <v>117</v>
       </c>
       <c r="B266" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -3642,7 +3642,7 @@
         <v>117</v>
       </c>
       <c r="B267" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -3650,7 +3650,7 @@
         <v>117</v>
       </c>
       <c r="B268" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -3658,7 +3658,7 @@
         <v>117</v>
       </c>
       <c r="B269" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -3666,7 +3666,7 @@
         <v>117</v>
       </c>
       <c r="B270" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -3674,7 +3674,7 @@
         <v>117</v>
       </c>
       <c r="B271" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -3682,7 +3682,7 @@
         <v>117</v>
       </c>
       <c r="B272" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -3690,23 +3690,23 @@
         <v>117</v>
       </c>
       <c r="B273" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="B274" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="B275" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -3714,7 +3714,7 @@
         <v>137</v>
       </c>
       <c r="B276" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -3722,7 +3722,7 @@
         <v>137</v>
       </c>
       <c r="B277" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -3730,7 +3730,7 @@
         <v>137</v>
       </c>
       <c r="B278" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -3738,7 +3738,7 @@
         <v>137</v>
       </c>
       <c r="B279" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -3746,7 +3746,7 @@
         <v>137</v>
       </c>
       <c r="B280" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -3754,7 +3754,7 @@
         <v>137</v>
       </c>
       <c r="B281" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -3762,7 +3762,7 @@
         <v>137</v>
       </c>
       <c r="B282" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -3770,7 +3770,7 @@
         <v>137</v>
       </c>
       <c r="B283" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -3778,7 +3778,7 @@
         <v>137</v>
       </c>
       <c r="B284" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -3786,7 +3786,7 @@
         <v>137</v>
       </c>
       <c r="B285" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -3794,7 +3794,7 @@
         <v>137</v>
       </c>
       <c r="B286" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -3802,7 +3802,7 @@
         <v>137</v>
       </c>
       <c r="B287" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -3810,7 +3810,7 @@
         <v>137</v>
       </c>
       <c r="B288" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -3818,7 +3818,7 @@
         <v>137</v>
       </c>
       <c r="B289" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -3826,7 +3826,7 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -3834,7 +3834,7 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -3842,7 +3842,7 @@
         <v>137</v>
       </c>
       <c r="B292" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -3850,7 +3850,7 @@
         <v>137</v>
       </c>
       <c r="B293" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -3858,31 +3858,31 @@
         <v>137</v>
       </c>
       <c r="B294" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B295" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B296" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B297" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -3890,7 +3890,7 @@
         <v>135</v>
       </c>
       <c r="B298" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -3898,7 +3898,7 @@
         <v>135</v>
       </c>
       <c r="B299" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -3906,7 +3906,7 @@
         <v>135</v>
       </c>
       <c r="B300" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -3914,7 +3914,7 @@
         <v>135</v>
       </c>
       <c r="B301" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -3922,7 +3922,7 @@
         <v>135</v>
       </c>
       <c r="B302" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -3930,7 +3930,7 @@
         <v>135</v>
       </c>
       <c r="B303" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -3938,7 +3938,7 @@
         <v>135</v>
       </c>
       <c r="B304" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -3946,7 +3946,7 @@
         <v>135</v>
       </c>
       <c r="B305" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -3954,7 +3954,7 @@
         <v>135</v>
       </c>
       <c r="B306" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -3962,7 +3962,7 @@
         <v>135</v>
       </c>
       <c r="B307" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -3970,7 +3970,7 @@
         <v>135</v>
       </c>
       <c r="B308" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -3978,7 +3978,7 @@
         <v>135</v>
       </c>
       <c r="B309" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -3986,7 +3986,7 @@
         <v>135</v>
       </c>
       <c r="B310" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -3994,7 +3994,7 @@
         <v>135</v>
       </c>
       <c r="B311" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -4002,7 +4002,7 @@
         <v>135</v>
       </c>
       <c r="B312" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -4010,7 +4010,7 @@
         <v>135</v>
       </c>
       <c r="B313" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -4018,7 +4018,7 @@
         <v>135</v>
       </c>
       <c r="B314" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -4026,31 +4026,31 @@
         <v>135</v>
       </c>
       <c r="B315" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B316" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B317" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B318" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -4058,7 +4058,7 @@
         <v>136</v>
       </c>
       <c r="B319" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -4066,7 +4066,7 @@
         <v>136</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -4074,7 +4074,7 @@
         <v>136</v>
       </c>
       <c r="B321" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
@@ -4082,7 +4082,7 @@
         <v>136</v>
       </c>
       <c r="B322" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -4090,7 +4090,7 @@
         <v>136</v>
       </c>
       <c r="B323" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -4098,7 +4098,7 @@
         <v>136</v>
       </c>
       <c r="B324" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -4106,7 +4106,7 @@
         <v>136</v>
       </c>
       <c r="B325" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -4114,7 +4114,7 @@
         <v>136</v>
       </c>
       <c r="B326" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -4122,7 +4122,7 @@
         <v>136</v>
       </c>
       <c r="B327" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -4130,7 +4130,7 @@
         <v>136</v>
       </c>
       <c r="B328" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -4138,7 +4138,7 @@
         <v>136</v>
       </c>
       <c r="B329" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -4146,7 +4146,7 @@
         <v>136</v>
       </c>
       <c r="B330" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -4154,7 +4154,7 @@
         <v>136</v>
       </c>
       <c r="B331" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -4162,7 +4162,7 @@
         <v>136</v>
       </c>
       <c r="B332" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -4170,7 +4170,7 @@
         <v>136</v>
       </c>
       <c r="B333" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -4178,7 +4178,7 @@
         <v>136</v>
       </c>
       <c r="B334" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -4186,7 +4186,7 @@
         <v>136</v>
       </c>
       <c r="B335" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -4194,7 +4194,7 @@
         <v>136</v>
       </c>
       <c r="B336" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -4202,52 +4202,52 @@
         <v>136</v>
       </c>
       <c r="B337" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="B338" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
+        <v>139</v>
+      </c>
+      <c r="B339" t="s">
         <v>97</v>
-      </c>
-      <c r="B339" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="B340" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
+        <v>109</v>
+      </c>
+      <c r="B341" t="s">
         <v>106</v>
-      </c>
-      <c r="B341" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="B342" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="B343" t="s">
         <v>118</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B344" t="s">
         <v>118</v>
@@ -4263,218 +4263,218 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="B345" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="B346" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B347" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B348" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B349" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B350" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B351" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B352" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="B353" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B354" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
+        <v>97</v>
+      </c>
+      <c r="B355" t="s">
         <v>99</v>
-      </c>
-      <c r="B355" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B356" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B357" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B358" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
+        <v>114</v>
+      </c>
+      <c r="B359" t="s">
         <v>112</v>
-      </c>
-      <c r="B359" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B360" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="B361" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="B362" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B363" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B364" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B365" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B366" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B367" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="B368" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B369" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
+        <v>140</v>
+      </c>
+      <c r="B370" t="s">
         <v>139</v>
-      </c>
-      <c r="B370" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="B371" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4484,7 +4484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I746"/>
+  <dimension ref="A1:I736"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -4533,7 +4533,7 @@
         <v>111.378</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G2">
         <v>10000000</v>
@@ -4562,7 +4562,7 @@
         <v>322.40999999999997</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G3">
         <v>10000000</v>
@@ -4591,7 +4591,7 @@
         <v>73.274999999999991</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G4">
         <v>10000000</v>
@@ -4620,7 +4620,7 @@
         <v>155.83149999999998</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G5">
         <v>10000000</v>
@@ -4649,7 +4649,7 @@
         <v>25.402000000000001</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G6">
         <v>10000000</v>
@@ -4678,7 +4678,7 @@
         <v>39.08</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G7">
         <v>10000000</v>
@@ -4707,7 +4707,7 @@
         <v>122.125</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G8">
         <v>10000000</v>
@@ -4736,7 +4736,7 @@
         <v>60.573999999999998</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G9">
         <v>10000000</v>
@@ -4765,7 +4765,7 @@
         <v>74.251999999999995</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G10">
         <v>10000000</v>
@@ -4794,7 +4794,7 @@
         <v>655.56699999999989</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G11">
         <v>10000000</v>
@@ -4823,7 +4823,7 @@
         <v>425.97199999999998</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G12">
         <v>10000000</v>
@@ -4852,7 +4852,7 @@
         <v>510.97099999999995</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G13">
         <v>10000000</v>
@@ -4881,7 +4881,7 @@
         <v>10000</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G14">
         <v>10000000</v>
@@ -4910,7 +4910,7 @@
         <v>10000</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>14.666222150434395</v>
       </c>
       <c r="G15">
         <v>10000000</v>
@@ -4939,7 +4939,7 @@
         <v>10000</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G16">
         <v>10000000</v>
@@ -4968,7 +4968,7 @@
         <v>10000</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G17">
         <v>10000000</v>
@@ -4997,7 +4997,7 @@
         <v>10000</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G18">
         <v>10000000</v>
@@ -5026,7 +5026,7 @@
         <v>10000</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G19">
         <v>10000000</v>
@@ -5055,7 +5055,7 @@
         <v>10000</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G20">
         <v>10000000</v>
@@ -5084,7 +5084,7 @@
         <v>10000</v>
       </c>
       <c r="F21">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G21">
         <v>10000000</v>
@@ -5113,7 +5113,7 @@
         <v>10000</v>
       </c>
       <c r="F22">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G22">
         <v>10000000</v>
@@ -5142,7 +5142,7 @@
         <v>10000</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G23">
         <v>10000000</v>
@@ -5171,7 +5171,7 @@
         <v>10000</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G24">
         <v>10000000</v>
@@ -5200,7 +5200,7 @@
         <v>10000</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G25">
         <v>10000000</v>
@@ -5229,7 +5229,7 @@
         <v>10000</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G26">
         <v>10000000</v>
@@ -5258,7 +5258,7 @@
         <v>10000</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G27">
         <v>10000000</v>
@@ -5287,7 +5287,7 @@
         <v>10000</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G28">
         <v>10000000</v>
@@ -5316,7 +5316,7 @@
         <v>10000</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G29">
         <v>10000000</v>
@@ -5345,7 +5345,7 @@
         <v>10000</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>14.666222150434395</v>
       </c>
       <c r="G30">
         <v>10000000</v>
@@ -5374,7 +5374,7 @@
         <v>10000</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G31">
         <v>10000000</v>
@@ -5403,7 +5403,7 @@
         <v>10000</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G32">
         <v>10000000</v>
@@ -5432,7 +5432,7 @@
         <v>10000</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G33">
         <v>10000000</v>
@@ -5461,7 +5461,7 @@
         <v>10000</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>14.666222150434395</v>
       </c>
       <c r="G34">
         <v>10000000</v>
@@ -5490,7 +5490,7 @@
         <v>10000</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G35">
         <v>10000000</v>
@@ -5519,7 +5519,7 @@
         <v>10000</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G36">
         <v>10000000</v>
@@ -5548,7 +5548,7 @@
         <v>10000</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G37">
         <v>10000000</v>
@@ -5577,7 +5577,7 @@
         <v>10000</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G38">
         <v>10000000</v>
@@ -5606,7 +5606,7 @@
         <v>10000</v>
       </c>
       <c r="F39">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>10000000</v>
@@ -5635,7 +5635,7 @@
         <v>10000</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>14.666222150434395</v>
       </c>
       <c r="G40">
         <v>10000000</v>
@@ -5664,7 +5664,7 @@
         <v>10000</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G41">
         <v>10000000</v>
@@ -5693,7 +5693,7 @@
         <v>10000</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G42">
         <v>10000000</v>
@@ -7781,7 +7781,7 @@
         <v>635.83000000000004</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G114">
         <v>10000000</v>
@@ -7810,7 +7810,7 @@
         <v>61.32</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G115">
         <v>10000000</v>
@@ -7839,7 +7839,7 @@
         <v>80.3</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G116">
         <v>10000000</v>
@@ -8013,7 +8013,7 @@
         <v>439.27749999999992</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G122">
         <v>10000000</v>
@@ -8071,7 +8071,7 @@
         <v>486.91</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="G124">
         <v>10000000</v>
@@ -12757,19 +12757,19 @@
         <v>11</v>
       </c>
       <c r="B286" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C286" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D286">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E286">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F286">
-        <v>20</v>
+        <v>17.659328711747538</v>
       </c>
       <c r="G286">
         <v>10000000</v>
@@ -12786,19 +12786,19 @@
         <v>11</v>
       </c>
       <c r="B287" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C287" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D287">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E287">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="F287">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G287">
         <v>10000000</v>
@@ -12812,13 +12812,13 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C288" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="D288">
         <v>10000</v>
@@ -12833,7 +12833,7 @@
         <v>10000000</v>
       </c>
       <c r="H288">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I288">
         <v>1</v>
@@ -12844,10 +12844,10 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C289" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D289">
         <v>10000</v>
@@ -12873,10 +12873,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C290" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D290">
         <v>10000</v>
@@ -12899,13 +12899,13 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B291" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C291" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="D291">
         <v>10000</v>
@@ -12920,7 +12920,7 @@
         <v>10000000</v>
       </c>
       <c r="H291">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I291">
         <v>1</v>
@@ -12931,10 +12931,10 @@
         <v>11</v>
       </c>
       <c r="B292" t="s">
+        <v>56</v>
+      </c>
+      <c r="C292" t="s">
         <v>69</v>
-      </c>
-      <c r="C292" t="s">
-        <v>56</v>
       </c>
       <c r="D292">
         <v>10000</v>
@@ -12960,10 +12960,10 @@
         <v>11</v>
       </c>
       <c r="B293" t="s">
+        <v>73</v>
+      </c>
+      <c r="C293" t="s">
         <v>56</v>
-      </c>
-      <c r="C293" t="s">
-        <v>69</v>
       </c>
       <c r="D293">
         <v>10000</v>
@@ -12989,10 +12989,10 @@
         <v>11</v>
       </c>
       <c r="B294" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="C294" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D294">
         <v>10000</v>
@@ -13018,10 +13018,10 @@
         <v>11</v>
       </c>
       <c r="B295" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C295" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D295">
         <v>10000</v>
@@ -13047,10 +13047,10 @@
         <v>11</v>
       </c>
       <c r="B296" t="s">
+        <v>93</v>
+      </c>
+      <c r="C296" t="s">
         <v>71</v>
-      </c>
-      <c r="C296" t="s">
-        <v>93</v>
       </c>
       <c r="D296">
         <v>10000</v>
@@ -13076,10 +13076,10 @@
         <v>11</v>
       </c>
       <c r="B297" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C297" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D297">
         <v>10000</v>
@@ -13102,13 +13102,13 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C298" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -13123,7 +13123,7 @@
         <v>10000000</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I298">
         <v>1</v>
@@ -13134,10 +13134,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
+        <v>56</v>
+      </c>
+      <c r="C299" t="s">
         <v>69</v>
-      </c>
-      <c r="C299" t="s">
-        <v>56</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -13163,10 +13163,10 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
+        <v>73</v>
+      </c>
+      <c r="C300" t="s">
         <v>56</v>
-      </c>
-      <c r="C300" t="s">
-        <v>69</v>
       </c>
       <c r="D300">
         <v>10000</v>
@@ -13192,10 +13192,10 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="C301" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D301">
         <v>10000</v>
@@ -13221,10 +13221,10 @@
         <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C302" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D302">
         <v>10000</v>
@@ -13250,10 +13250,10 @@
         <v>12</v>
       </c>
       <c r="B303" t="s">
+        <v>93</v>
+      </c>
+      <c r="C303" t="s">
         <v>71</v>
-      </c>
-      <c r="C303" t="s">
-        <v>93</v>
       </c>
       <c r="D303">
         <v>10000</v>
@@ -13279,10 +13279,10 @@
         <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C304" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D304">
         <v>10000</v>
@@ -13305,13 +13305,13 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B305" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="C305" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D305">
         <v>10000</v>
@@ -13320,13 +13320,13 @@
         <v>10000</v>
       </c>
       <c r="F305">
-        <v>100</v>
+        <v>16.04838333298461</v>
       </c>
       <c r="G305">
         <v>10000000</v>
       </c>
       <c r="H305">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I305">
         <v>1</v>
@@ -13340,7 +13340,7 @@
         <v>99</v>
       </c>
       <c r="C306" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D306">
         <v>10000</v>
@@ -13349,7 +13349,7 @@
         <v>10000</v>
       </c>
       <c r="F306">
-        <v>1</v>
+        <v>15.497987514705351</v>
       </c>
       <c r="G306">
         <v>10000000</v>
@@ -13369,7 +13369,7 @@
         <v>99</v>
       </c>
       <c r="C307" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D307">
         <v>10000</v>
@@ -13378,7 +13378,7 @@
         <v>10000</v>
       </c>
       <c r="F307">
-        <v>1</v>
+        <v>20.132899668635929</v>
       </c>
       <c r="G307">
         <v>10000000</v>
@@ -13398,7 +13398,7 @@
         <v>99</v>
       </c>
       <c r="C308" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D308">
         <v>10000</v>
@@ -13407,7 +13407,7 @@
         <v>10000</v>
       </c>
       <c r="F308">
-        <v>1</v>
+        <v>18.143749869240722</v>
       </c>
       <c r="G308">
         <v>10000000</v>
@@ -13427,7 +13427,7 @@
         <v>99</v>
       </c>
       <c r="C309" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D309">
         <v>10000</v>
@@ -13436,7 +13436,7 @@
         <v>10000</v>
       </c>
       <c r="F309">
-        <v>1</v>
+        <v>20.53523579310907</v>
       </c>
       <c r="G309">
         <v>10000000</v>
@@ -13456,7 +13456,7 @@
         <v>99</v>
       </c>
       <c r="C310" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D310">
         <v>10000</v>
@@ -13465,7 +13465,7 @@
         <v>10000</v>
       </c>
       <c r="F310">
-        <v>1</v>
+        <v>18.134093802253371</v>
       </c>
       <c r="G310">
         <v>10000000</v>
@@ -13485,7 +13485,7 @@
         <v>99</v>
       </c>
       <c r="C311" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D311">
         <v>10000</v>
@@ -13494,7 +13494,7 @@
         <v>10000</v>
       </c>
       <c r="F311">
-        <v>1</v>
+        <v>16.26081680670643</v>
       </c>
       <c r="G311">
         <v>10000000</v>
@@ -13514,7 +13514,7 @@
         <v>99</v>
       </c>
       <c r="C312" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D312">
         <v>10000</v>
@@ -13523,7 +13523,7 @@
         <v>10000</v>
       </c>
       <c r="F312">
-        <v>1</v>
+        <v>17.51932420405841</v>
       </c>
       <c r="G312">
         <v>10000000</v>
@@ -13543,7 +13543,7 @@
         <v>99</v>
       </c>
       <c r="C313" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D313">
         <v>10000</v>
@@ -13552,7 +13552,7 @@
         <v>10000</v>
       </c>
       <c r="F313">
-        <v>1</v>
+        <v>14.69331526575907</v>
       </c>
       <c r="G313">
         <v>10000000</v>
@@ -13572,7 +13572,7 @@
         <v>99</v>
       </c>
       <c r="C314" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D314">
         <v>10000</v>
@@ -13581,7 +13581,7 @@
         <v>10000</v>
       </c>
       <c r="F314">
-        <v>1</v>
+        <v>15.40464553382759</v>
       </c>
       <c r="G314">
         <v>10000000</v>
@@ -13601,7 +13601,7 @@
         <v>99</v>
       </c>
       <c r="C315" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D315">
         <v>10000</v>
@@ -13610,7 +13610,7 @@
         <v>10000</v>
       </c>
       <c r="F315">
-        <v>1</v>
+        <v>20.62857777398683</v>
       </c>
       <c r="G315">
         <v>10000000</v>
@@ -13630,7 +13630,7 @@
         <v>99</v>
       </c>
       <c r="C316" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D316">
         <v>10000</v>
@@ -13639,7 +13639,7 @@
         <v>10000</v>
       </c>
       <c r="F316">
-        <v>1</v>
+        <v>15.01840285433337</v>
       </c>
       <c r="G316">
         <v>10000000</v>
@@ -13653,13 +13653,13 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B317" t="s">
         <v>99</v>
       </c>
       <c r="C317" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D317">
         <v>10000</v>
@@ -13668,13 +13668,13 @@
         <v>10000</v>
       </c>
       <c r="F317">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G317">
         <v>10000000</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I317">
         <v>1</v>
@@ -13688,7 +13688,7 @@
         <v>99</v>
       </c>
       <c r="C318" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D318">
         <v>10000</v>
@@ -13717,7 +13717,7 @@
         <v>99</v>
       </c>
       <c r="C319" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D319">
         <v>10000</v>
@@ -13746,7 +13746,7 @@
         <v>99</v>
       </c>
       <c r="C320" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="D320">
         <v>10000</v>
@@ -13775,7 +13775,7 @@
         <v>99</v>
       </c>
       <c r="C321" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D321">
         <v>10000</v>
@@ -13804,7 +13804,7 @@
         <v>99</v>
       </c>
       <c r="C322" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D322">
         <v>10000</v>
@@ -13833,7 +13833,7 @@
         <v>99</v>
       </c>
       <c r="C323" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D323">
         <v>10000</v>
@@ -13862,7 +13862,7 @@
         <v>99</v>
       </c>
       <c r="C324" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D324">
         <v>10000</v>
@@ -13891,7 +13891,7 @@
         <v>99</v>
       </c>
       <c r="C325" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D325">
         <v>10000</v>
@@ -13920,7 +13920,7 @@
         <v>99</v>
       </c>
       <c r="C326" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D326">
         <v>10000</v>
@@ -13949,7 +13949,7 @@
         <v>99</v>
       </c>
       <c r="C327" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D327">
         <v>10000</v>
@@ -13978,7 +13978,7 @@
         <v>99</v>
       </c>
       <c r="C328" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D328">
         <v>10000</v>
@@ -14001,13 +14001,13 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B329" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C329" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="D329">
         <v>10000</v>
@@ -14016,13 +14016,13 @@
         <v>10000</v>
       </c>
       <c r="F329">
-        <v>100</v>
+        <v>15.264843462697021</v>
       </c>
       <c r="G329">
         <v>10000000</v>
       </c>
       <c r="H329">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I329">
         <v>1</v>
@@ -14033,10 +14033,10 @@
         <v>11</v>
       </c>
       <c r="B330" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C330" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D330">
         <v>10000</v>
@@ -14045,7 +14045,7 @@
         <v>10000</v>
       </c>
       <c r="F330">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G330">
         <v>10000000</v>
@@ -14062,10 +14062,10 @@
         <v>11</v>
       </c>
       <c r="B331" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C331" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D331">
         <v>10000</v>
@@ -14074,7 +14074,7 @@
         <v>10000</v>
       </c>
       <c r="F331">
-        <v>1</v>
+        <v>12.826475648203701</v>
       </c>
       <c r="G331">
         <v>10000000</v>
@@ -14094,7 +14094,7 @@
         <v>105</v>
       </c>
       <c r="C332" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D332">
         <v>10000</v>
@@ -14103,7 +14103,7 @@
         <v>10000</v>
       </c>
       <c r="F332">
-        <v>1</v>
+        <v>13.19984357171478</v>
       </c>
       <c r="G332">
         <v>10000000</v>
@@ -14123,7 +14123,7 @@
         <v>105</v>
       </c>
       <c r="C333" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="D333">
         <v>10000</v>
@@ -14132,7 +14132,7 @@
         <v>10000</v>
       </c>
       <c r="F333">
-        <v>1</v>
+        <v>15.76513870135552</v>
       </c>
       <c r="G333">
         <v>10000000</v>
@@ -14152,7 +14152,7 @@
         <v>105</v>
       </c>
       <c r="C334" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D334">
         <v>10000</v>
@@ -14161,7 +14161,7 @@
         <v>10000</v>
       </c>
       <c r="F334">
-        <v>1</v>
+        <v>13.775988901960311</v>
       </c>
       <c r="G334">
         <v>10000000</v>
@@ -14181,7 +14181,7 @@
         <v>105</v>
       </c>
       <c r="C335" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D335">
         <v>10000</v>
@@ -14190,7 +14190,7 @@
         <v>10000</v>
       </c>
       <c r="F335">
-        <v>1</v>
+        <v>16.167474825828659</v>
       </c>
       <c r="G335">
         <v>10000000</v>
@@ -14210,7 +14210,7 @@
         <v>105</v>
       </c>
       <c r="C336" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D336">
         <v>10000</v>
@@ -14219,7 +14219,7 @@
         <v>10000</v>
       </c>
       <c r="F336">
-        <v>1</v>
+        <v>15.523737026671631</v>
       </c>
       <c r="G336">
         <v>10000000</v>
@@ -14239,7 +14239,7 @@
         <v>105</v>
       </c>
       <c r="C337" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D337">
         <v>10000</v>
@@ -14248,7 +14248,7 @@
         <v>10000</v>
       </c>
       <c r="F337">
-        <v>1</v>
+        <v>13.038909121925521</v>
       </c>
       <c r="G337">
         <v>10000000</v>
@@ -14268,7 +14268,7 @@
         <v>105</v>
       </c>
       <c r="C338" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D338">
         <v>10000</v>
@@ -14277,7 +14277,7 @@
         <v>10000</v>
       </c>
       <c r="F338">
-        <v>1</v>
+        <v>14.90896742847668</v>
       </c>
       <c r="G338">
         <v>10000000</v>
@@ -14297,7 +14297,7 @@
         <v>105</v>
       </c>
       <c r="C339" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D339">
         <v>10000</v>
@@ -14306,7 +14306,7 @@
         <v>10000</v>
       </c>
       <c r="F339">
-        <v>1</v>
+        <v>10.61845499709511</v>
       </c>
       <c r="G339">
         <v>10000000</v>
@@ -14326,7 +14326,7 @@
         <v>105</v>
       </c>
       <c r="C340" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D340">
         <v>10000</v>
@@ -14335,7 +14335,7 @@
         <v>10000</v>
       </c>
       <c r="F340">
-        <v>1</v>
+        <v>10.83410715981271</v>
       </c>
       <c r="G340">
         <v>10000000</v>
@@ -14355,7 +14355,7 @@
         <v>105</v>
       </c>
       <c r="C341" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D341">
         <v>10000</v>
@@ -14364,7 +14364,7 @@
         <v>10000</v>
       </c>
       <c r="F341">
-        <v>1</v>
+        <v>16.26081680670643</v>
       </c>
       <c r="G341">
         <v>10000000</v>
@@ -14384,7 +14384,7 @@
         <v>105</v>
       </c>
       <c r="C342" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D342">
         <v>10000</v>
@@ -14393,7 +14393,7 @@
         <v>10000</v>
       </c>
       <c r="F342">
-        <v>1</v>
+        <v>12.01536602126585</v>
       </c>
       <c r="G342">
         <v>10000000</v>
@@ -14413,7 +14413,7 @@
         <v>105</v>
       </c>
       <c r="C343" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D343">
         <v>10000</v>
@@ -14422,7 +14422,7 @@
         <v>10000</v>
       </c>
       <c r="F343">
-        <v>1</v>
+        <v>10.09380869078214</v>
       </c>
       <c r="G343">
         <v>10000000</v>
@@ -14442,7 +14442,7 @@
         <v>105</v>
       </c>
       <c r="C344" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="D344">
         <v>10000</v>
@@ -14451,7 +14451,7 @@
         <v>10000</v>
       </c>
       <c r="F344">
-        <v>1</v>
+        <v>13.43480786840709</v>
       </c>
       <c r="G344">
         <v>10000000</v>
@@ -14471,7 +14471,7 @@
         <v>105</v>
       </c>
       <c r="C345" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D345">
         <v>10000</v>
@@ -14480,7 +14480,7 @@
         <v>10000</v>
       </c>
       <c r="F345">
-        <v>1</v>
+        <v>2031.5624642926689</v>
       </c>
       <c r="G345">
         <v>10000000</v>
@@ -14500,7 +14500,7 @@
         <v>105</v>
       </c>
       <c r="C346" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D346">
         <v>10000</v>
@@ -14509,7 +14509,7 @@
         <v>10000</v>
       </c>
       <c r="F346">
-        <v>1</v>
+        <v>2028.5755209045799</v>
       </c>
       <c r="G346">
         <v>10000000</v>
@@ -14529,7 +14529,7 @@
         <v>105</v>
       </c>
       <c r="C347" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D347">
         <v>10000</v>
@@ -14538,7 +14538,7 @@
         <v>10000</v>
       </c>
       <c r="F347">
-        <v>1</v>
+        <v>2026.4286553443919</v>
       </c>
       <c r="G347">
         <v>10000000</v>
@@ -14558,7 +14558,7 @@
         <v>105</v>
       </c>
       <c r="C348" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D348">
         <v>10000</v>
@@ -14567,7 +14567,7 @@
         <v>10000</v>
       </c>
       <c r="F348">
-        <v>1</v>
+        <v>2035.9495373939239</v>
       </c>
       <c r="G348">
         <v>10000000</v>
@@ -14587,7 +14587,7 @@
         <v>105</v>
       </c>
       <c r="C349" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D349">
         <v>10000</v>
@@ -14596,7 +14596,7 @@
         <v>10000</v>
       </c>
       <c r="F349">
-        <v>1</v>
+        <v>17.136300213559981</v>
       </c>
       <c r="G349">
         <v>10000000</v>
@@ -14613,10 +14613,10 @@
         <v>11</v>
       </c>
       <c r="B350" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C350" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="D350">
         <v>10000</v>
@@ -14625,7 +14625,7 @@
         <v>10000</v>
       </c>
       <c r="F350">
-        <v>1</v>
+        <v>8.9793196839394245</v>
       </c>
       <c r="G350">
         <v>10000000</v>
@@ -14642,10 +14642,10 @@
         <v>11</v>
       </c>
       <c r="B351" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C351" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="D351">
         <v>10000</v>
@@ -14654,7 +14654,7 @@
         <v>10000</v>
       </c>
       <c r="F351">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G351">
         <v>10000000</v>
@@ -14671,10 +14671,10 @@
         <v>11</v>
       </c>
       <c r="B352" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C352" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="D352">
         <v>10000</v>
@@ -14683,7 +14683,7 @@
         <v>10000</v>
       </c>
       <c r="F352">
-        <v>1</v>
+        <v>2019.988058663826</v>
       </c>
       <c r="G352">
         <v>10000000</v>
@@ -14700,10 +14700,10 @@
         <v>11</v>
       </c>
       <c r="B353" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C353" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="D353">
         <v>10000</v>
@@ -14712,7 +14712,7 @@
         <v>10000</v>
       </c>
       <c r="F353">
-        <v>1</v>
+        <v>2014.5291621269739</v>
       </c>
       <c r="G353">
         <v>10000000</v>
@@ -14732,7 +14732,7 @@
         <v>108</v>
       </c>
       <c r="C354" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="D354">
         <v>10000</v>
@@ -14741,7 +14741,7 @@
         <v>10000</v>
       </c>
       <c r="F354">
-        <v>1</v>
+        <v>2011.590499073822</v>
       </c>
       <c r="G354">
         <v>10000000</v>
@@ -14761,7 +14761,7 @@
         <v>108</v>
       </c>
       <c r="C355" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D355">
         <v>10000</v>
@@ -14770,7 +14770,7 @@
         <v>10000</v>
       </c>
       <c r="F355">
-        <v>1</v>
+        <v>2014.1139512465179</v>
       </c>
       <c r="G355">
         <v>10000000</v>
@@ -14790,7 +14790,7 @@
         <v>108</v>
       </c>
       <c r="C356" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D356">
         <v>10000</v>
@@ -14799,7 +14799,7 @@
         <v>10000</v>
       </c>
       <c r="F356">
-        <v>1</v>
+        <v>2013.711615122045</v>
       </c>
       <c r="G356">
         <v>10000000</v>
@@ -14819,7 +14819,7 @@
         <v>108</v>
       </c>
       <c r="C357" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="D357">
         <v>10000</v>
@@ -14828,7 +14828,7 @@
         <v>10000</v>
       </c>
       <c r="F357">
-        <v>1</v>
+        <v>2022.9943141858889</v>
       </c>
       <c r="G357">
         <v>10000000</v>
@@ -14848,7 +14848,7 @@
         <v>108</v>
       </c>
       <c r="C358" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D358">
         <v>10000</v>
@@ -14857,7 +14857,7 @@
         <v>10000</v>
       </c>
       <c r="F358">
-        <v>1</v>
+        <v>2020.2004921375469</v>
       </c>
       <c r="G358">
         <v>10000000</v>
@@ -14877,7 +14877,7 @@
         <v>108</v>
       </c>
       <c r="C359" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D359">
         <v>10000</v>
@@ -14886,7 +14886,7 @@
         <v>10000</v>
       </c>
       <c r="F359">
-        <v>1</v>
+        <v>2022.379544587694</v>
       </c>
       <c r="G359">
         <v>10000000</v>
@@ -14906,7 +14906,7 @@
         <v>108</v>
       </c>
       <c r="C360" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D360">
         <v>10000</v>
@@ -14915,7 +14915,7 @@
         <v>10000</v>
       </c>
       <c r="F360">
-        <v>1</v>
+        <v>2016.7339640890871</v>
       </c>
       <c r="G360">
         <v>10000000</v>
@@ -14935,7 +14935,7 @@
         <v>108</v>
       </c>
       <c r="C361" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D361">
         <v>10000</v>
@@ -14944,7 +14944,7 @@
         <v>10000</v>
       </c>
       <c r="F361">
-        <v>1</v>
+        <v>2014.773782490654</v>
       </c>
       <c r="G361">
         <v>10000000</v>
@@ -14964,7 +14964,7 @@
         <v>108</v>
       </c>
       <c r="C362" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D362">
         <v>10000</v>
@@ -14973,7 +14973,7 @@
         <v>10000</v>
       </c>
       <c r="F362">
-        <v>1</v>
+        <v>2011.587280384826</v>
       </c>
       <c r="G362">
         <v>10000000</v>
@@ -14993,7 +14993,7 @@
         <v>108</v>
       </c>
       <c r="C363" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D363">
         <v>10000</v>
@@ -15002,7 +15002,7 @@
         <v>10000</v>
       </c>
       <c r="F363">
-        <v>1</v>
+        <v>2019.389382510609</v>
       </c>
       <c r="G363">
         <v>10000000</v>
@@ -15022,7 +15022,7 @@
         <v>108</v>
       </c>
       <c r="C364" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D364">
         <v>10000</v>
@@ -15031,7 +15031,7 @@
         <v>10000</v>
       </c>
       <c r="F364">
-        <v>1</v>
+        <v>26.042412664897409</v>
       </c>
       <c r="G364">
         <v>10000000</v>
@@ -15051,7 +15051,7 @@
         <v>108</v>
       </c>
       <c r="C365" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="D365">
         <v>10000</v>
@@ -15060,7 +15060,7 @@
         <v>10000</v>
       </c>
       <c r="F365">
-        <v>1</v>
+        <v>23.438493267307241</v>
       </c>
       <c r="G365">
         <v>10000000</v>
@@ -15080,7 +15080,7 @@
         <v>108</v>
       </c>
       <c r="C366" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="D366">
         <v>10000</v>
@@ -15089,7 +15089,7 @@
         <v>10000</v>
       </c>
       <c r="F366">
-        <v>1</v>
+        <v>19.827124214036338</v>
       </c>
       <c r="G366">
         <v>10000000</v>
@@ -15109,7 +15109,7 @@
         <v>108</v>
       </c>
       <c r="C367" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="D367">
         <v>10000</v>
@@ -15118,7 +15118,7 @@
         <v>10000</v>
       </c>
       <c r="F367">
-        <v>1</v>
+        <v>20.744450577835099</v>
       </c>
       <c r="G367">
         <v>10000000</v>
@@ -15138,7 +15138,7 @@
         <v>108</v>
       </c>
       <c r="C368" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D368">
         <v>10000</v>
@@ -15147,7 +15147,7 @@
         <v>10000</v>
       </c>
       <c r="F368">
-        <v>1</v>
+        <v>3.060973234991649</v>
       </c>
       <c r="G368">
         <v>10000000</v>
@@ -15167,7 +15167,7 @@
         <v>108</v>
       </c>
       <c r="C369" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D369">
         <v>10000</v>
@@ -15176,7 +15176,7 @@
         <v>10000</v>
       </c>
       <c r="F369">
-        <v>1</v>
+        <v>14.072108289572551</v>
       </c>
       <c r="G369">
         <v>10000000</v>
@@ -15196,7 +15196,7 @@
         <v>108</v>
       </c>
       <c r="C370" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D370">
         <v>10000</v>
@@ -15205,7 +15205,7 @@
         <v>10000</v>
       </c>
       <c r="F370">
-        <v>1</v>
+        <v>9.3824784227136249</v>
       </c>
       <c r="G370">
         <v>10000000</v>
@@ -15222,10 +15222,10 @@
         <v>11</v>
       </c>
       <c r="B371" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C371" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D371">
         <v>10000</v>
@@ -15234,7 +15234,7 @@
         <v>10000</v>
       </c>
       <c r="F371">
-        <v>1</v>
+        <v>7.1834557471515401</v>
       </c>
       <c r="G371">
         <v>10000000</v>
@@ -15251,10 +15251,10 @@
         <v>11</v>
       </c>
       <c r="B372" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C372" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D372">
         <v>10000</v>
@@ -15263,7 +15263,7 @@
         <v>10000</v>
       </c>
       <c r="F372">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G372">
         <v>10000000</v>
@@ -15280,10 +15280,10 @@
         <v>11</v>
       </c>
       <c r="B373" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C373" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="D373">
         <v>10000</v>
@@ -15292,7 +15292,7 @@
         <v>10000</v>
       </c>
       <c r="F373">
-        <v>1</v>
+        <v>2020.2037108265431</v>
       </c>
       <c r="G373">
         <v>10000000</v>
@@ -15309,10 +15309,10 @@
         <v>11</v>
       </c>
       <c r="B374" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C374" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="D374">
         <v>10000</v>
@@ -15321,7 +15321,7 @@
         <v>10000</v>
       </c>
       <c r="F374">
-        <v>1</v>
+        <v>2014.7448142896919</v>
       </c>
       <c r="G374">
         <v>10000000</v>
@@ -15338,10 +15338,10 @@
         <v>11</v>
       </c>
       <c r="B375" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C375" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D375">
         <v>10000</v>
@@ -15350,7 +15350,7 @@
         <v>10000</v>
       </c>
       <c r="F375">
-        <v>1</v>
+        <v>2011.80615123654</v>
       </c>
       <c r="G375">
         <v>10000000</v>
@@ -15370,7 +15370,7 @@
         <v>111</v>
       </c>
       <c r="C376" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D376">
         <v>10000</v>
@@ -15379,7 +15379,7 @@
         <v>10000</v>
       </c>
       <c r="F376">
-        <v>1</v>
+        <v>2014.329603409235</v>
       </c>
       <c r="G376">
         <v>10000000</v>
@@ -15399,7 +15399,7 @@
         <v>111</v>
       </c>
       <c r="C377" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D377">
         <v>10000</v>
@@ -15408,7 +15408,7 @@
         <v>10000</v>
       </c>
       <c r="F377">
-        <v>1</v>
+        <v>2013.9272672847619</v>
       </c>
       <c r="G377">
         <v>10000000</v>
@@ -15428,7 +15428,7 @@
         <v>111</v>
       </c>
       <c r="C378" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D378">
         <v>10000</v>
@@ -15437,7 +15437,7 @@
         <v>10000</v>
       </c>
       <c r="F378">
-        <v>1</v>
+        <v>2023.209966348606</v>
       </c>
       <c r="G378">
         <v>10000000</v>
@@ -15457,7 +15457,7 @@
         <v>111</v>
       </c>
       <c r="C379" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="D379">
         <v>10000</v>
@@ -15466,7 +15466,7 @@
         <v>10000</v>
       </c>
       <c r="F379">
-        <v>1</v>
+        <v>2020.4258003672519</v>
       </c>
       <c r="G379">
         <v>10000000</v>
@@ -15486,7 +15486,7 @@
         <v>111</v>
       </c>
       <c r="C380" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D380">
         <v>10000</v>
@@ -15495,7 +15495,7 @@
         <v>10000</v>
       </c>
       <c r="F380">
-        <v>1</v>
+        <v>2022.595196750412</v>
       </c>
       <c r="G380">
         <v>10000000</v>
@@ -15515,7 +15515,7 @@
         <v>111</v>
       </c>
       <c r="C381" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D381">
         <v>10000</v>
@@ -15524,7 +15524,7 @@
         <v>10000</v>
       </c>
       <c r="F381">
-        <v>1</v>
+        <v>2016.9496162518039</v>
       </c>
       <c r="G381">
         <v>10000000</v>
@@ -15544,7 +15544,7 @@
         <v>111</v>
       </c>
       <c r="C382" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D382">
         <v>10000</v>
@@ -15553,7 +15553,7 @@
         <v>10000</v>
       </c>
       <c r="F382">
-        <v>1</v>
+        <v>2014.9894346533711</v>
       </c>
       <c r="G382">
         <v>10000000</v>
@@ -15573,7 +15573,7 @@
         <v>111</v>
       </c>
       <c r="C383" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D383">
         <v>10000</v>
@@ -15582,7 +15582,7 @@
         <v>10000</v>
       </c>
       <c r="F383">
-        <v>1</v>
+        <v>2011.8029325475441</v>
       </c>
       <c r="G383">
         <v>10000000</v>
@@ -15602,7 +15602,7 @@
         <v>111</v>
       </c>
       <c r="C384" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D384">
         <v>10000</v>
@@ -15611,7 +15611,7 @@
         <v>10000</v>
       </c>
       <c r="F384">
-        <v>1</v>
+        <v>2019.6050346733271</v>
       </c>
       <c r="G384">
         <v>10000000</v>
@@ -15631,7 +15631,7 @@
         <v>111</v>
       </c>
       <c r="C385" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="D385">
         <v>10000</v>
@@ -15640,7 +15640,7 @@
         <v>10000</v>
       </c>
       <c r="F385">
-        <v>1</v>
+        <v>26.258064827615009</v>
       </c>
       <c r="G385">
         <v>10000000</v>
@@ -15660,7 +15660,7 @@
         <v>111</v>
       </c>
       <c r="C386" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="D386">
         <v>10000</v>
@@ -15669,7 +15669,7 @@
         <v>10000</v>
       </c>
       <c r="F386">
-        <v>1</v>
+        <v>23.654145430024851</v>
       </c>
       <c r="G386">
         <v>10000000</v>
@@ -15689,7 +15689,7 @@
         <v>111</v>
       </c>
       <c r="C387" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="D387">
         <v>10000</v>
@@ -15698,7 +15698,7 @@
         <v>10000</v>
       </c>
       <c r="F387">
-        <v>1</v>
+        <v>20.042776376753942</v>
       </c>
       <c r="G387">
         <v>10000000</v>
@@ -15718,7 +15718,7 @@
         <v>111</v>
       </c>
       <c r="C388" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="D388">
         <v>10000</v>
@@ -15727,7 +15727,7 @@
         <v>10000</v>
       </c>
       <c r="F388">
-        <v>1</v>
+        <v>20.960102740552699</v>
       </c>
       <c r="G388">
         <v>10000000</v>
@@ -15747,7 +15747,7 @@
         <v>111</v>
       </c>
       <c r="C389" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D389">
         <v>10000</v>
@@ -15756,7 +15756,7 @@
         <v>10000</v>
       </c>
       <c r="F389">
-        <v>1</v>
+        <v>3.2766253977092519</v>
       </c>
       <c r="G389">
         <v>10000000</v>
@@ -15776,7 +15776,7 @@
         <v>111</v>
       </c>
       <c r="C390" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D390">
         <v>10000</v>
@@ -15785,7 +15785,7 @@
         <v>10000</v>
       </c>
       <c r="F390">
-        <v>1</v>
+        <v>14.287760452290151</v>
       </c>
       <c r="G390">
         <v>10000000</v>
@@ -15805,7 +15805,7 @@
         <v>111</v>
       </c>
       <c r="C391" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D391">
         <v>10000</v>
@@ -15814,7 +15814,7 @@
         <v>10000</v>
       </c>
       <c r="F391">
-        <v>1</v>
+        <v>9.5981305854312264</v>
       </c>
       <c r="G391">
         <v>10000000</v>
@@ -15831,10 +15831,10 @@
         <v>11</v>
       </c>
       <c r="B392" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C392" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D392">
         <v>10000</v>
@@ -15843,7 +15843,7 @@
         <v>10000</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>13.468979525909138</v>
       </c>
       <c r="G392">
         <v>10000000</v>
@@ -15860,10 +15860,10 @@
         <v>11</v>
       </c>
       <c r="B393" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C393" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D393">
         <v>10000</v>
@@ -15872,7 +15872,7 @@
         <v>10000</v>
       </c>
       <c r="F393">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G393">
         <v>10000000</v>
@@ -15889,10 +15889,10 @@
         <v>11</v>
       </c>
       <c r="B394" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C394" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="D394">
         <v>10000</v>
@@ -15901,7 +15901,7 @@
         <v>10000</v>
       </c>
       <c r="F394">
-        <v>1</v>
+        <v>13.994859753673699</v>
       </c>
       <c r="G394">
         <v>10000000</v>
@@ -15918,10 +15918,10 @@
         <v>11</v>
       </c>
       <c r="B395" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C395" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="D395">
         <v>10000</v>
@@ -15930,7 +15930,7 @@
         <v>10000</v>
       </c>
       <c r="F395">
-        <v>1</v>
+        <v>12.96166058602668</v>
       </c>
       <c r="G395">
         <v>10000000</v>
@@ -15947,10 +15947,10 @@
         <v>11</v>
       </c>
       <c r="B396" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C396" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D396">
         <v>10000</v>
@@ -15959,7 +15959,7 @@
         <v>10000</v>
       </c>
       <c r="F396">
-        <v>1</v>
+        <v>15.52695571566742</v>
       </c>
       <c r="G396">
         <v>10000000</v>
@@ -15976,10 +15976,10 @@
         <v>11</v>
       </c>
       <c r="B397" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C397" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="D397">
         <v>10000</v>
@@ -15988,7 +15988,7 @@
         <v>10000</v>
       </c>
       <c r="F397">
-        <v>1</v>
+        <v>13.537805916272211</v>
       </c>
       <c r="G397">
         <v>10000000</v>
@@ -16008,7 +16008,7 @@
         <v>114</v>
       </c>
       <c r="C398" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D398">
         <v>10000</v>
@@ -16017,7 +16017,7 @@
         <v>10000</v>
       </c>
       <c r="F398">
-        <v>1</v>
+        <v>15.929291840140561</v>
       </c>
       <c r="G398">
         <v>10000000</v>
@@ -16037,7 +16037,7 @@
         <v>114</v>
       </c>
       <c r="C399" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D399">
         <v>10000</v>
@@ -16046,7 +16046,7 @@
         <v>10000</v>
       </c>
       <c r="F399">
-        <v>1</v>
+        <v>17.001115275737</v>
       </c>
       <c r="G399">
         <v>10000000</v>
@@ -16066,7 +16066,7 @@
         <v>114</v>
       </c>
       <c r="C400" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D400">
         <v>10000</v>
@@ -16075,7 +16075,7 @@
         <v>10000</v>
       </c>
       <c r="F400">
-        <v>1</v>
+        <v>14.207293227395519</v>
       </c>
       <c r="G400">
         <v>10000000</v>
@@ -16095,7 +16095,7 @@
         <v>114</v>
       </c>
       <c r="C401" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="D401">
         <v>10000</v>
@@ -16104,7 +16104,7 @@
         <v>10000</v>
       </c>
       <c r="F401">
-        <v>1</v>
+        <v>16.38634567754205</v>
       </c>
       <c r="G401">
         <v>10000000</v>
@@ -16124,7 +16124,7 @@
         <v>114</v>
       </c>
       <c r="C402" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D402">
         <v>10000</v>
@@ -16133,7 +16133,7 @@
         <v>10000</v>
       </c>
       <c r="F402">
-        <v>1</v>
+        <v>10.908137006715769</v>
       </c>
       <c r="G402">
         <v>10000000</v>
@@ -16153,7 +16153,7 @@
         <v>114</v>
       </c>
       <c r="C403" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D403">
         <v>10000</v>
@@ -16162,7 +16162,7 @@
         <v>10000</v>
       </c>
       <c r="F403">
-        <v>1</v>
+        <v>10.81157633684222</v>
       </c>
       <c r="G403">
         <v>10000000</v>
@@ -16182,7 +16182,7 @@
         <v>114</v>
       </c>
       <c r="C404" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D404">
         <v>10000</v>
@@ -16191,7 +16191,7 @@
         <v>10000</v>
       </c>
       <c r="F404">
-        <v>1</v>
+        <v>16.022633821018331</v>
       </c>
       <c r="G404">
         <v>10000000</v>
@@ -16211,7 +16211,7 @@
         <v>114</v>
       </c>
       <c r="C405" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D405">
         <v>10000</v>
@@ -16220,7 +16220,7 @@
         <v>10000</v>
       </c>
       <c r="F405">
-        <v>1</v>
+        <v>13.39618360045767</v>
       </c>
       <c r="G405">
         <v>10000000</v>
@@ -16240,7 +16240,7 @@
         <v>114</v>
       </c>
       <c r="C406" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="D406">
         <v>10000</v>
@@ -16249,7 +16249,7 @@
         <v>10000</v>
       </c>
       <c r="F406">
-        <v>1</v>
+        <v>11.00791636558511</v>
       </c>
       <c r="G406">
         <v>10000000</v>
@@ -16269,7 +16269,7 @@
         <v>114</v>
       </c>
       <c r="C407" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="D407">
         <v>10000</v>
@@ -16278,7 +16278,7 @@
         <v>10000</v>
       </c>
       <c r="F407">
-        <v>1</v>
+        <v>33.783359699760616</v>
       </c>
       <c r="G407">
         <v>10000000</v>
@@ -16298,7 +16298,7 @@
         <v>114</v>
       </c>
       <c r="C408" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="D408">
         <v>10000</v>
@@ -16307,7 +16307,7 @@
         <v>10000</v>
       </c>
       <c r="F408">
-        <v>1</v>
+        <v>34.697467374563587</v>
       </c>
       <c r="G408">
         <v>10000000</v>
@@ -16327,7 +16327,7 @@
         <v>114</v>
       </c>
       <c r="C409" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="D409">
         <v>10000</v>
@@ -16336,7 +16336,7 @@
         <v>10000</v>
       </c>
       <c r="F409">
-        <v>1</v>
+        <v>22.582321994428401</v>
       </c>
       <c r="G409">
         <v>10000000</v>
@@ -16356,7 +16356,7 @@
         <v>114</v>
       </c>
       <c r="C410" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="D410">
         <v>10000</v>
@@ -16365,7 +16365,7 @@
         <v>10000</v>
       </c>
       <c r="F410">
-        <v>1</v>
+        <v>28.440335966757321</v>
       </c>
       <c r="G410">
         <v>10000000</v>
@@ -16385,7 +16385,7 @@
         <v>114</v>
       </c>
       <c r="C411" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="D411">
         <v>10000</v>
@@ -16394,7 +16394,7 @@
         <v>10000</v>
       </c>
       <c r="F411">
-        <v>1</v>
+        <v>16.898117227871879</v>
       </c>
       <c r="G411">
         <v>10000000</v>
@@ -16411,10 +16411,10 @@
         <v>11</v>
       </c>
       <c r="B412" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C412" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D412">
         <v>10000</v>
@@ -16423,7 +16423,7 @@
         <v>10000</v>
       </c>
       <c r="F412">
-        <v>1</v>
+        <v>22.448299209848564</v>
       </c>
       <c r="G412">
         <v>10000000</v>
@@ -16440,10 +16440,10 @@
         <v>11</v>
       </c>
       <c r="B413" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C413" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D413">
         <v>10000</v>
@@ -16452,7 +16452,7 @@
         <v>10000</v>
       </c>
       <c r="F413">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G413">
         <v>10000000</v>
@@ -16469,10 +16469,10 @@
         <v>11</v>
       </c>
       <c r="B414" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C414" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D414">
         <v>10000</v>
@@ -16481,7 +16481,7 @@
         <v>10000</v>
       </c>
       <c r="F414">
-        <v>1</v>
+        <v>2032.025955508062</v>
       </c>
       <c r="G414">
         <v>10000000</v>
@@ -16498,10 +16498,10 @@
         <v>11</v>
       </c>
       <c r="B415" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C415" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D415">
         <v>10000</v>
@@ -16510,7 +16510,7 @@
         <v>10000</v>
       </c>
       <c r="F415">
-        <v>1</v>
+        <v>2026.5670589712099</v>
       </c>
       <c r="G415">
         <v>10000000</v>
@@ -16527,10 +16527,10 @@
         <v>11</v>
       </c>
       <c r="B416" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C416" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="D416">
         <v>10000</v>
@@ -16539,7 +16539,7 @@
         <v>10000</v>
       </c>
       <c r="F416">
-        <v>1</v>
+        <v>2023.628395918058</v>
       </c>
       <c r="G416">
         <v>10000000</v>
@@ -16556,10 +16556,10 @@
         <v>11</v>
       </c>
       <c r="B417" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C417" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="D417">
         <v>10000</v>
@@ -16568,7 +16568,7 @@
         <v>10000</v>
       </c>
       <c r="F417">
-        <v>1</v>
+        <v>2026.1518480907539</v>
       </c>
       <c r="G417">
         <v>10000000</v>
@@ -16585,10 +16585,10 @@
         <v>11</v>
       </c>
       <c r="B418" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C418" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="D418">
         <v>10000</v>
@@ -16597,7 +16597,7 @@
         <v>10000</v>
       </c>
       <c r="F418">
-        <v>1</v>
+        <v>2025.749511966281</v>
       </c>
       <c r="G418">
         <v>10000000</v>
@@ -16614,10 +16614,10 @@
         <v>11</v>
       </c>
       <c r="B419" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C419" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="D419">
         <v>10000</v>
@@ -16626,7 +16626,7 @@
         <v>10000</v>
       </c>
       <c r="F419">
-        <v>1</v>
+        <v>2035.0322110301249</v>
       </c>
       <c r="G419">
         <v>10000000</v>
@@ -16646,7 +16646,7 @@
         <v>117</v>
       </c>
       <c r="C420" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D420">
         <v>10000</v>
@@ -16655,7 +16655,7 @@
         <v>10000</v>
       </c>
       <c r="F420">
-        <v>1</v>
+        <v>2032.2383889817841</v>
       </c>
       <c r="G420">
         <v>10000000</v>
@@ -16675,7 +16675,7 @@
         <v>117</v>
       </c>
       <c r="C421" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D421">
         <v>10000</v>
@@ -16684,7 +16684,7 @@
         <v>10000</v>
       </c>
       <c r="F421">
-        <v>1</v>
+        <v>2034.41744143193</v>
       </c>
       <c r="G421">
         <v>10000000</v>
@@ -16704,7 +16704,7 @@
         <v>117</v>
       </c>
       <c r="C422" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D422">
         <v>10000</v>
@@ -16713,7 +16713,7 @@
         <v>10000</v>
       </c>
       <c r="F422">
-        <v>1</v>
+        <v>2028.7718609333231</v>
       </c>
       <c r="G422">
         <v>10000000</v>
@@ -16733,7 +16733,7 @@
         <v>117</v>
       </c>
       <c r="C423" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="D423">
         <v>10000</v>
@@ -16742,7 +16742,7 @@
         <v>10000</v>
       </c>
       <c r="F423">
-        <v>1</v>
+        <v>2026.81167933489</v>
       </c>
       <c r="G423">
         <v>10000000</v>
@@ -16762,7 +16762,7 @@
         <v>117</v>
       </c>
       <c r="C424" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D424">
         <v>10000</v>
@@ -16771,7 +16771,7 @@
         <v>10000</v>
       </c>
       <c r="F424">
-        <v>1</v>
+        <v>2023.625177229063</v>
       </c>
       <c r="G424">
         <v>10000000</v>
@@ -16791,7 +16791,7 @@
         <v>117</v>
       </c>
       <c r="C425" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D425">
         <v>10000</v>
@@ -16800,7 +16800,7 @@
         <v>10000</v>
       </c>
       <c r="F425">
-        <v>1</v>
+        <v>2031.427279354846</v>
       </c>
       <c r="G425">
         <v>10000000</v>
@@ -16820,7 +16820,7 @@
         <v>117</v>
       </c>
       <c r="C426" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="D426">
         <v>10000</v>
@@ -16829,7 +16829,7 @@
         <v>10000</v>
       </c>
       <c r="F426">
-        <v>1</v>
+        <v>27.600258138857399</v>
       </c>
       <c r="G426">
         <v>10000000</v>
@@ -16849,7 +16849,7 @@
         <v>117</v>
       </c>
       <c r="C427" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="D427">
         <v>10000</v>
@@ -16858,7 +16858,7 @@
         <v>10000</v>
       </c>
       <c r="F427">
-        <v>1</v>
+        <v>27.532665669945921</v>
       </c>
       <c r="G427">
         <v>10000000</v>
@@ -16878,7 +16878,7 @@
         <v>117</v>
       </c>
       <c r="C428" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="D428">
         <v>10000</v>
@@ -16887,7 +16887,7 @@
         <v>10000</v>
       </c>
       <c r="F428">
-        <v>1</v>
+        <v>10.21933756161776</v>
       </c>
       <c r="G428">
         <v>10000000</v>
@@ -16907,7 +16907,7 @@
         <v>117</v>
       </c>
       <c r="C429" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="D429">
         <v>10000</v>
@@ -16916,7 +16916,7 @@
         <v>10000</v>
       </c>
       <c r="F429">
-        <v>1</v>
+        <v>9.7622837242162692</v>
       </c>
       <c r="G429">
         <v>10000000</v>
@@ -16936,7 +16936,7 @@
         <v>117</v>
       </c>
       <c r="C430" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="D430">
         <v>10000</v>
@@ -16945,7 +16945,7 @@
         <v>10000</v>
       </c>
       <c r="F430">
-        <v>1</v>
+        <v>13.454120002381799</v>
       </c>
       <c r="G430">
         <v>10000000</v>
@@ -16965,7 +16965,7 @@
         <v>117</v>
       </c>
       <c r="C431" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="D431">
         <v>10000</v>
@@ -16974,7 +16974,7 @@
         <v>10000</v>
       </c>
       <c r="F431">
-        <v>1</v>
+        <v>8.4072156569907328</v>
       </c>
       <c r="G431">
         <v>10000000</v>
@@ -16994,7 +16994,7 @@
         <v>117</v>
       </c>
       <c r="C432" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="D432">
         <v>10000</v>
@@ -17003,7 +17003,7 @@
         <v>10000</v>
       </c>
       <c r="F432">
-        <v>1</v>
+        <v>21.420375266949971</v>
       </c>
       <c r="G432">
         <v>10000000</v>
@@ -17020,10 +17020,10 @@
         <v>11</v>
       </c>
       <c r="B433" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="C433" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D433">
         <v>10000</v>
@@ -17032,7 +17032,7 @@
         <v>10000</v>
       </c>
       <c r="F433">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G433">
         <v>10000000</v>
@@ -17049,10 +17049,10 @@
         <v>11</v>
       </c>
       <c r="B434" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C434" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="D434">
         <v>10000</v>
@@ -17061,7 +17061,7 @@
         <v>10000</v>
       </c>
       <c r="F434">
-        <v>1</v>
+        <v>9.1507328150170952</v>
       </c>
       <c r="G434">
         <v>10000000</v>
@@ -17078,10 +17078,10 @@
         <v>11</v>
       </c>
       <c r="B435" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C435" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D435">
         <v>10000</v>
@@ -17090,7 +17090,7 @@
         <v>10000</v>
       </c>
       <c r="F435">
-        <v>1</v>
+        <v>9.2472934848906494</v>
       </c>
       <c r="G435">
         <v>10000000</v>
@@ -17107,10 +17107,10 @@
         <v>11</v>
       </c>
       <c r="B436" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C436" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D436">
         <v>10000</v>
@@ -17119,7 +17119,7 @@
         <v>10000</v>
       </c>
       <c r="F436">
-        <v>1</v>
+        <v>17.966721974472541</v>
       </c>
       <c r="G436">
         <v>10000000</v>
@@ -17136,10 +17136,10 @@
         <v>11</v>
       </c>
       <c r="B437" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C437" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="D437">
         <v>10000</v>
@@ -17148,7 +17148,7 @@
         <v>10000</v>
       </c>
       <c r="F437">
-        <v>1</v>
+        <v>15.97757217507734</v>
       </c>
       <c r="G437">
         <v>10000000</v>
@@ -17165,10 +17165,10 @@
         <v>11</v>
       </c>
       <c r="B438" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C438" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="D438">
         <v>10000</v>
@@ -17177,7 +17177,7 @@
         <v>10000</v>
       </c>
       <c r="F438">
-        <v>1</v>
+        <v>18.369058098945679</v>
       </c>
       <c r="G438">
         <v>10000000</v>
@@ -17194,10 +17194,10 @@
         <v>11</v>
       </c>
       <c r="B439" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C439" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="D439">
         <v>10000</v>
@@ -17206,7 +17206,7 @@
         <v>10000</v>
       </c>
       <c r="F439">
-        <v>1</v>
+        <v>9.8073453701572593</v>
       </c>
       <c r="G439">
         <v>10000000</v>
@@ -17223,10 +17223,10 @@
         <v>11</v>
       </c>
       <c r="B440" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C440" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="D440">
         <v>10000</v>
@@ -17235,7 +17235,7 @@
         <v>10000</v>
       </c>
       <c r="F440">
-        <v>20</v>
+        <v>9.0992337910845347</v>
       </c>
       <c r="G440">
         <v>10000000</v>
@@ -17255,7 +17255,7 @@
         <v>137</v>
       </c>
       <c r="C441" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D441">
         <v>10000</v>
@@ -17264,7 +17264,7 @@
         <v>10000</v>
       </c>
       <c r="F441">
-        <v>20</v>
+        <v>9.1925757719623018</v>
       </c>
       <c r="G441">
         <v>10000000</v>
@@ -17284,7 +17284,7 @@
         <v>137</v>
       </c>
       <c r="C442" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D442">
         <v>10000</v>
@@ -17293,7 +17293,7 @@
         <v>10000</v>
       </c>
       <c r="F442">
-        <v>20</v>
+        <v>12.35976574381486</v>
       </c>
       <c r="G442">
         <v>10000000</v>
@@ -17313,7 +17313,7 @@
         <v>137</v>
       </c>
       <c r="C443" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D443">
         <v>10000</v>
@@ -17322,7 +17322,7 @@
         <v>10000</v>
       </c>
       <c r="F443">
-        <v>20</v>
+        <v>11.26219279625214</v>
       </c>
       <c r="G443">
         <v>10000000</v>
@@ -17342,7 +17342,7 @@
         <v>137</v>
       </c>
       <c r="C444" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="D444">
         <v>10000</v>
@@ -17351,7 +17351,7 @@
         <v>10000</v>
       </c>
       <c r="F444">
-        <v>20</v>
+        <v>18.46240007982345</v>
       </c>
       <c r="G444">
         <v>10000000</v>
@@ -17371,7 +17371,7 @@
         <v>137</v>
       </c>
       <c r="C445" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D445">
         <v>10000</v>
@@ -17380,7 +17380,7 @@
         <v>10000</v>
       </c>
       <c r="F445">
-        <v>20</v>
+        <v>9.2247626619201526</v>
       </c>
       <c r="G445">
         <v>10000000</v>
@@ -17400,7 +17400,7 @@
         <v>137</v>
       </c>
       <c r="C446" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="D446">
         <v>10000</v>
@@ -17409,7 +17409,7 @@
         <v>10000</v>
       </c>
       <c r="F446">
-        <v>20</v>
+        <v>25.405112243731949</v>
       </c>
       <c r="G446">
         <v>10000000</v>
@@ -17429,7 +17429,7 @@
         <v>137</v>
       </c>
       <c r="C447" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="D447">
         <v>10000</v>
@@ -17438,7 +17438,7 @@
         <v>10000</v>
       </c>
       <c r="F447">
-        <v>20</v>
+        <v>22.923503027981621</v>
       </c>
       <c r="G447">
         <v>10000000</v>
@@ -17458,7 +17458,7 @@
         <v>137</v>
       </c>
       <c r="C448" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="D448">
         <v>10000</v>
@@ -17467,7 +17467,7 @@
         <v>10000</v>
       </c>
       <c r="F448">
-        <v>20</v>
+        <v>2043.9061365915049</v>
       </c>
       <c r="G448">
         <v>10000000</v>
@@ -17487,7 +17487,7 @@
         <v>137</v>
       </c>
       <c r="C449" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="D449">
         <v>10000</v>
@@ -17496,7 +17496,7 @@
         <v>10000</v>
       </c>
       <c r="F449">
-        <v>20</v>
+        <v>3.0545358570000789</v>
       </c>
       <c r="G449">
         <v>10000000</v>
@@ -17516,7 +17516,7 @@
         <v>137</v>
       </c>
       <c r="C450" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="D450">
         <v>10000</v>
@@ -17525,7 +17525,7 @@
         <v>10000</v>
       </c>
       <c r="F450">
-        <v>20</v>
+        <v>2028.6302386175089</v>
       </c>
       <c r="G450">
         <v>10000000</v>
@@ -17545,7 +17545,7 @@
         <v>137</v>
       </c>
       <c r="C451" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="D451">
         <v>10000</v>
@@ -17554,7 +17554,7 @@
         <v>10000</v>
       </c>
       <c r="F451">
-        <v>20</v>
+        <v>2038.1511206670409</v>
       </c>
       <c r="G451">
         <v>10000000</v>
@@ -17574,7 +17574,7 @@
         <v>137</v>
       </c>
       <c r="C452" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="D452">
         <v>10000</v>
@@ -17583,7 +17583,7 @@
         <v>10000</v>
       </c>
       <c r="F452">
-        <v>20</v>
+        <v>19.337883486677001</v>
       </c>
       <c r="G452">
         <v>10000000</v>
@@ -17600,10 +17600,10 @@
         <v>11</v>
       </c>
       <c r="B453" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C453" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="D453">
         <v>10000</v>
@@ -17612,7 +17612,7 @@
         <v>10000</v>
       </c>
       <c r="F453">
-        <v>20</v>
+        <v>14.666222150434395</v>
       </c>
       <c r="G453">
         <v>10000000</v>
@@ -17629,10 +17629,10 @@
         <v>11</v>
       </c>
       <c r="B454" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C454" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="D454">
         <v>10000</v>
@@ -17641,7 +17641,7 @@
         <v>10000</v>
       </c>
       <c r="F454">
-        <v>20</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G454">
         <v>10000000</v>
@@ -17658,10 +17658,10 @@
         <v>11</v>
       </c>
       <c r="B455" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C455" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="D455">
         <v>10000</v>
@@ -17670,7 +17670,7 @@
         <v>10000</v>
       </c>
       <c r="F455">
-        <v>20</v>
+        <v>10.325554298478661</v>
       </c>
       <c r="G455">
         <v>10000000</v>
@@ -17687,10 +17687,10 @@
         <v>11</v>
       </c>
       <c r="B456" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C456" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D456">
         <v>10000</v>
@@ -17699,7 +17699,7 @@
         <v>10000</v>
       </c>
       <c r="F456">
-        <v>20</v>
+        <v>4.8666577616271018</v>
       </c>
       <c r="G456">
         <v>10000000</v>
@@ -17716,10 +17716,10 @@
         <v>11</v>
       </c>
       <c r="B457" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C457" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D457">
         <v>10000</v>
@@ -17728,7 +17728,7 @@
         <v>10000</v>
       </c>
       <c r="F457">
-        <v>20</v>
+        <v>1.9279947084752871</v>
       </c>
       <c r="G457">
         <v>10000000</v>
@@ -17745,10 +17745,10 @@
         <v>11</v>
       </c>
       <c r="B458" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C458" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="D458">
         <v>10000</v>
@@ -17757,7 +17757,7 @@
         <v>10000</v>
       </c>
       <c r="F458">
-        <v>20</v>
+        <v>4.4514468811708214</v>
       </c>
       <c r="G458">
         <v>10000000</v>
@@ -17774,10 +17774,10 @@
         <v>11</v>
       </c>
       <c r="B459" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C459" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="D459">
         <v>10000</v>
@@ -17786,7 +17786,7 @@
         <v>10000</v>
       </c>
       <c r="F459">
-        <v>20</v>
+        <v>4.0491107566976803</v>
       </c>
       <c r="G459">
         <v>10000000</v>
@@ -17803,10 +17803,10 @@
         <v>11</v>
       </c>
       <c r="B460" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C460" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="D460">
         <v>10000</v>
@@ -17815,7 +17815,7 @@
         <v>10000</v>
       </c>
       <c r="F460">
-        <v>20</v>
+        <v>13.33180982054197</v>
       </c>
       <c r="G460">
         <v>10000000</v>
@@ -17832,10 +17832,10 @@
         <v>11</v>
       </c>
       <c r="B461" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C461" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="D461">
         <v>10000</v>
@@ -17844,7 +17844,7 @@
         <v>10000</v>
       </c>
       <c r="F461">
-        <v>20</v>
+        <v>10.537987772200481</v>
       </c>
       <c r="G461">
         <v>10000000</v>
@@ -17861,10 +17861,10 @@
         <v>11</v>
       </c>
       <c r="B462" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C462" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="D462">
         <v>10000</v>
@@ -17873,7 +17873,7 @@
         <v>10000</v>
       </c>
       <c r="F462">
-        <v>20</v>
+        <v>12.717040222347009</v>
       </c>
       <c r="G462">
         <v>10000000</v>
@@ -17893,7 +17893,7 @@
         <v>135</v>
       </c>
       <c r="C463" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D463">
         <v>10000</v>
@@ -17902,7 +17902,7 @@
         <v>10000</v>
       </c>
       <c r="F463">
-        <v>20</v>
+        <v>7.0714597237399088</v>
       </c>
       <c r="G463">
         <v>10000000</v>
@@ -17922,7 +17922,7 @@
         <v>135</v>
       </c>
       <c r="C464" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D464">
         <v>10000</v>
@@ -17931,7 +17931,7 @@
         <v>10000</v>
       </c>
       <c r="F464">
-        <v>20</v>
+        <v>5.1112781253067707</v>
       </c>
       <c r="G464">
         <v>10000000</v>
@@ -17951,7 +17951,7 @@
         <v>135</v>
       </c>
       <c r="C465" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D465">
         <v>10000</v>
@@ -17960,7 +17960,7 @@
         <v>10000</v>
       </c>
       <c r="F465">
-        <v>20</v>
+        <v>1.9247760194795021</v>
       </c>
       <c r="G465">
         <v>10000000</v>
@@ -17980,7 +17980,7 @@
         <v>135</v>
       </c>
       <c r="C466" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D466">
         <v>10000</v>
@@ -17989,7 +17989,7 @@
         <v>10000</v>
       </c>
       <c r="F466">
-        <v>20</v>
+        <v>9.7268781452626314</v>
       </c>
       <c r="G466">
         <v>10000000</v>
@@ -18009,7 +18009,7 @@
         <v>135</v>
       </c>
       <c r="C467" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="D467">
         <v>10000</v>
@@ -18018,7 +18018,7 @@
         <v>10000</v>
       </c>
       <c r="F467">
-        <v>20</v>
+        <v>19.643658941276591</v>
       </c>
       <c r="G467">
         <v>10000000</v>
@@ -18038,7 +18038,7 @@
         <v>135</v>
       </c>
       <c r="C468" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D468">
         <v>10000</v>
@@ -18047,7 +18047,7 @@
         <v>10000</v>
       </c>
       <c r="F468">
-        <v>20</v>
+        <v>16.898117227871879</v>
       </c>
       <c r="G468">
         <v>10000000</v>
@@ -18067,7 +18067,7 @@
         <v>135</v>
       </c>
       <c r="C469" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="D469">
         <v>10000</v>
@@ -18076,7 +18076,7 @@
         <v>10000</v>
       </c>
       <c r="F469">
-        <v>20</v>
+        <v>24.288227162194509</v>
       </c>
       <c r="G469">
         <v>10000000</v>
@@ -18096,7 +18096,7 @@
         <v>135</v>
       </c>
       <c r="C470" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="D470">
         <v>10000</v>
@@ -18105,7 +18105,7 @@
         <v>10000</v>
       </c>
       <c r="F470">
-        <v>20</v>
+        <v>25.20555352599327</v>
       </c>
       <c r="G470">
         <v>10000000</v>
@@ -18125,7 +18125,7 @@
         <v>135</v>
       </c>
       <c r="C471" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="D471">
         <v>10000</v>
@@ -18134,7 +18134,7 @@
         <v>10000</v>
       </c>
       <c r="F471">
-        <v>20</v>
+        <v>9.0123291881983345</v>
       </c>
       <c r="G471">
         <v>10000000</v>
@@ -18154,7 +18154,7 @@
         <v>135</v>
       </c>
       <c r="C472" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="D472">
         <v>10000</v>
@@ -18163,7 +18163,7 @@
         <v>10000</v>
       </c>
       <c r="F472">
-        <v>20</v>
+        <v>18.533211237730718</v>
       </c>
       <c r="G472">
         <v>10000000</v>
@@ -18180,10 +18180,10 @@
         <v>11</v>
       </c>
       <c r="B473" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C473" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="D473">
         <v>10000</v>
@@ -18192,7 +18192,7 @@
         <v>10000</v>
       </c>
       <c r="F473">
-        <v>20</v>
+        <v>17.958639367878849</v>
       </c>
       <c r="G473">
         <v>10000000</v>
@@ -18209,10 +18209,10 @@
         <v>11</v>
       </c>
       <c r="B474" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C474" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="D474">
         <v>10000</v>
@@ -18221,7 +18221,7 @@
         <v>10000</v>
       </c>
       <c r="F474">
-        <v>20</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G474">
         <v>10000000</v>
@@ -18238,10 +18238,10 @@
         <v>11</v>
       </c>
       <c r="B475" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C475" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D475">
         <v>10000</v>
@@ -18250,7 +18250,7 @@
         <v>10000</v>
       </c>
       <c r="F475">
-        <v>20</v>
+        <v>2029.731030254067</v>
       </c>
       <c r="G475">
         <v>10000000</v>
@@ -18267,10 +18267,10 @@
         <v>11</v>
       </c>
       <c r="B476" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C476" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="D476">
         <v>10000</v>
@@ -18279,7 +18279,7 @@
         <v>10000</v>
       </c>
       <c r="F476">
-        <v>20</v>
+        <v>2024.2721337172161</v>
       </c>
       <c r="G476">
         <v>10000000</v>
@@ -18296,10 +18296,10 @@
         <v>11</v>
       </c>
       <c r="B477" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C477" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D477">
         <v>10000</v>
@@ -18308,7 +18308,7 @@
         <v>10000</v>
       </c>
       <c r="F477">
-        <v>20</v>
+        <v>2021.333470664064</v>
       </c>
       <c r="G477">
         <v>10000000</v>
@@ -18325,10 +18325,10 @@
         <v>11</v>
       </c>
       <c r="B478" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C478" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="D478">
         <v>10000</v>
@@ -18337,7 +18337,7 @@
         <v>10000</v>
       </c>
       <c r="F478">
-        <v>20</v>
+        <v>2023.8569228367589</v>
       </c>
       <c r="G478">
         <v>10000000</v>
@@ -18354,10 +18354,10 @@
         <v>11</v>
       </c>
       <c r="B479" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C479" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D479">
         <v>10000</v>
@@ -18366,7 +18366,7 @@
         <v>10000</v>
       </c>
       <c r="F479">
-        <v>20</v>
+        <v>2023.4545867122861</v>
       </c>
       <c r="G479">
         <v>10000000</v>
@@ -18383,10 +18383,10 @@
         <v>11</v>
       </c>
       <c r="B480" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C480" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="D480">
         <v>10000</v>
@@ -18395,7 +18395,7 @@
         <v>10000</v>
       </c>
       <c r="F480">
-        <v>20</v>
+        <v>2032.73728577613</v>
       </c>
       <c r="G480">
         <v>10000000</v>
@@ -18412,10 +18412,10 @@
         <v>11</v>
       </c>
       <c r="B481" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C481" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="D481">
         <v>10000</v>
@@ -18424,7 +18424,7 @@
         <v>10000</v>
       </c>
       <c r="F481">
-        <v>20</v>
+        <v>2029.9434637277891</v>
       </c>
       <c r="G481">
         <v>10000000</v>
@@ -18441,10 +18441,10 @@
         <v>11</v>
       </c>
       <c r="B482" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C482" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="D482">
         <v>10000</v>
@@ -18453,7 +18453,7 @@
         <v>10000</v>
       </c>
       <c r="F482">
-        <v>20</v>
+        <v>2032.122516177935</v>
       </c>
       <c r="G482">
         <v>10000000</v>
@@ -18470,10 +18470,10 @@
         <v>11</v>
       </c>
       <c r="B483" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C483" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="D483">
         <v>10000</v>
@@ -18482,7 +18482,7 @@
         <v>10000</v>
       </c>
       <c r="F483">
-        <v>20</v>
+        <v>2026.4769356793281</v>
       </c>
       <c r="G483">
         <v>10000000</v>
@@ -18511,7 +18511,7 @@
         <v>10000</v>
       </c>
       <c r="F484">
-        <v>20</v>
+        <v>2024.516754080895</v>
       </c>
       <c r="G484">
         <v>10000000</v>
@@ -18531,7 +18531,7 @@
         <v>136</v>
       </c>
       <c r="C485" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D485">
         <v>10000</v>
@@ -18540,7 +18540,7 @@
         <v>10000</v>
       </c>
       <c r="F485">
-        <v>20</v>
+        <v>2021.330251975068</v>
       </c>
       <c r="G485">
         <v>10000000</v>
@@ -18560,7 +18560,7 @@
         <v>136</v>
       </c>
       <c r="C486" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D486">
         <v>10000</v>
@@ -18569,7 +18569,7 @@
         <v>10000</v>
       </c>
       <c r="F486">
-        <v>20</v>
+        <v>2029.132354100851</v>
       </c>
       <c r="G486">
         <v>10000000</v>
@@ -18589,7 +18589,7 @@
         <v>136</v>
       </c>
       <c r="C487" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D487">
         <v>10000</v>
@@ -18598,7 +18598,7 @@
         <v>10000</v>
       </c>
       <c r="F487">
-        <v>20</v>
+        <v>29.492847268379052</v>
       </c>
       <c r="G487">
         <v>10000000</v>
@@ -18618,7 +18618,7 @@
         <v>136</v>
       </c>
       <c r="C488" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D488">
         <v>10000</v>
@@ -18627,7 +18627,7 @@
         <v>10000</v>
       </c>
       <c r="F488">
-        <v>20</v>
+        <v>26.888927870788891</v>
       </c>
       <c r="G488">
         <v>10000000</v>
@@ -18647,7 +18647,7 @@
         <v>136</v>
       </c>
       <c r="C489" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D489">
         <v>10000</v>
@@ -18656,7 +18656,7 @@
         <v>10000</v>
       </c>
       <c r="F489">
-        <v>20</v>
+        <v>8.3138736761129639</v>
       </c>
       <c r="G489">
         <v>10000000</v>
@@ -18676,7 +18676,7 @@
         <v>136</v>
       </c>
       <c r="C490" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="D490">
         <v>10000</v>
@@ -18685,7 +18685,7 @@
         <v>10000</v>
       </c>
       <c r="F490">
-        <v>20</v>
+        <v>8.5520566618010641</v>
       </c>
       <c r="G490">
         <v>10000000</v>
@@ -18705,7 +18705,7 @@
         <v>136</v>
       </c>
       <c r="C491" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="D491">
         <v>10000</v>
@@ -18714,7 +18714,7 @@
         <v>10000</v>
       </c>
       <c r="F491">
-        <v>20</v>
+        <v>11.146319992403869</v>
       </c>
       <c r="G491">
         <v>10000000</v>
@@ -18734,7 +18734,7 @@
         <v>136</v>
       </c>
       <c r="C492" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D492">
         <v>10000</v>
@@ -18743,7 +18743,7 @@
         <v>10000</v>
       </c>
       <c r="F492">
-        <v>20</v>
+        <v>5.7131729675185881</v>
       </c>
       <c r="G492">
         <v>10000000</v>
@@ -18763,7 +18763,7 @@
         <v>136</v>
       </c>
       <c r="C493" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D493">
         <v>10000</v>
@@ -18772,7 +18772,7 @@
         <v>10000</v>
       </c>
       <c r="F493">
-        <v>20</v>
+        <v>19.125450012955181</v>
       </c>
       <c r="G493">
         <v>10000000</v>
@@ -18786,13 +18786,13 @@
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B494" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C494" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D494">
         <v>10000</v>
@@ -18801,7 +18801,7 @@
         <v>10000</v>
       </c>
       <c r="F494">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G494">
         <v>10000000</v>
@@ -18815,13 +18815,13 @@
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B495" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="C495" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="D495">
         <v>10000</v>
@@ -18830,7 +18830,7 @@
         <v>10000</v>
       </c>
       <c r="F495">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G495">
         <v>10000000</v>
@@ -18844,13 +18844,13 @@
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B496" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C496" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D496">
         <v>10000</v>
@@ -18859,7 +18859,7 @@
         <v>10000</v>
       </c>
       <c r="F496">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G496">
         <v>10000000</v>
@@ -18873,13 +18873,13 @@
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B497" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C497" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="D497">
         <v>10000</v>
@@ -18888,7 +18888,7 @@
         <v>10000</v>
       </c>
       <c r="F497">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G497">
         <v>10000000</v>
@@ -18902,13 +18902,13 @@
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B498" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C498" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D498">
         <v>10000</v>
@@ -18917,7 +18917,7 @@
         <v>10000</v>
       </c>
       <c r="F498">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G498">
         <v>10000000</v>
@@ -18931,13 +18931,13 @@
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B499" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C499" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D499">
         <v>10000</v>
@@ -18946,7 +18946,7 @@
         <v>10000</v>
       </c>
       <c r="F499">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G499">
         <v>10000000</v>
@@ -18960,13 +18960,13 @@
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B500" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C500" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D500">
         <v>10000</v>
@@ -18975,7 +18975,7 @@
         <v>10000</v>
       </c>
       <c r="F500">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G500">
         <v>10000000</v>
@@ -18989,13 +18989,13 @@
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B501" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C501" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D501">
         <v>10000</v>
@@ -19004,7 +19004,7 @@
         <v>10000</v>
       </c>
       <c r="F501">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G501">
         <v>10000000</v>
@@ -19018,13 +19018,13 @@
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B502" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C502" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="D502">
         <v>10000</v>
@@ -19033,7 +19033,7 @@
         <v>10000</v>
       </c>
       <c r="F502">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G502">
         <v>10000000</v>
@@ -19047,13 +19047,13 @@
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B503" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C503" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="D503">
         <v>10000</v>
@@ -19062,7 +19062,7 @@
         <v>10000</v>
       </c>
       <c r="F503">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G503">
         <v>10000000</v>
@@ -19079,10 +19079,10 @@
         <v>12</v>
       </c>
       <c r="B504" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C504" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D504">
         <v>10000</v>
@@ -19108,10 +19108,10 @@
         <v>12</v>
       </c>
       <c r="B505" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C505" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="D505">
         <v>10000</v>
@@ -19169,7 +19169,7 @@
         <v>105</v>
       </c>
       <c r="C507" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D507">
         <v>10000</v>
@@ -19198,7 +19198,7 @@
         <v>105</v>
       </c>
       <c r="C508" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D508">
         <v>10000</v>
@@ -19227,7 +19227,7 @@
         <v>105</v>
       </c>
       <c r="C509" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D509">
         <v>10000</v>
@@ -19256,7 +19256,7 @@
         <v>105</v>
       </c>
       <c r="C510" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D510">
         <v>10000</v>
@@ -19285,7 +19285,7 @@
         <v>105</v>
       </c>
       <c r="C511" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D511">
         <v>10000</v>
@@ -19314,7 +19314,7 @@
         <v>105</v>
       </c>
       <c r="C512" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="D512">
         <v>10000</v>
@@ -19343,7 +19343,7 @@
         <v>105</v>
       </c>
       <c r="C513" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="D513">
         <v>10000</v>
@@ -19372,7 +19372,7 @@
         <v>105</v>
       </c>
       <c r="C514" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D514">
         <v>10000</v>
@@ -19401,7 +19401,7 @@
         <v>105</v>
       </c>
       <c r="C515" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D515">
         <v>10000</v>
@@ -19427,10 +19427,10 @@
         <v>12</v>
       </c>
       <c r="B516" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C516" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="D516">
         <v>10000</v>
@@ -19456,10 +19456,10 @@
         <v>12</v>
       </c>
       <c r="B517" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C517" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="D517">
         <v>10000</v>
@@ -19485,10 +19485,10 @@
         <v>12</v>
       </c>
       <c r="B518" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C518" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D518">
         <v>10000</v>
@@ -19514,10 +19514,10 @@
         <v>12</v>
       </c>
       <c r="B519" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C519" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="D519">
         <v>10000</v>
@@ -19543,10 +19543,10 @@
         <v>12</v>
       </c>
       <c r="B520" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C520" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D520">
         <v>10000</v>
@@ -19572,10 +19572,10 @@
         <v>12</v>
       </c>
       <c r="B521" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C521" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D521">
         <v>10000</v>
@@ -19601,10 +19601,10 @@
         <v>12</v>
       </c>
       <c r="B522" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C522" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D522">
         <v>10000</v>
@@ -19630,10 +19630,10 @@
         <v>12</v>
       </c>
       <c r="B523" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C523" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D523">
         <v>10000</v>
@@ -19659,10 +19659,10 @@
         <v>12</v>
       </c>
       <c r="B524" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C524" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="D524">
         <v>10000</v>
@@ -19688,10 +19688,10 @@
         <v>12</v>
       </c>
       <c r="B525" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C525" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="D525">
         <v>10000</v>
@@ -19717,10 +19717,10 @@
         <v>12</v>
       </c>
       <c r="B526" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C526" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="D526">
         <v>10000</v>
@@ -19746,10 +19746,10 @@
         <v>12</v>
       </c>
       <c r="B527" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C527" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="D527">
         <v>10000</v>
@@ -19807,7 +19807,7 @@
         <v>108</v>
       </c>
       <c r="C529" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D529">
         <v>10000</v>
@@ -19836,7 +19836,7 @@
         <v>108</v>
       </c>
       <c r="C530" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D530">
         <v>10000</v>
@@ -19865,7 +19865,7 @@
         <v>108</v>
       </c>
       <c r="C531" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D531">
         <v>10000</v>
@@ -19894,7 +19894,7 @@
         <v>108</v>
       </c>
       <c r="C532" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D532">
         <v>10000</v>
@@ -19923,7 +19923,7 @@
         <v>108</v>
       </c>
       <c r="C533" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D533">
         <v>10000</v>
@@ -19952,7 +19952,7 @@
         <v>108</v>
       </c>
       <c r="C534" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="D534">
         <v>10000</v>
@@ -19981,7 +19981,7 @@
         <v>108</v>
       </c>
       <c r="C535" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="D535">
         <v>10000</v>
@@ -20010,7 +20010,7 @@
         <v>108</v>
       </c>
       <c r="C536" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D536">
         <v>10000</v>
@@ -20039,7 +20039,7 @@
         <v>108</v>
       </c>
       <c r="C537" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D537">
         <v>10000</v>
@@ -20065,10 +20065,10 @@
         <v>12</v>
       </c>
       <c r="B538" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C538" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="D538">
         <v>10000</v>
@@ -20094,10 +20094,10 @@
         <v>12</v>
       </c>
       <c r="B539" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C539" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="D539">
         <v>10000</v>
@@ -20123,10 +20123,10 @@
         <v>12</v>
       </c>
       <c r="B540" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C540" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D540">
         <v>10000</v>
@@ -20152,10 +20152,10 @@
         <v>12</v>
       </c>
       <c r="B541" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C541" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="D541">
         <v>10000</v>
@@ -20181,10 +20181,10 @@
         <v>12</v>
       </c>
       <c r="B542" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C542" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D542">
         <v>10000</v>
@@ -20210,10 +20210,10 @@
         <v>12</v>
       </c>
       <c r="B543" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C543" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D543">
         <v>10000</v>
@@ -20239,10 +20239,10 @@
         <v>12</v>
       </c>
       <c r="B544" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C544" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D544">
         <v>10000</v>
@@ -20268,10 +20268,10 @@
         <v>12</v>
       </c>
       <c r="B545" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C545" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D545">
         <v>10000</v>
@@ -20297,10 +20297,10 @@
         <v>12</v>
       </c>
       <c r="B546" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C546" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="D546">
         <v>10000</v>
@@ -20326,10 +20326,10 @@
         <v>12</v>
       </c>
       <c r="B547" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C547" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="D547">
         <v>10000</v>
@@ -20355,10 +20355,10 @@
         <v>12</v>
       </c>
       <c r="B548" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C548" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="D548">
         <v>10000</v>
@@ -20384,10 +20384,10 @@
         <v>12</v>
       </c>
       <c r="B549" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C549" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="D549">
         <v>10000</v>
@@ -20445,7 +20445,7 @@
         <v>111</v>
       </c>
       <c r="C551" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D551">
         <v>10000</v>
@@ -20474,7 +20474,7 @@
         <v>111</v>
       </c>
       <c r="C552" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D552">
         <v>10000</v>
@@ -20503,7 +20503,7 @@
         <v>111</v>
       </c>
       <c r="C553" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D553">
         <v>10000</v>
@@ -20532,7 +20532,7 @@
         <v>111</v>
       </c>
       <c r="C554" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D554">
         <v>10000</v>
@@ -20561,7 +20561,7 @@
         <v>111</v>
       </c>
       <c r="C555" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D555">
         <v>10000</v>
@@ -20590,7 +20590,7 @@
         <v>111</v>
       </c>
       <c r="C556" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="D556">
         <v>10000</v>
@@ -20619,7 +20619,7 @@
         <v>111</v>
       </c>
       <c r="C557" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="D557">
         <v>10000</v>
@@ -20648,7 +20648,7 @@
         <v>111</v>
       </c>
       <c r="C558" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D558">
         <v>10000</v>
@@ -20677,7 +20677,7 @@
         <v>111</v>
       </c>
       <c r="C559" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D559">
         <v>10000</v>
@@ -20703,10 +20703,10 @@
         <v>12</v>
       </c>
       <c r="B560" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C560" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="D560">
         <v>10000</v>
@@ -20732,10 +20732,10 @@
         <v>12</v>
       </c>
       <c r="B561" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C561" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="D561">
         <v>10000</v>
@@ -20761,10 +20761,10 @@
         <v>12</v>
       </c>
       <c r="B562" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C562" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D562">
         <v>10000</v>
@@ -20790,10 +20790,10 @@
         <v>12</v>
       </c>
       <c r="B563" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C563" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="D563">
         <v>10000</v>
@@ -20819,10 +20819,10 @@
         <v>12</v>
       </c>
       <c r="B564" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C564" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D564">
         <v>10000</v>
@@ -20848,10 +20848,10 @@
         <v>12</v>
       </c>
       <c r="B565" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C565" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D565">
         <v>10000</v>
@@ -20877,10 +20877,10 @@
         <v>12</v>
       </c>
       <c r="B566" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C566" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D566">
         <v>10000</v>
@@ -20906,10 +20906,10 @@
         <v>12</v>
       </c>
       <c r="B567" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C567" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D567">
         <v>10000</v>
@@ -20935,10 +20935,10 @@
         <v>12</v>
       </c>
       <c r="B568" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C568" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="D568">
         <v>10000</v>
@@ -20964,10 +20964,10 @@
         <v>12</v>
       </c>
       <c r="B569" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C569" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="D569">
         <v>10000</v>
@@ -20993,10 +20993,10 @@
         <v>12</v>
       </c>
       <c r="B570" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C570" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="D570">
         <v>10000</v>
@@ -21022,10 +21022,10 @@
         <v>12</v>
       </c>
       <c r="B571" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C571" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="D571">
         <v>10000</v>
@@ -21083,7 +21083,7 @@
         <v>114</v>
       </c>
       <c r="C573" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D573">
         <v>10000</v>
@@ -21112,7 +21112,7 @@
         <v>114</v>
       </c>
       <c r="C574" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D574">
         <v>10000</v>
@@ -21141,7 +21141,7 @@
         <v>114</v>
       </c>
       <c r="C575" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D575">
         <v>10000</v>
@@ -21170,7 +21170,7 @@
         <v>114</v>
       </c>
       <c r="C576" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D576">
         <v>10000</v>
@@ -21199,7 +21199,7 @@
         <v>114</v>
       </c>
       <c r="C577" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="D577">
         <v>10000</v>
@@ -21228,7 +21228,7 @@
         <v>114</v>
       </c>
       <c r="C578" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="D578">
         <v>10000</v>
@@ -21257,7 +21257,7 @@
         <v>114</v>
       </c>
       <c r="C579" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="D579">
         <v>10000</v>
@@ -21286,7 +21286,7 @@
         <v>114</v>
       </c>
       <c r="C580" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="D580">
         <v>10000</v>
@@ -21312,10 +21312,10 @@
         <v>12</v>
       </c>
       <c r="B581" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C581" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="D581">
         <v>10000</v>
@@ -21341,10 +21341,10 @@
         <v>12</v>
       </c>
       <c r="B582" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C582" t="s">
-        <v>31</v>
+        <v>117</v>
       </c>
       <c r="D582">
         <v>10000</v>
@@ -21370,10 +21370,10 @@
         <v>12</v>
       </c>
       <c r="B583" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C583" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D583">
         <v>10000</v>
@@ -21399,10 +21399,10 @@
         <v>12</v>
       </c>
       <c r="B584" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C584" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D584">
         <v>10000</v>
@@ -21428,10 +21428,10 @@
         <v>12</v>
       </c>
       <c r="B585" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C585" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="D585">
         <v>10000</v>
@@ -21457,10 +21457,10 @@
         <v>12</v>
       </c>
       <c r="B586" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C586" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D586">
         <v>10000</v>
@@ -21486,10 +21486,10 @@
         <v>12</v>
       </c>
       <c r="B587" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C587" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="D587">
         <v>10000</v>
@@ -21515,10 +21515,10 @@
         <v>12</v>
       </c>
       <c r="B588" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C588" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D588">
         <v>10000</v>
@@ -21544,10 +21544,10 @@
         <v>12</v>
       </c>
       <c r="B589" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C589" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="D589">
         <v>10000</v>
@@ -21573,10 +21573,10 @@
         <v>12</v>
       </c>
       <c r="B590" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C590" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="D590">
         <v>10000</v>
@@ -21602,10 +21602,10 @@
         <v>12</v>
       </c>
       <c r="B591" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C591" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="D591">
         <v>10000</v>
@@ -21631,10 +21631,10 @@
         <v>12</v>
       </c>
       <c r="B592" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C592" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="D592">
         <v>10000</v>
@@ -21660,10 +21660,10 @@
         <v>12</v>
       </c>
       <c r="B593" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C593" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D593">
         <v>10000</v>
@@ -21692,7 +21692,7 @@
         <v>117</v>
       </c>
       <c r="C594" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D594">
         <v>10000</v>
@@ -21721,7 +21721,7 @@
         <v>117</v>
       </c>
       <c r="C595" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D595">
         <v>10000</v>
@@ -21750,7 +21750,7 @@
         <v>117</v>
       </c>
       <c r="C596" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D596">
         <v>10000</v>
@@ -21779,7 +21779,7 @@
         <v>117</v>
       </c>
       <c r="C597" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D597">
         <v>10000</v>
@@ -21808,7 +21808,7 @@
         <v>117</v>
       </c>
       <c r="C598" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D598">
         <v>10000</v>
@@ -21837,7 +21837,7 @@
         <v>117</v>
       </c>
       <c r="C599" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="D599">
         <v>10000</v>
@@ -21866,7 +21866,7 @@
         <v>117</v>
       </c>
       <c r="C600" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="D600">
         <v>10000</v>
@@ -21895,7 +21895,7 @@
         <v>117</v>
       </c>
       <c r="C601" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="D601">
         <v>10000</v>
@@ -21924,7 +21924,7 @@
         <v>117</v>
       </c>
       <c r="C602" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="D602">
         <v>10000</v>
@@ -21950,10 +21950,10 @@
         <v>12</v>
       </c>
       <c r="B603" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="C603" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="D603">
         <v>10000</v>
@@ -21979,7 +21979,7 @@
         <v>12</v>
       </c>
       <c r="B604" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C604" t="s">
         <v>31</v>
@@ -22008,10 +22008,10 @@
         <v>12</v>
       </c>
       <c r="B605" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C605" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D605">
         <v>10000</v>
@@ -22037,10 +22037,10 @@
         <v>12</v>
       </c>
       <c r="B606" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C606" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D606">
         <v>10000</v>
@@ -22066,10 +22066,10 @@
         <v>12</v>
       </c>
       <c r="B607" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C607" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D607">
         <v>10000</v>
@@ -22095,10 +22095,10 @@
         <v>12</v>
       </c>
       <c r="B608" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C608" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="D608">
         <v>10000</v>
@@ -22124,10 +22124,10 @@
         <v>12</v>
       </c>
       <c r="B609" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C609" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="D609">
         <v>10000</v>
@@ -22153,10 +22153,10 @@
         <v>12</v>
       </c>
       <c r="B610" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C610" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="D610">
         <v>10000</v>
@@ -22182,10 +22182,10 @@
         <v>12</v>
       </c>
       <c r="B611" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C611" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="D611">
         <v>10000</v>
@@ -22211,10 +22211,10 @@
         <v>12</v>
       </c>
       <c r="B612" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C612" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="D612">
         <v>10000</v>
@@ -22240,10 +22240,10 @@
         <v>12</v>
       </c>
       <c r="B613" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C613" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="D613">
         <v>10000</v>
@@ -22269,10 +22269,10 @@
         <v>12</v>
       </c>
       <c r="B614" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="C614" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D614">
         <v>10000</v>
@@ -22298,10 +22298,10 @@
         <v>12</v>
       </c>
       <c r="B615" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C615" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="D615">
         <v>10000</v>
@@ -22330,7 +22330,7 @@
         <v>137</v>
       </c>
       <c r="C616" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D616">
         <v>10000</v>
@@ -22359,7 +22359,7 @@
         <v>137</v>
       </c>
       <c r="C617" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="D617">
         <v>10000</v>
@@ -22388,7 +22388,7 @@
         <v>137</v>
       </c>
       <c r="C618" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="D618">
         <v>10000</v>
@@ -22417,7 +22417,7 @@
         <v>137</v>
       </c>
       <c r="C619" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D619">
         <v>10000</v>
@@ -22446,7 +22446,7 @@
         <v>137</v>
       </c>
       <c r="C620" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="D620">
         <v>10000</v>
@@ -22475,7 +22475,7 @@
         <v>137</v>
       </c>
       <c r="C621" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="D621">
         <v>10000</v>
@@ -22504,7 +22504,7 @@
         <v>137</v>
       </c>
       <c r="C622" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="D622">
         <v>10000</v>
@@ -22533,7 +22533,7 @@
         <v>137</v>
       </c>
       <c r="C623" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="D623">
         <v>10000</v>
@@ -22559,10 +22559,10 @@
         <v>12</v>
       </c>
       <c r="B624" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C624" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="D624">
         <v>10000</v>
@@ -22588,10 +22588,10 @@
         <v>12</v>
       </c>
       <c r="B625" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C625" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D625">
         <v>10000</v>
@@ -22617,7 +22617,7 @@
         <v>12</v>
       </c>
       <c r="B626" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C626" t="s">
         <v>31</v>
@@ -22646,10 +22646,10 @@
         <v>12</v>
       </c>
       <c r="B627" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C627" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D627">
         <v>10000</v>
@@ -22675,10 +22675,10 @@
         <v>12</v>
       </c>
       <c r="B628" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C628" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D628">
         <v>10000</v>
@@ -22704,10 +22704,10 @@
         <v>12</v>
       </c>
       <c r="B629" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C629" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D629">
         <v>10000</v>
@@ -22733,10 +22733,10 @@
         <v>12</v>
       </c>
       <c r="B630" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C630" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="D630">
         <v>10000</v>
@@ -22762,10 +22762,10 @@
         <v>12</v>
       </c>
       <c r="B631" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C631" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="D631">
         <v>10000</v>
@@ -22791,10 +22791,10 @@
         <v>12</v>
       </c>
       <c r="B632" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C632" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="D632">
         <v>10000</v>
@@ -22820,10 +22820,10 @@
         <v>12</v>
       </c>
       <c r="B633" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C633" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="D633">
         <v>10000</v>
@@ -22849,10 +22849,10 @@
         <v>12</v>
       </c>
       <c r="B634" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C634" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="D634">
         <v>10000</v>
@@ -22878,10 +22878,10 @@
         <v>12</v>
       </c>
       <c r="B635" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C635" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="D635">
         <v>10000</v>
@@ -22907,10 +22907,10 @@
         <v>12</v>
       </c>
       <c r="B636" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C636" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="D636">
         <v>10000</v>
@@ -22936,10 +22936,10 @@
         <v>12</v>
       </c>
       <c r="B637" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C637" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="D637">
         <v>10000</v>
@@ -22968,7 +22968,7 @@
         <v>135</v>
       </c>
       <c r="C638" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D638">
         <v>10000</v>
@@ -22997,7 +22997,7 @@
         <v>135</v>
       </c>
       <c r="C639" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="D639">
         <v>10000</v>
@@ -23026,7 +23026,7 @@
         <v>135</v>
       </c>
       <c r="C640" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="D640">
         <v>10000</v>
@@ -23055,7 +23055,7 @@
         <v>135</v>
       </c>
       <c r="C641" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D641">
         <v>10000</v>
@@ -23084,7 +23084,7 @@
         <v>135</v>
       </c>
       <c r="C642" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="D642">
         <v>10000</v>
@@ -23113,7 +23113,7 @@
         <v>135</v>
       </c>
       <c r="C643" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="D643">
         <v>10000</v>
@@ -23142,7 +23142,7 @@
         <v>135</v>
       </c>
       <c r="C644" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="D644">
         <v>10000</v>
@@ -23168,10 +23168,10 @@
         <v>12</v>
       </c>
       <c r="B645" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C645" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="D645">
         <v>10000</v>
@@ -23197,10 +23197,10 @@
         <v>12</v>
       </c>
       <c r="B646" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C646" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="D646">
         <v>10000</v>
@@ -23226,10 +23226,10 @@
         <v>12</v>
       </c>
       <c r="B647" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C647" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D647">
         <v>10000</v>
@@ -23255,10 +23255,10 @@
         <v>12</v>
       </c>
       <c r="B648" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C648" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D648">
         <v>10000</v>
@@ -23284,10 +23284,10 @@
         <v>12</v>
       </c>
       <c r="B649" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C649" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D649">
         <v>10000</v>
@@ -23313,10 +23313,10 @@
         <v>12</v>
       </c>
       <c r="B650" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C650" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D650">
         <v>10000</v>
@@ -23342,10 +23342,10 @@
         <v>12</v>
       </c>
       <c r="B651" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C651" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="D651">
         <v>10000</v>
@@ -23371,10 +23371,10 @@
         <v>12</v>
       </c>
       <c r="B652" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C652" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="D652">
         <v>10000</v>
@@ -23400,10 +23400,10 @@
         <v>12</v>
       </c>
       <c r="B653" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C653" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="D653">
         <v>10000</v>
@@ -23429,10 +23429,10 @@
         <v>12</v>
       </c>
       <c r="B654" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C654" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="D654">
         <v>10000</v>
@@ -23458,10 +23458,10 @@
         <v>12</v>
       </c>
       <c r="B655" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C655" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="D655">
         <v>10000</v>
@@ -23487,10 +23487,10 @@
         <v>12</v>
       </c>
       <c r="B656" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C656" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="D656">
         <v>10000</v>
@@ -23516,10 +23516,10 @@
         <v>12</v>
       </c>
       <c r="B657" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C657" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="D657">
         <v>10000</v>
@@ -23545,10 +23545,10 @@
         <v>12</v>
       </c>
       <c r="B658" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C658" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D658">
         <v>10000</v>
@@ -23577,7 +23577,7 @@
         <v>136</v>
       </c>
       <c r="C659" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D659">
         <v>10000</v>
@@ -23606,7 +23606,7 @@
         <v>136</v>
       </c>
       <c r="C660" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="D660">
         <v>10000</v>
@@ -23635,7 +23635,7 @@
         <v>136</v>
       </c>
       <c r="C661" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="D661">
         <v>10000</v>
@@ -23664,7 +23664,7 @@
         <v>136</v>
       </c>
       <c r="C662" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D662">
         <v>10000</v>
@@ -23693,7 +23693,7 @@
         <v>136</v>
       </c>
       <c r="C663" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="D663">
         <v>10000</v>
@@ -23722,7 +23722,7 @@
         <v>136</v>
       </c>
       <c r="C664" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="D664">
         <v>10000</v>
@@ -23751,7 +23751,7 @@
         <v>136</v>
       </c>
       <c r="C665" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="D665">
         <v>10000</v>
@@ -23780,7 +23780,7 @@
         <v>136</v>
       </c>
       <c r="C666" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="D666">
         <v>10000</v>
@@ -23803,13 +23803,13 @@
     </row>
     <row r="667" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B667" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="C667" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="D667">
         <v>10000</v>
@@ -23818,7 +23818,7 @@
         <v>10000</v>
       </c>
       <c r="F667">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G667">
         <v>10000000</v>
@@ -23832,13 +23832,13 @@
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B668" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C668" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="D668">
         <v>10000</v>
@@ -23847,7 +23847,7 @@
         <v>10000</v>
       </c>
       <c r="F668">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G668">
         <v>10000000</v>
@@ -23861,13 +23861,13 @@
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B669" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C669" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="D669">
         <v>10000</v>
@@ -23876,7 +23876,7 @@
         <v>10000</v>
       </c>
       <c r="F669">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G669">
         <v>10000000</v>
@@ -23890,13 +23890,13 @@
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B670" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="C670" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="D670">
         <v>10000</v>
@@ -23905,7 +23905,7 @@
         <v>10000</v>
       </c>
       <c r="F670">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G670">
         <v>10000000</v>
@@ -23919,13 +23919,13 @@
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B671" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C671" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="D671">
         <v>10000</v>
@@ -23934,7 +23934,7 @@
         <v>10000</v>
       </c>
       <c r="F671">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G671">
         <v>10000000</v>
@@ -23948,13 +23948,13 @@
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B672" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C672" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D672">
         <v>10000</v>
@@ -23963,7 +23963,7 @@
         <v>10000</v>
       </c>
       <c r="F672">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G672">
         <v>10000000</v>
@@ -23977,13 +23977,13 @@
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B673" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C673" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D673">
         <v>10000</v>
@@ -23992,7 +23992,7 @@
         <v>10000</v>
       </c>
       <c r="F673">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G673">
         <v>10000000</v>
@@ -24006,13 +24006,13 @@
     </row>
     <row r="674" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B674" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C674" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D674">
         <v>10000</v>
@@ -24021,7 +24021,7 @@
         <v>10000</v>
       </c>
       <c r="F674">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G674">
         <v>10000000</v>
@@ -24035,13 +24035,13 @@
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B675" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C675" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D675">
         <v>10000</v>
@@ -24050,7 +24050,7 @@
         <v>10000</v>
       </c>
       <c r="F675">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G675">
         <v>10000000</v>
@@ -24064,13 +24064,13 @@
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B676" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C676" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D676">
         <v>10000</v>
@@ -24079,7 +24079,7 @@
         <v>10000</v>
       </c>
       <c r="F676">
-        <v>100</v>
+        <v>17.659328711747538</v>
       </c>
       <c r="G676">
         <v>10000000</v>
@@ -24093,13 +24093,13 @@
     </row>
     <row r="677" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B677" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C677" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D677">
         <v>10000</v>
@@ -24108,7 +24108,7 @@
         <v>10000</v>
       </c>
       <c r="F677">
-        <v>100</v>
+        <v>25.142095115030386</v>
       </c>
       <c r="G677">
         <v>10000000</v>
@@ -24122,13 +24122,13 @@
     </row>
     <row r="678" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B678" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C678" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D678">
         <v>10000</v>
@@ -24137,7 +24137,7 @@
         <v>10000</v>
       </c>
       <c r="F678">
-        <v>100</v>
+        <v>25.142095115030386</v>
       </c>
       <c r="G678">
         <v>10000000</v>
@@ -24154,10 +24154,10 @@
         <v>11</v>
       </c>
       <c r="B679" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C679" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D679">
         <v>10000</v>
@@ -24166,7 +24166,7 @@
         <v>10000</v>
       </c>
       <c r="F679">
-        <v>1</v>
+        <v>14.965532806565706</v>
       </c>
       <c r="G679">
         <v>10000000</v>
@@ -24183,10 +24183,10 @@
         <v>11</v>
       </c>
       <c r="B680" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C680" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D680">
         <v>10000</v>
@@ -24195,7 +24195,7 @@
         <v>10000</v>
       </c>
       <c r="F680">
-        <v>1</v>
+        <v>25.142095115030386</v>
       </c>
       <c r="G680">
         <v>10000000</v>
@@ -24212,10 +24212,10 @@
         <v>11</v>
       </c>
       <c r="B681" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C681" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D681">
         <v>10000</v>
@@ -24224,7 +24224,7 @@
         <v>10000</v>
       </c>
       <c r="F681">
-        <v>1</v>
+        <v>25.142095115030386</v>
       </c>
       <c r="G681">
         <v>10000000</v>
@@ -24241,10 +24241,10 @@
         <v>11</v>
       </c>
       <c r="B682" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C682" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D682">
         <v>10000</v>
@@ -24253,7 +24253,7 @@
         <v>10000</v>
       </c>
       <c r="F682">
-        <v>1</v>
+        <v>17.958639367878849</v>
       </c>
       <c r="G682">
         <v>10000000</v>
@@ -24267,13 +24267,13 @@
     </row>
     <row r="683" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B683" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="C683" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D683">
         <v>10000</v>
@@ -24282,7 +24282,7 @@
         <v>10000</v>
       </c>
       <c r="F683">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G683">
         <v>10000000</v>
@@ -24296,13 +24296,13 @@
     </row>
     <row r="684" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B684" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C684" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D684">
         <v>10000</v>
@@ -24311,7 +24311,7 @@
         <v>10000</v>
       </c>
       <c r="F684">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G684">
         <v>10000000</v>
@@ -24325,13 +24325,13 @@
     </row>
     <row r="685" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B685" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C685" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D685">
         <v>10000</v>
@@ -24340,7 +24340,7 @@
         <v>10000</v>
       </c>
       <c r="F685">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G685">
         <v>10000000</v>
@@ -24354,13 +24354,13 @@
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B686" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="C686" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D686">
         <v>10000</v>
@@ -24369,7 +24369,7 @@
         <v>10000</v>
       </c>
       <c r="F686">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G686">
         <v>10000000</v>
@@ -24383,13 +24383,13 @@
     </row>
     <row r="687" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B687" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="C687" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D687">
         <v>10000</v>
@@ -24398,7 +24398,7 @@
         <v>10000</v>
       </c>
       <c r="F687">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G687">
         <v>10000000</v>
@@ -24412,13 +24412,13 @@
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B688" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C688" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D688">
         <v>10000</v>
@@ -24427,7 +24427,7 @@
         <v>10000</v>
       </c>
       <c r="F688">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G688">
         <v>10000000</v>
@@ -24441,13 +24441,13 @@
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B689" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C689" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D689">
         <v>10000</v>
@@ -24456,7 +24456,7 @@
         <v>10000</v>
       </c>
       <c r="F689">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G689">
         <v>10000000</v>
@@ -24470,13 +24470,13 @@
     </row>
     <row r="690" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B690" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="C690" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D690">
         <v>10000</v>
@@ -24485,7 +24485,7 @@
         <v>10000</v>
       </c>
       <c r="F690">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G690">
         <v>10000000</v>
@@ -24499,13 +24499,13 @@
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B691" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C691" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D691">
         <v>10000</v>
@@ -24514,7 +24514,7 @@
         <v>10000</v>
       </c>
       <c r="F691">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G691">
         <v>10000000</v>
@@ -24528,13 +24528,13 @@
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B692" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C692" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D692">
         <v>10000</v>
@@ -24543,7 +24543,7 @@
         <v>10000</v>
       </c>
       <c r="F692">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G692">
         <v>10000000</v>
@@ -24557,13 +24557,13 @@
     </row>
     <row r="693" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B693" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C693" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D693">
         <v>10000</v>
@@ -24572,7 +24572,7 @@
         <v>10000</v>
       </c>
       <c r="F693">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G693">
         <v>10000000</v>
@@ -24586,22 +24586,22 @@
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B694" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C694" t="s">
+        <v>118</v>
+      </c>
+      <c r="D694">
+        <v>10000</v>
+      </c>
+      <c r="E694">
+        <v>10000</v>
+      </c>
+      <c r="F694">
         <v>100</v>
-      </c>
-      <c r="D694">
-        <v>10000</v>
-      </c>
-      <c r="E694">
-        <v>10000</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
       </c>
       <c r="G694">
         <v>10000000</v>
@@ -24618,10 +24618,10 @@
         <v>12</v>
       </c>
       <c r="B695" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C695" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D695">
         <v>10000</v>
@@ -24647,10 +24647,10 @@
         <v>12</v>
       </c>
       <c r="B696" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C696" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D696">
         <v>10000</v>
@@ -24676,10 +24676,10 @@
         <v>12</v>
       </c>
       <c r="B697" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C697" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D697">
         <v>10000</v>
@@ -24705,10 +24705,10 @@
         <v>12</v>
       </c>
       <c r="B698" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C698" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D698">
         <v>10000</v>
@@ -24731,13 +24731,13 @@
     </row>
     <row r="699" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B699" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="C699" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D699">
         <v>10000</v>
@@ -24746,7 +24746,7 @@
         <v>10000</v>
       </c>
       <c r="F699">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G699">
         <v>10000000</v>
@@ -24760,22 +24760,22 @@
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B700" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="C700" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D700">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E700">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F700">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G700">
         <v>10000000</v>
@@ -24789,13 +24789,13 @@
     </row>
     <row r="701" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B701" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C701" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D701">
         <v>10000</v>
@@ -24804,7 +24804,7 @@
         <v>10000</v>
       </c>
       <c r="F701">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G701">
         <v>10000000</v>
@@ -24818,13 +24818,13 @@
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B702" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="C702" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="D702">
         <v>10000</v>
@@ -24833,7 +24833,7 @@
         <v>10000</v>
       </c>
       <c r="F702">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G702">
         <v>10000000</v>
@@ -24847,22 +24847,22 @@
     </row>
     <row r="703" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B703" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C703" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D703">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E703">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F703">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G703">
         <v>10000000</v>
@@ -24876,13 +24876,13 @@
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B704" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="C704" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="D704">
         <v>10000</v>
@@ -24891,7 +24891,7 @@
         <v>10000</v>
       </c>
       <c r="F704">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G704">
         <v>10000000</v>
@@ -24905,13 +24905,13 @@
     </row>
     <row r="705" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B705" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C705" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D705">
         <v>10000</v>
@@ -24920,7 +24920,7 @@
         <v>10000</v>
       </c>
       <c r="F705">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G705">
         <v>10000000</v>
@@ -24934,22 +24934,22 @@
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B706" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C706" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D706">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E706">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="F706">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G706">
         <v>10000000</v>
@@ -24963,13 +24963,13 @@
     </row>
     <row r="707" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B707" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="C707" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D707">
         <v>10000</v>
@@ -24978,7 +24978,7 @@
         <v>10000</v>
       </c>
       <c r="F707">
-        <v>100</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G707">
         <v>10000000</v>
@@ -24992,13 +24992,13 @@
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B708" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C708" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D708">
         <v>10000</v>
@@ -25007,7 +25007,7 @@
         <v>10000</v>
       </c>
       <c r="F708">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G708">
         <v>10000000</v>
@@ -25021,10 +25021,10 @@
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B709" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C709" t="s">
         <v>121</v>
@@ -25036,7 +25036,7 @@
         <v>10000</v>
       </c>
       <c r="F709">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G709">
         <v>10000000</v>
@@ -25050,13 +25050,13 @@
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B710" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C710" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D710">
         <v>10000</v>
@@ -25065,7 +25065,7 @@
         <v>10000</v>
       </c>
       <c r="F710">
-        <v>100</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G710">
         <v>10000000</v>
@@ -25082,10 +25082,10 @@
         <v>11</v>
       </c>
       <c r="B711" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C711" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D711">
         <v>10000</v>
@@ -25094,7 +25094,7 @@
         <v>10000</v>
       </c>
       <c r="F711">
-        <v>1</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G711">
         <v>10000000</v>
@@ -25111,19 +25111,19 @@
         <v>11</v>
       </c>
       <c r="B712" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C712" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="D712">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E712">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="F712">
-        <v>1</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G712">
         <v>10000000</v>
@@ -25140,10 +25140,10 @@
         <v>11</v>
       </c>
       <c r="B713" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C713" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D713">
         <v>10000</v>
@@ -25152,7 +25152,7 @@
         <v>10000</v>
       </c>
       <c r="F713">
-        <v>1</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G713">
         <v>10000000</v>
@@ -25169,10 +25169,10 @@
         <v>11</v>
       </c>
       <c r="B714" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C714" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D714">
         <v>10000</v>
@@ -25181,7 +25181,7 @@
         <v>10000</v>
       </c>
       <c r="F714">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G714">
         <v>10000000</v>
@@ -25198,19 +25198,19 @@
         <v>11</v>
       </c>
       <c r="B715" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C715" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="D715">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E715">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="F715">
-        <v>1</v>
+        <v>8.5303536997424505</v>
       </c>
       <c r="G715">
         <v>10000000</v>
@@ -25227,10 +25227,10 @@
         <v>11</v>
       </c>
       <c r="B716" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C716" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D716">
         <v>10000</v>
@@ -25239,7 +25239,7 @@
         <v>10000</v>
       </c>
       <c r="F716">
-        <v>1</v>
+        <v>2.2178919619330402</v>
       </c>
       <c r="G716">
         <v>10000000</v>
@@ -25253,13 +25253,13 @@
     </row>
     <row r="717" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B717" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C717" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D717">
         <v>10000</v>
@@ -25268,7 +25268,7 @@
         <v>10000</v>
       </c>
       <c r="F717">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G717">
         <v>10000000</v>
@@ -25282,22 +25282,22 @@
     </row>
     <row r="718" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B718" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C718" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D718">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E718">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="F718">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G718">
         <v>10000000</v>
@@ -25311,13 +25311,13 @@
     </row>
     <row r="719" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B719" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C719" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D719">
         <v>10000</v>
@@ -25326,7 +25326,7 @@
         <v>10000</v>
       </c>
       <c r="F719">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G719">
         <v>10000000</v>
@@ -25340,13 +25340,13 @@
     </row>
     <row r="720" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B720" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C720" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D720">
         <v>10000</v>
@@ -25355,7 +25355,7 @@
         <v>10000</v>
       </c>
       <c r="F720">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G720">
         <v>10000000</v>
@@ -25369,13 +25369,13 @@
     </row>
     <row r="721" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B721" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C721" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D721">
         <v>10000</v>
@@ -25384,7 +25384,7 @@
         <v>10000</v>
       </c>
       <c r="F721">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G721">
         <v>10000000</v>
@@ -25398,13 +25398,13 @@
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B722" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C722" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D722">
         <v>10000</v>
@@ -25413,7 +25413,7 @@
         <v>10000</v>
       </c>
       <c r="F722">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G722">
         <v>10000000</v>
@@ -25427,13 +25427,13 @@
     </row>
     <row r="723" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B723" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C723" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D723">
         <v>10000</v>
@@ -25442,7 +25442,7 @@
         <v>10000</v>
       </c>
       <c r="F723">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G723">
         <v>10000000</v>
@@ -25456,13 +25456,13 @@
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B724" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C724" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D724">
         <v>10000</v>
@@ -25471,7 +25471,7 @@
         <v>10000</v>
       </c>
       <c r="F724">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G724">
         <v>10000000</v>
@@ -25485,22 +25485,22 @@
     </row>
     <row r="725" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B725" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="C725" t="s">
+        <v>137</v>
+      </c>
+      <c r="D725">
+        <v>10000</v>
+      </c>
+      <c r="E725">
+        <v>10000</v>
+      </c>
+      <c r="F725">
         <v>100</v>
-      </c>
-      <c r="D725">
-        <v>10000</v>
-      </c>
-      <c r="E725">
-        <v>10000</v>
-      </c>
-      <c r="F725">
-        <v>1</v>
       </c>
       <c r="G725">
         <v>10000000</v>
@@ -25514,13 +25514,13 @@
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B726" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C726" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D726">
         <v>10000</v>
@@ -25529,7 +25529,7 @@
         <v>10000</v>
       </c>
       <c r="F726">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G726">
         <v>10000000</v>
@@ -25543,13 +25543,13 @@
     </row>
     <row r="727" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B727" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C727" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="D727">
         <v>10000</v>
@@ -25558,7 +25558,7 @@
         <v>10000</v>
       </c>
       <c r="F727">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G727">
         <v>10000000</v>
@@ -25572,13 +25572,13 @@
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B728" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C728" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D728">
         <v>10000</v>
@@ -25587,7 +25587,7 @@
         <v>10000</v>
       </c>
       <c r="F728">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G728">
         <v>10000000</v>
@@ -25604,10 +25604,10 @@
         <v>12</v>
       </c>
       <c r="B729" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C729" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D729">
         <v>10000</v>
@@ -25633,10 +25633,10 @@
         <v>12</v>
       </c>
       <c r="B730" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C730" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="D730">
         <v>10000</v>
@@ -25662,10 +25662,10 @@
         <v>12</v>
       </c>
       <c r="B731" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C731" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D731">
         <v>10000</v>
@@ -25691,10 +25691,10 @@
         <v>12</v>
       </c>
       <c r="B732" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C732" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D732">
         <v>10000</v>
@@ -25720,10 +25720,10 @@
         <v>12</v>
       </c>
       <c r="B733" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C733" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="D733">
         <v>10000</v>
@@ -25749,10 +25749,10 @@
         <v>12</v>
       </c>
       <c r="B734" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C734" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D734">
         <v>10000</v>
@@ -25775,13 +25775,13 @@
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B735" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C735" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D735">
         <v>10000</v>
@@ -25790,7 +25790,7 @@
         <v>10000</v>
       </c>
       <c r="F735">
-        <v>100</v>
+        <v>17133.081525000001</v>
       </c>
       <c r="G735">
         <v>10000000</v>
@@ -25807,10 +25807,10 @@
         <v>12</v>
       </c>
       <c r="B736" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C736" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D736">
         <v>10000</v>
@@ -25828,296 +25828,6 @@
         <v>0</v>
       </c>
       <c r="I736">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A737" t="s">
-        <v>12</v>
-      </c>
-      <c r="B737" t="s">
-        <v>51</v>
-      </c>
-      <c r="C737" t="s">
-        <v>137</v>
-      </c>
-      <c r="D737">
-        <v>10000</v>
-      </c>
-      <c r="E737">
-        <v>10000</v>
-      </c>
-      <c r="F737">
-        <v>100</v>
-      </c>
-      <c r="G737">
-        <v>10000000</v>
-      </c>
-      <c r="H737">
-        <v>0</v>
-      </c>
-      <c r="I737">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A738" t="s">
-        <v>12</v>
-      </c>
-      <c r="B738" t="s">
-        <v>120</v>
-      </c>
-      <c r="C738" t="s">
-        <v>118</v>
-      </c>
-      <c r="D738">
-        <v>10000</v>
-      </c>
-      <c r="E738">
-        <v>10000</v>
-      </c>
-      <c r="F738">
-        <v>100</v>
-      </c>
-      <c r="G738">
-        <v>10000000</v>
-      </c>
-      <c r="H738">
-        <v>0</v>
-      </c>
-      <c r="I738">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A739" t="s">
-        <v>12</v>
-      </c>
-      <c r="B739" t="s">
-        <v>123</v>
-      </c>
-      <c r="C739" t="s">
-        <v>121</v>
-      </c>
-      <c r="D739">
-        <v>10000</v>
-      </c>
-      <c r="E739">
-        <v>10000</v>
-      </c>
-      <c r="F739">
-        <v>100</v>
-      </c>
-      <c r="G739">
-        <v>10000000</v>
-      </c>
-      <c r="H739">
-        <v>0</v>
-      </c>
-      <c r="I739">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A740" t="s">
-        <v>12</v>
-      </c>
-      <c r="B740" t="s">
-        <v>126</v>
-      </c>
-      <c r="C740" t="s">
-        <v>124</v>
-      </c>
-      <c r="D740">
-        <v>10000</v>
-      </c>
-      <c r="E740">
-        <v>10000</v>
-      </c>
-      <c r="F740">
-        <v>100</v>
-      </c>
-      <c r="G740">
-        <v>10000000</v>
-      </c>
-      <c r="H740">
-        <v>0</v>
-      </c>
-      <c r="I740">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A741" t="s">
-        <v>12</v>
-      </c>
-      <c r="B741" t="s">
-        <v>129</v>
-      </c>
-      <c r="C741" t="s">
-        <v>127</v>
-      </c>
-      <c r="D741">
-        <v>10000</v>
-      </c>
-      <c r="E741">
-        <v>10000</v>
-      </c>
-      <c r="F741">
-        <v>100</v>
-      </c>
-      <c r="G741">
-        <v>10000000</v>
-      </c>
-      <c r="H741">
-        <v>0</v>
-      </c>
-      <c r="I741">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A742" t="s">
-        <v>12</v>
-      </c>
-      <c r="B742" t="s">
-        <v>135</v>
-      </c>
-      <c r="C742" t="s">
-        <v>131</v>
-      </c>
-      <c r="D742">
-        <v>10000</v>
-      </c>
-      <c r="E742">
-        <v>10000</v>
-      </c>
-      <c r="F742">
-        <v>100</v>
-      </c>
-      <c r="G742">
-        <v>10000000</v>
-      </c>
-      <c r="H742">
-        <v>0</v>
-      </c>
-      <c r="I742">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A743" t="s">
-        <v>12</v>
-      </c>
-      <c r="B743" t="s">
-        <v>102</v>
-      </c>
-      <c r="C743" t="s">
-        <v>100</v>
-      </c>
-      <c r="D743">
-        <v>10000</v>
-      </c>
-      <c r="E743">
-        <v>10000</v>
-      </c>
-      <c r="F743">
-        <v>100</v>
-      </c>
-      <c r="G743">
-        <v>10000000</v>
-      </c>
-      <c r="H743">
-        <v>0</v>
-      </c>
-      <c r="I743">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A744" t="s">
-        <v>12</v>
-      </c>
-      <c r="B744" t="s">
-        <v>131</v>
-      </c>
-      <c r="C744" t="s">
-        <v>135</v>
-      </c>
-      <c r="D744">
-        <v>10000</v>
-      </c>
-      <c r="E744">
-        <v>10000</v>
-      </c>
-      <c r="F744">
-        <v>100</v>
-      </c>
-      <c r="G744">
-        <v>10000000</v>
-      </c>
-      <c r="H744">
-        <v>0</v>
-      </c>
-      <c r="I744">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A745" t="s">
-        <v>12</v>
-      </c>
-      <c r="B745" t="s">
-        <v>139</v>
-      </c>
-      <c r="C745" t="s">
-        <v>140</v>
-      </c>
-      <c r="D745">
-        <v>10000</v>
-      </c>
-      <c r="E745">
-        <v>10000</v>
-      </c>
-      <c r="F745">
-        <v>100</v>
-      </c>
-      <c r="G745">
-        <v>10000000</v>
-      </c>
-      <c r="H745">
-        <v>0</v>
-      </c>
-      <c r="I745">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A746" t="s">
-        <v>12</v>
-      </c>
-      <c r="B746" t="s">
-        <v>140</v>
-      </c>
-      <c r="C746" t="s">
-        <v>139</v>
-      </c>
-      <c r="D746">
-        <v>10000</v>
-      </c>
-      <c r="E746">
-        <v>10000</v>
-      </c>
-      <c r="F746">
-        <v>100</v>
-      </c>
-      <c r="G746">
-        <v>10000000</v>
-      </c>
-      <c r="H746">
-        <v>0</v>
-      </c>
-      <c r="I746">
         <v>1</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC617E2-61F9-4316-B75B-582595AA4FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767F2F6-3EEF-41EB-B557-CD1B72D02024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -15292,7 +15292,7 @@
         <v>10000</v>
       </c>
       <c r="F373">
-        <v>2020.2037108265431</v>
+        <v>22.203710826543102</v>
       </c>
       <c r="G373">
         <v>10000000</v>
@@ -15321,7 +15321,7 @@
         <v>10000</v>
       </c>
       <c r="F374">
-        <v>2014.7448142896919</v>
+        <v>16.744814289691931</v>
       </c>
       <c r="G374">
         <v>10000000</v>
@@ -15350,7 +15350,7 @@
         <v>10000</v>
       </c>
       <c r="F375">
-        <v>2011.80615123654</v>
+        <v>13.806151236540018</v>
       </c>
       <c r="G375">
         <v>10000000</v>
@@ -15379,7 +15379,7 @@
         <v>10000</v>
       </c>
       <c r="F376">
-        <v>2014.329603409235</v>
+        <v>16.329603409235006</v>
       </c>
       <c r="G376">
         <v>10000000</v>
@@ -15408,7 +15408,7 @@
         <v>10000</v>
       </c>
       <c r="F377">
-        <v>2013.9272672847619</v>
+        <v>15.927267284761911</v>
       </c>
       <c r="G377">
         <v>10000000</v>
@@ -15437,7 +15437,7 @@
         <v>10000</v>
       </c>
       <c r="F378">
-        <v>2023.209966348606</v>
+        <v>25.209966348606031</v>
       </c>
       <c r="G378">
         <v>10000000</v>
@@ -15466,7 +15466,7 @@
         <v>10000</v>
       </c>
       <c r="F379">
-        <v>2020.4258003672519</v>
+        <v>22.425800367251895</v>
       </c>
       <c r="G379">
         <v>10000000</v>
@@ -15495,7 +15495,7 @@
         <v>10000</v>
       </c>
       <c r="F380">
-        <v>2022.595196750412</v>
+        <v>24.595196750412015</v>
       </c>
       <c r="G380">
         <v>10000000</v>
@@ -15524,7 +15524,7 @@
         <v>10000</v>
       </c>
       <c r="F381">
-        <v>2016.9496162518039</v>
+        <v>18.949616251803945</v>
       </c>
       <c r="G381">
         <v>10000000</v>
@@ -15553,7 +15553,7 @@
         <v>10000</v>
       </c>
       <c r="F382">
-        <v>2014.9894346533711</v>
+        <v>16.989434653371063</v>
       </c>
       <c r="G382">
         <v>10000000</v>
@@ -15582,7 +15582,7 @@
         <v>10000</v>
       </c>
       <c r="F383">
-        <v>2011.8029325475441</v>
+        <v>13.80293254754406</v>
       </c>
       <c r="G383">
         <v>10000000</v>
@@ -15611,7 +15611,7 @@
         <v>10000</v>
       </c>
       <c r="F384">
-        <v>2019.6050346733271</v>
+        <v>21.605034673327054</v>
       </c>
       <c r="G384">
         <v>10000000</v>

--- a/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_BASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767F2F6-3EEF-41EB-B557-CD1B72D02024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFE2E38-9A8A-4488-8CD7-67ABD93F7527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
